--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 33.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 33.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -557,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-185.25</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.64227e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-65.235</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.48207236842109</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.400931414055879</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.035965386695553</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.499666481378524</v>
+      </c>
+      <c r="J2" t="n">
+        <v>590.3886297375767</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.94582735578604</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 14.109x + -29859.922</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>4.204039583916335e-11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2390.985395897151</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000386e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.81982275423088</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-145.29</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.65191e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-67.15300000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3050061050061186</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.4682904411764696</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.577008310249292</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.21507847533634</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14.69264376398916</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.2948350617868</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.150x + -24355.135</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.172147360603292e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2302.662388551644</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000003237e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8199731307578405</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-130.3100000000002</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.65466e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-67.83</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.031893687707678</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.099839743589634</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.370752089136459</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.548501742160285</v>
+      </c>
+      <c r="J4" t="n">
+        <v>11.25307049511366</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.8813083360975</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 11.164x + -21874.976</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>8.18651266872507e-12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2262.444813030469</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8199645705086693</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-120.72</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.65669e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-68.29900000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.09078726968172954</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1570871261378327</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.180935251798549</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.091418563922966</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.911495962810958</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.70529366106189</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 10.791x + -20819.546</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.100008246601336e-13</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2231.191228183235</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8199906873213119</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-114.3900000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.65641e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-68.694</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5417322834645314</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7358251057827501</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.240104166666692</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.934028294862285</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.087770008437776</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.52897811928533</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 10.441x + -19865.042</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.14872799628043e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2202.656825986536</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000026e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8200850499410226</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-102.4100000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.65833e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-69.056</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4603085553996977</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.161321909424691</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.24003451251079</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.438137603796026</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.51653384220252</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 10.417x + -19584.635</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.892303492952694e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2174.075280317639</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8202484572555447</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-104.9400000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.66245e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-69.39</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1195928753180559</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.3042912873862121</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8398406374502164</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.391939769707634</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.368094086808174</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.04022788674311</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 9.579x + -17700.284</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.891435410634521e-11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2145.9636290176</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000007962e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8204383417175178</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-89.81000000000017</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.66563e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-69.702</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9963235294118561</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8723270440251951</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.766092572658859</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.989671610169512</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.08656974053565</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 9.655x + -17641.887</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.926336666255582e-12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2118.736673633471</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8206714947602654</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-94.31000000000017</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.66705e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-70.01600000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4621276595744636</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.2642570281124456</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8114537444933201</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.74745437079728</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>83.80104399174131</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.207x + -16575.321</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.791494586579274e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2092.45788017693</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000061e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8209176843098924</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-86.44000000000005</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.67083e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-70.29900000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3496845425867304</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8812080536913663</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.297379912663769</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.013353798925547</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.65353850953689</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 8.991x + -15976.272</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>5.246897560617112e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2066.77760191502</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8211914455797964</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +1192,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +1221,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-166.79</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.59517e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-66.387</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3498648648648978</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8582846003898275</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.58509202453988</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.238054668086644</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14.76200049900674</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.41844920460768</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.479x + -26059.557</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.517162670059875e-12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2340.098654230078</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8216355947521953</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-138.5699999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.63148e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-67.569</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4799313893652959</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8714142427281782</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.537384412153228</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.851886792452837</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.38795754740228</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.396x + -24702.396</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.223984938664334e-12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2250.548177932228</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8218353998585043</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-144.4399999999998</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.64489e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-67.959</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4499043977055115</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4347989949748487</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.228180574555391</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.935774218154159</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15.7319907398999</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.9718179812352</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 11.366x + -22137.283</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.269634963428622e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2213.557889513751</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000042e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.821907509895526</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-129.6000000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.65485e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-68.316</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1988888888888962</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5314356435643262</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.763714902807723</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.314861751152055</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.96051487970739</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 11.340x + -21825.956</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.985164566310267e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2185.307694417118</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8220211664326268</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-126.0500000000002</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.66196e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-68.59</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.7158273381295092</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3926764314247396</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.989651837524171</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.078025751072936</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9.048945698289437</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.79546621383511</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 10.979x + -20844.751</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.360509578287997e-13</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2159.086460870488</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8221677501227233</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-115.6499999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.67142e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-68.84999999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1415902140672975</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5494661921708068</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.433389687235785</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.316384522369956</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.88619344014531</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 11.174x + -21002.291</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.727758901970407e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2132.533271332957</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000028e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.822371698426117</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-122.6800000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.67993e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-69.107</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.364794007490817</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2998355263157834</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8847036328873156</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.320799999999978</v>
+      </c>
+      <c r="J8" t="n">
+        <v>9.941863304148601</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.40255464874983</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 10.203x + -18847.544</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.244666819998783e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2106.050594134085</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8225854250764777</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-115.76</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.68604e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-69.355</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1738127544097739</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6409523809524335</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.328554502369687</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.801531728665196</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.040995942706003</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.62380496977696</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 10.626x + -19448.941</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.75650277969944e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2080.535938651296</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8228326258450532</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-113.03</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.69371e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-69.649</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1610021786492481</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.3360699865410465</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7757489300998794</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.494150417827324</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.82202226721379</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.13958206467814</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.743x + -17551.288</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.79939967823599e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2055.775233809128</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000003671e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8231242008609685</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-96.42000000000007</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.70096e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-69.902</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6927197802197121</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.501510989010983</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.209592760181024</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.327213695395557</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.35554874398558</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 10.118x + -18067.918</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>9.773633489941073e-13</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2030.944370319675</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8234233849416606</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-89.90999999999985</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.70871e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-70.15000000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3286713286713192</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.477029096477831</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.498476702508994</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.500185988840585</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.08605671225612</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 9.654x + -17005.346</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>7.235881936574009e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2006.715501291098</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8237496713461573</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-91.46000000000004</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.71297e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-70.40300000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1543778801843056</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6257400257400629</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8887391722810615</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.340226876090768</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>83.89811554975765</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 9.354x + -16259.351</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.401181279531593e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1983.467222920582</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8240747769248813</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-81.08999999999992</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.7203e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-70.63</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.8469184890655707</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.209730538921986</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.108705882353007</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.464153275648998</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>83.72793630392982</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 9.099x + -15627.051</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.139214244621695e-08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1960.761275159777</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000013e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8244141683169292</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-81.00999999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.72673e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-70.886</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3079491255961759</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.725074626865691</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.630298507462821</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.073650282030629</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>83.1759593932062</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 8.356x + -14130.278</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.634382466793408e-12</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1938.452634928891</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8247686032601121</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-71.17000000000007</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.73212e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-71.122</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.6015624999999677</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8166453265045015</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.733372921615076</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.22810344827591</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>82.49982684944662</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 7.596x + -12626.270</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.324614760934189e-12</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1916.914366877109</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8251218515212776</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-78.63999999999987</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.73692e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-71.342</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.08343949044586582</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.048936170212753</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.349999999999935</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.964772727272719</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>82.52185690839273</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 7.618x + -12538.885</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.128613551560124e-12</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1895.969017966253</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8254789231270092</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-68.59999999999991</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.74213e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-71.56999999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2171383647798574</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.036890243902319</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.501148105625846</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.1738435660219</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>81.84680826846503</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 6.980x + -11298.307</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.504780107670999e-09</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1874.836665168918</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8258447851166493</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-61.29999999999995</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.74817e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-71.81</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2049469964663993</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.227967806841013</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.87187500000013</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.088451668092362</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>80.45896450817675</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 5.950x + -9418.730</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>4.961926791858e-10</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1854.21653397075</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8262054678320458</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-53.86000000000013</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.7531e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-72.041</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.5336879432624162</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8279521674140824</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.82271386430676</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.062346185397784</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>78.97838886808351</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 5.134x + -7937.578</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.119806457727727e-07</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1833.870774858342</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000314e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8265912400963579</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-53.40000000000009</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.75968e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-72.23</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.6228174603174474</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.096654929577439</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.091033755274279</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.064186046511649</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>78.36171159587786</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 4.855x + -7380.131</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.62179654675983e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1813.341687290567</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000001505e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8269705879571928</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-60.09000000000015</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.7627e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-72.45399999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.05761453201377743</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7130882412773585</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.937996036379833</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>9.980899619195149</v>
+      </c>
+      <c r="K22" t="n">
+        <v>79.12113507093649</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 5.203x + -7900.013</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>8.991918499063288e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1793.115291214006</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000005826e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8273530917654275</v>
       </c>
     </row>
   </sheetData>
@@ -718,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,8 +2430,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -853,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-194.9200000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.62418e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-66.309</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3579051383398678</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6274422735346141</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.330699364214254</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.002010309278313</v>
+      </c>
+      <c r="J2" t="n">
+        <v>32.05811205644559</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.50992878672422</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.734x + -26065.306</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>3.280095204512863e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2317.987113242924</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000067e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8219186706503709</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-136.8599999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.6527e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-68.161</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4658720200752547</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.14646271510503</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.587276154571059</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.322985915492937</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7.837979990338566</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.2370321315834</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.002x + -23216.308</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.95725077814474e-12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2218.99336004235</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8221535652619504</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-116.29</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.66039e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-68.76600000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3756983240223543</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5195367573010737</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.501974333662486</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.393579072532694</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.92505461052374</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 11.260x + -21325.901</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>9.319554814802288e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2182.408812275879</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000001162e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8222091634447025</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-112.6900000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.66399e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-69.14100000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.01629139072846818</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6876080691642518</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.240201005025126</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.728072531900668</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5083756495040356</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.4734213373351</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 10.335x + -19260.088</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.974436311851379e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2156.458503682248</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000403e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8222789341415548</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-103.22</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.66739e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-69.43600000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.797222222221707</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5987261146496629</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.749275362318756</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.044019138755969</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.39960783810704</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 10.198x + -18782.084</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.036806407992319e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2132.105885280056</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000003822e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8224245199003771</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-97.26999999999998</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.67021e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-69.742</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1142857142857149</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3544262295081979</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.045775301764169</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.767153846153811</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.07618099718908</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 9.638x + -17512.347</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.275280223422031e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2107.64763762722</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000954e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8226179925527323</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-90.00999999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.67316e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-70.02200000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5517699115044945</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4197120708748424</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.405296803652972</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.482151442307846</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>83.99663404680085</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 9.509x + -17069.875</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.584913484726683e-13</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2082.236589874</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.822864831062158</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-98.52999999999997</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.67727e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-70.312</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.001857134415590141</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.5824440358438487</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.409311389880022</v>
+      </c>
+      <c r="I9" t="n">
+        <v>161.3871557774448</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7.743216677337101</v>
+      </c>
+      <c r="K9" t="n">
+        <v>83.47238817139875</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 8.739x + -15432.598</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.075103827481586e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2056.856670172265</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000001008e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8231360229418946</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-89.64999999999986</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.68281e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-70.572</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2458974358974174</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9644000000000549</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.297352024922137</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.862622309197636</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>83.38407604161917</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 8.622x + -15040.778</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.080420979594384e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2032.25573188414</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.00000000000003e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.823439546616572</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-87.29999999999995</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.68569e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-70.791</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1099173553719306</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4817073170731939</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.993661971831013</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.098720930232617</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.59096702059908</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 8.903x + -15376.035</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>5.373398823314694e-12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2008.241206799612</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.823755846138125</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-81.05000000000018</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.69017e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-71.08</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1586056644880281</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.5190909090909129</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6127129750982767</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.613631739572843</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>83.05696024543155</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 8.212x + -13960.519</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>3.893378595722602e-12</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1984.466328154522</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8240940037430385</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-75.99000000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.69528e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-71.327</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6098173515981552</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7236486486486938</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.197828863346105</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.577833500501537</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>82.61312021248209</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 7.713x + -12920.975</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.110579714385463e-09</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1961.263994443591</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000012e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.824439880056978</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-78.23000000000002</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.69888e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-71.563</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2997772264303737</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7341005387874503</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.919615727231762</v>
+      </c>
+      <c r="I14" t="n">
+        <v>134.9165910818152</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8.856622196533639</v>
+      </c>
+      <c r="K14" t="n">
+        <v>82.48480152314912</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 7.580x + -12542.358</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.002837192826697e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1938.507873288195</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8247961509654098</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-66.96000000000004</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.70251e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-71.783</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3725856697819301</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.65656324582322</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.536585365853588</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.264893617021202</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>82.09753003249165</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 7.204x + -11738.957</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.850922014780705e-08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1916.077332681858</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8251521473337728</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-67.56999999999994</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.70732e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-72.005</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.09201451905625552</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.342332613390901</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.40470756062764</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.138245219347435</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>81.84520404063061</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 6.979x + -11227.009</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>9.432620631498664e-09</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1894.06110208856</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000002523e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8255125344964727</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-69.18000000000006</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.71091e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-72.21899999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.267708762317431</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8670899335276891</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.742061237140803</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6.648971451577206</v>
+      </c>
+      <c r="J17" t="n">
+        <v>9.999633598850501</v>
+      </c>
+      <c r="K17" t="n">
+        <v>81.8250895427506</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 6.961x + -11077.095</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.853713705324117e-08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1872.683521897972</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000131e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8258785088841245</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-66.79999999999995</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.71498e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-72.47</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2252598853478025</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.4863307993201499</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.340424254473961</v>
+      </c>
+      <c r="I18" t="n">
+        <v>222.0461020926</v>
+      </c>
+      <c r="J18" t="n">
+        <v>7.81397569371829</v>
+      </c>
+      <c r="K18" t="n">
+        <v>81.03643831979308</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 6.340x + -9920.344</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>7.070886380029249e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1851.661623058608</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000128e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8262411842592029</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-54.61000000000013</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.71864e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-72.687</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1762906309751435</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9829174664108274</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.392434662998503</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.803735632183932</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>79.37238831340754</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 5.329x + -8122.600</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>3.113456246604454e-09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1831.170759546947</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000915e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8265940936078365</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-58.73000000000002</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.72255e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-72.911</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.01059876956813175</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.3243992355791574</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.441325307988031</v>
+      </c>
+      <c r="I20" t="n">
+        <v>35.48909235669068</v>
+      </c>
+      <c r="J20" t="n">
+        <v>8.353957243352188</v>
+      </c>
+      <c r="K20" t="n">
+        <v>79.3740569682499</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 5.330x + -8055.102</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.263184852026903e-09</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1810.825821371916</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8269723034584328</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-51.47000000000003</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.72595e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-73.10899999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9723878903388321</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.960927134289194</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>10.97861997858375</v>
+      </c>
+      <c r="K21" t="n">
+        <v>78.08299783233819</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 4.738x + -6998.014</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>7.600141770234294e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1790.89786862746</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000504e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8273353370494128</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-44.11000000000013</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.73001e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-73.34</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4953947368421447</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.058117520481102</v>
+      </c>
+      <c r="H22" t="n">
+        <v>358.2361475530578</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.767699649999159</v>
+      </c>
+      <c r="J22" t="n">
+        <v>11.23496669277206</v>
+      </c>
+      <c r="K22" t="n">
+        <v>74.91059589705391</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 3.709x + -5270.136</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>9.852978614820137e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1771.232181134933</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000012479e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8277055231048595</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +3564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +3668,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +3697,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-327.0500000000002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.47098e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-60.345</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2503368623676738</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6286616886846471</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.404273858921136</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.798421169668669</v>
+      </c>
+      <c r="J2" t="n">
+        <v>39.26066559743369</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.74625765654378</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.875x + -26749.093</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>5.382119852803023e-14</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2762.790328834013</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8200905420564774</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-192.8899999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.59225e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-64.264</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05472636815920133</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7280320366132469</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.218796561604556</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.459468957438557</v>
+      </c>
+      <c r="J3" t="n">
+        <v>35.40976257885469</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.31455811676005</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.201x + -27066.494</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.811649962108427e-12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2539.555963231845</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8208648474971949</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-149</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.61657e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-65.47199999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1352583586626175</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7505446623094025</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.639275956284139</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.481667309918941</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.01066443356866</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 11.455x + -24587.768</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.715798711589326e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2473.256688502569</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8210685047357984</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-113.5500000000002</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.62951e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-66.148</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6610372340425219</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8157698056801249</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.133430742256008</v>
+      </c>
+      <c r="I5" t="n">
+        <v>174.1331821617531</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.961567241737709</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.7079322811538</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 10.796x + -22734.586</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.327850201614981e-11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2431.40922110609</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.00000000019688e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8211823698758364</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-114.3600000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.64183e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-66.663</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3583434835566406</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6355415352260882</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.259999999999965</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.286107784431023</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.69587766788189</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 9.052x + -18601.303</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.873416580058254e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2393.262113320538</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000241e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8213723981014407</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-92.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.65391e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-67.111</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6368686868686673</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7930635838150775</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.467676767676839</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.763910761154819</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>83.03470530347117</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 8.185x + -16492.848</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>4.961029159219708e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2356.403134490525</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000014953e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8216248132197638</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-95.29999999999973</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.66435e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-67.459</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1737847222222228</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.3862420382165547</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.175901495162729</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.916097077761236</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>82.87920329466156</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 8.005x + -15867.965</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>9.657881295270694e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2320.550811716739</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000001489e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.82188949392447</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-83.73000000000002</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.67776e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-67.846</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3885634588563568</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.24547983310148</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.229591836734678</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.909664082687268</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>81.76779421434706</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 6.912x + -13392.606</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.090463821237727e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2285.336101852824</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8221916440689659</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-80.49000000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.68876e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-68.179</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2464012251148298</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5136239782016202</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.278227360308344</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.470738440303673</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>81.19911037390143</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 6.459x + -12272.749</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>8.07705365690651e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2250.767494666186</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000053e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8225428378599089</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-71.93000000000006</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.69876e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-68.517</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.104749679075746</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8521103896103747</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.702304609218545</v>
+      </c>
+      <c r="I11" t="n">
+        <v>270.4158163265315</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.854183510675107</v>
+      </c>
+      <c r="K11" t="n">
+        <v>80.22474139061949</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 5.804x + -10794.562</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>5.047978207424955e-12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2218.54949805969</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8228636931858677</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +4230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +4334,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +4363,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-218.0700000000002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.65784e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-65.36499999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1549234135667359</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7841256366723153</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.274252873563301</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.317019722425083</v>
+      </c>
+      <c r="J2" t="n">
+        <v>45.67542656572978</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.56228544008681</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.885x + -26604.875</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>4.459750480210157e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2301.280264219839</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.00000000000002e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8232333125127144</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-139.2900000000002</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.68056e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-67.553</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6516556291390079</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.315028901734066</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.704815073272805</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.735790370685948</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.32959225175115</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.241x + -23930.420</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.397427979873818e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2235.785445240768</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000024e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8222037681080281</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-131.01</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.69365e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-68.133</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1611023622047158</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4715762273901579</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8545353982300221</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.664186046511682</v>
+      </c>
+      <c r="J4" t="n">
+        <v>10.52590894672121</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.76062942108304</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 10.905x + -20799.784</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.973598942241607e-12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2200.995743445253</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.822051624670001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-110.6700000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.70344e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-68.48999999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5862433862433301</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9122377622377509</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.596229802513449</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.200059171597498</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.74273982432568</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 10.868x + -20488.700</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.944714651105882e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2174.548673782294</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000003598e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8220916949254755</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-112.96</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.71011e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-68.74299999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3935652173912987</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7655263157895068</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.009775086505134</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.863333333333299</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.342511895202115</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.48996503234633</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 10.366x + -19278.115</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>7.357967015642599e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2150.073866540657</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000001432e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8221880205424738</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-101.21</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.71684e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-69.023</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1708955223880645</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5300389105058139</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.672238514173972</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.313247362250765</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.41211347390004</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 10.221x + -18801.331</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.147136252978873e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2125.749199236592</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000018e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8223490635523646</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-95.14999999999986</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.72394e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-69.292</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3823617339312608</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8615835777125675</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.661111111111147</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.466819371727763</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.22639826351902</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 9.890x + -17967.859</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.343226854772491e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2101.511587230581</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000676e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8225627796279517</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-90.19000000000005</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.73011e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-69.554</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8513089005235369</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6718220338983197</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.475136116152505</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.448584298584322</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.01308378521934</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 9.535x + -17097.271</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.897653207837191e-15</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2077.385943568945</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8228046894797199</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-83.03999999999996</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.738e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-69.855</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.07552742616032819</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4673151750972815</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.760132890365512</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.006757843925887</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>83.2342641148764</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 8.429x + -14856.241</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.432346286854933e-11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2054.491693778788</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8230699406618915</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-86.18000000000006</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.73995e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-70.059</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1355263157894502</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4376249999999644</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.240355029585817</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.85544703230658</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.46946754329267</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 8.735x + -15261.003</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>8.661103947393544e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2031.761843559136</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.00000000000002e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8233651418284813</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-84.56999999999994</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.74768e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-70.33499999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2967370441458553</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.2879699248120292</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6229577464788624</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.438682432432453</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>82.69994191030902</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 7.806x + -13408.684</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.388509157290579e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2009.651086581542</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8236660766185427</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-84.16000000000008</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.75174e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-70.557</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1740975077081064</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7745059754498637</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.417360560640208</v>
+      </c>
+      <c r="I13" t="n">
+        <v>180.4342785643213</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8.225472155469568</v>
+      </c>
+      <c r="K13" t="n">
+        <v>82.59350423339932</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 7.693x + -13069.586</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.077326304336074e-09</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1988.585488459867</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000005184e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8239785177168746</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-77.10000000000014</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.7566e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-70.79000000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.07228017883756932</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.5903743315508162</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.872657743785835</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.830857740585665</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>82.0950520240951</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 7.202x + -12063.399</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>5.745777848336679e-11</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1967.523521816388</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.824319895403579</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-67.98000000000002</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.7625e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-71.023</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.7080691642650176</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.03500000000012</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.120486111111598</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.706535269709471</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>81.45129944275661</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 6.652x + -10976.940</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.495153740909959e-10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1946.970922529222</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8246568875002308</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-64.84999999999991</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.76572e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-71.26900000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2940217391304338</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.5027950310559265</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.060914760914743</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.405245346869701</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>80.5446591910015</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 6.005x + -9732.801</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>5.831367481518386e-08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1926.281913312374</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000026e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8249424076402582</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-55.42000000000007</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.77116e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-71.499</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5907407407406674</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9509459459459231</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.09574468085107</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.951561248999203</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>78.20205392491371</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 4.788x + -7522.883</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.449667463875538e-11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1905.594758694585</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8252732783295348</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-61.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.77452e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-71.691</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.05265833102465583</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7998210873784934</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.902399482802148</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>9.373800261783792</v>
+      </c>
+      <c r="K18" t="n">
+        <v>79.81499891722838</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 5.566x + -8795.637</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.613185758314617e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1885.516390533847</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8256325459764058</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-49.51999999999998</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.78037e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-71.929</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.857142857142704</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9847133757962135</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.7144047619047696</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.830672748004423</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>76.68177150693184</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 4.224x + -6428.456</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>4.754854925663405e-09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1865.299388057059</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000125e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8260036706665999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-48.67999999999984</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.78435e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-72.149</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.02145110410093945</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.708555133079825</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.41637426900578</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.649490268767301</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>74.58129143416832</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 3.626x + -5358.523</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>8.397442968575009e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1845.048278003251</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000021e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8263735995242902</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-45.74000000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.7898e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-72.392</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.005976717288810052</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8701798541264308</v>
+      </c>
+      <c r="H21" t="n">
+        <v>376.4305183689333</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.284040568836838</v>
+      </c>
+      <c r="J21" t="n">
+        <v>10.15971456049067</v>
+      </c>
+      <c r="K21" t="n">
+        <v>72.7319841918561</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 3.217x + -4640.011</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>5.1358516570408e-11</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1824.420477384447</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8267393185947064</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-35.18000000000006</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.79508e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-72.57299999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5602150537634824</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9211188811189446</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.729335260115459</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6.935952516011239</v>
+      </c>
+      <c r="K22" t="n">
+        <v>56.62122742932809</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 1.518x + -1761.508</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.263197602822182e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1803.789355113339</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000001634e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8271204443236575</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +5468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +5572,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +5601,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-413.0799999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.33552e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-57.967</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09109286165508743</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6247368421052423</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.23029480217222</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.445699765441741</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25.89752808988752</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.80765960470836</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.217x + -24610.888</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.30217154712413e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2956.937998599872</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8174605004191169</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-234.1900000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.57134e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-63.752</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1692753623188512</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3643251775848382</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.22494261667939</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.818419777023742</v>
+      </c>
+      <c r="J3" t="n">
+        <v>27.90072492848662</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.06810833982642</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 11.589x + -25885.726</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>8.913567043653538e-11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2557.221942423093</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000201e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8186566601939841</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-180.3900000000003</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.61433e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-65.229</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05367454068241435</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5109987357774642</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.354144805876208</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.990791599353727</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24.20834884299304</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.09578309874748</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 11.654x + -24952.472</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.71801248566196e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2467.479528630048</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.00000000000012e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8188875523917936</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-155.0599999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.62997e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-65.84099999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4908979089790891</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6739959839357871</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.304851425106044</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.635847526358431</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.34465363018386</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 12.280x + -25876.234</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>7.712620956868486e-11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2424.155405503865</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000314e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8189936531108708</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-142.4100000000003</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.64377e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-66.319</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03820422535212128</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7253079507278997</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.23071297989036</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.017837837837821</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8.090640802271711</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.89622426258084</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 11.196x + -23152.450</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>5.699170757619234e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2389.607794254967</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8191128686660192</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-133.0100000000002</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.65565e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-66.71299999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1233807266982714</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.053680203045704</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.605777310924286</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.060463800904861</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.68915754534621</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 10.758x + -21908.664</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>4.539782532175464e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2356.375305165897</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000108e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8192964298817575</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-115.71</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.66743e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-67.089</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4805377720870485</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8029940119760549</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.696036801132299</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.781554227156302</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.67237947613681</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 10.723x + -21553.714</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.237800321216792e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2322.96340590222</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000139e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8195047748476998</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-120.1000000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.68108e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-67.413</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1259677419354762</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7469026548672157</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.908752025931885</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.65399293286225</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.123815247365526</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.05347696306657</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 9.601x + -18920.234</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.176184117052209e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2290.390876427691</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000144e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8197871273052044</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-110.3300000000002</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.69206e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-67.696</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.100273972602726</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5396026490065886</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.152487008166276</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.253723706651552</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.25065353894558</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.932x + -19355.013</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.230642257829192e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2258.123496609084</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.820086404286682</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-108.3200000000002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.70435e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-68.003</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2180821917808301</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.048662207357943</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.203913630229352</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.792718822618102</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.89167338657766</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 9.344x + -17907.335</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.590275806571983e-11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2227.137972494579</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000297e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8203877992848398</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +6134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +6238,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +6267,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-288.8999999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.70776e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-64.414</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.07584905660377424</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.064193548386997</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.670253807106499</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.073858695652242</v>
+      </c>
+      <c r="J2" t="n">
+        <v>23.44648566664206</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.11404348831725</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 11.698x + -23620.800</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>4.750412073314734e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2285.751530651358</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000508e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8226285353246754</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-181.2999999999997</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.70426e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-67.10299999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2406578947368502</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.046183206106803</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.430521091811341</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.026781970649952</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33.57000149001077</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.68576719638271</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.256x + -25690.897</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.374154993122139e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2209.635421278826</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.00000000000296e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.822687494559461</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-156.1700000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.71258e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-67.789</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7180645161290309</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.591984732824409</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.656389452332802</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.373803827751231</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26.03766825901814</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.58964852361886</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 12.966x + -24674.245</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.196231976292161e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2174.993664999086</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.00000000000007e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8227010879327041</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-149.24</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.72158e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-68.175</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.064578833693177</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6492588369441223</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9906542056074612</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.9778681855167</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20.83001940265311</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.3194994772585</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 12.214x + -22867.404</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.664984294725045e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2146.383493230952</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000369e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8227968142890212</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-143.55</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.73062e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-68.462</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1124555160142279</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3077008928571481</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.322046285018268</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.746796874999952</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20.15279901815257</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.370899357526</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 12.350x + -22849.579</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.503533905028396e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2118.771618117882</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8229708081128672</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-143.8099999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.7394e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-68.74299999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2934086629001744</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3926380368097859</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.650085470085539</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.587379576107959</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18.14656418307256</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.16055918361722</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 11.811x + -21523.632</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.211580991380278e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2091.723620345841</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000114e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8232214068193421</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-122.28</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.75028e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-69.087</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4926708074534421</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.417706576728563</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.595721393034925</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.809263311451663</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.624638146692394</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.33776379585787</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 12.262x + -22142.381</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.280687187380231e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2065.374477437337</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000784e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8234818555599837</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-122.72</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.75623e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-69.34699999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3753564154785911</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3752762430938947</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.5808344198175</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.747588652482267</v>
+      </c>
+      <c r="J9" t="n">
+        <v>11.96818497705109</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.13304476401103</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 11.744x + -20908.723</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.162138625882955e-12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2040.539887676406</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8237680616765072</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-119.55</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.76358e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-69.59</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2436585365854118</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.550761421319756</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.594674556213093</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.834782608695657</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11.09635722699806</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.17625381144693</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 11.850x + -20853.774</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.669281048614839e-12</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2015.913478467688</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.00000000000128e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8240725341018178</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-108.6500000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.77004e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-69.914</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1056179775281018</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5942890442889717</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.534677419354755</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.072188841201735</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.700042027831177</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.97806591274967</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 11.380x + -19764.409</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.752490992783068e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1991.670976810645</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8243843461484566</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-111.8200000000002</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.77827e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-70.126</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1457085828343149</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.181107491856748</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7885148514851397</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.463856427378901</v>
+      </c>
+      <c r="J12" t="n">
+        <v>9.830817834200094</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.73535267549072</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 10.852x + -18589.918</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.706400667419449e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1968.324983783407</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000010839e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8247131982781635</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-105.2700000000002</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.78304e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-70.42400000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7941988950275826</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.1318234610917418</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.7736543909347754</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.012550607287457</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6.755100425087938</v>
+      </c>
+      <c r="K13" t="n">
+        <v>84.52678892630873</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 10.437x + -17643.119</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>6.884180004263952e-10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1945.471008717886</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000047e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8250518781297221</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-99.87999999999988</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.78987e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-70.67100000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2978896103896136</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.054352030947658</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6036748329621043</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.679307201458577</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.180720242968725</v>
+      </c>
+      <c r="K14" t="n">
+        <v>84.36149186208348</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 10.129x + -16908.978</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>4.56634905634774e-08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1922.492970663477</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8254103940322196</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-88.95000000000005</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.79545e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-70.928</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.6541198501872596</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.658260869565182</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.667524509803852</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.872619047619055</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>84.31767378985994</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 10.050x + -16587.382</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.691081942066405e-09</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1899.672234094086</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000019e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8257762745721798</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-87.98000000000002</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.80233e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-71.17400000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.6683257918550842</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.3953599999999707</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.261853188929063</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.745937813440248</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>84.01873278681242</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 9.544x + -15529.555</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.013786200246354e-08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1877.628540771008</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000004754e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8261421362313737</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-82.00999999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.80835e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-71.425</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5019955654102487</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7874476987446895</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.003699136868</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.183928571428503</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>83.59985721293998</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 8.915x + -14299.698</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.448334698901164e-08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1856.200708671826</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000352e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8264937808231316</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-80.80999999999995</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.81236e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-71.65300000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1499199999999961</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.4361921097769856</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.532315112540325</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.467336244541429</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>83.48341894311713</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 8.754x + -13869.471</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.497192290068686e-09</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1834.692257238707</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000137e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8268651153805456</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-76.11000000000013</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.81805e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-71.911</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2925696996148781</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.562924099970449</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.85518955223104</v>
+      </c>
+      <c r="I19" t="n">
+        <v>162.1301122954848</v>
+      </c>
+      <c r="J19" t="n">
+        <v>8.814223924086953</v>
+      </c>
+      <c r="K19" t="n">
+        <v>82.93010656660049</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 8.063x + -12577.835</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.24225376749655e-09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1813.426360493051</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.827226381242459</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-72.76000000000022</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.82349e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-72.129</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2925970109286169</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6305830558962776</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.929434579345934</v>
+      </c>
+      <c r="I20" t="n">
+        <v>123.1873000005592</v>
+      </c>
+      <c r="J20" t="n">
+        <v>9.270953039274513</v>
+      </c>
+      <c r="K20" t="n">
+        <v>82.63846008968149</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 7.740x + -11912.078</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>4.776005379892511e-09</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1792.483501758146</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000036e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8275886121577776</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-67.81999999999994</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.82974e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-72.36199999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1596055150152194</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9359730132649966</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.758762539153802</v>
+      </c>
+      <c r="I21" t="n">
+        <v>47.57537566104428</v>
+      </c>
+      <c r="J21" t="n">
+        <v>9.611448363536983</v>
+      </c>
+      <c r="K21" t="n">
+        <v>82.06207163726515</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 7.172x + -10863.727</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>4.606707441049849e-12</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1771.999555216325</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8279650952822593</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-66.72000000000003</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.83504e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-72.586</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.06827836582401391</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.6569812868080362</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.458485667041711</v>
+      </c>
+      <c r="I22" t="n">
+        <v>225.367033219555</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7.87666188600532</v>
+      </c>
+      <c r="K22" t="n">
+        <v>81.54512984426755</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 6.727x + -10041.348</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.996311958269129e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1752.045499276904</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000155e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8283381996472022</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +7372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +7476,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +7505,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-447.4900000000002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.42018e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-58.858</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.008651026392965833</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7536173089925484</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.558067299396029</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.618088597210754</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20.3586741442251</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.54108925815363</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.833x + -21927.464</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.613250234160914e-12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2724.81086859951</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8221723623971363</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-245.8599999999997</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.60505e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-64.26900000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4456007568590308</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9687327823691341</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.770609981515682</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.215442124258851</v>
+      </c>
+      <c r="J3" t="n">
+        <v>88.51087387189081</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.6027742174788</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.004x + -28086.546</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.924982133438359e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2412.801406091939</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000125615e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8230839475952438</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-204.8299999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.63961e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-65.637</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.06873065015479886</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.222237569060778</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.604619758351159</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.568809904153365</v>
+      </c>
+      <c r="J4" t="n">
+        <v>45.13849373294494</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.56660121506683</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 12.898x + -26752.548</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.745932340444233e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2335.828889204699</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000057e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.823231155927322</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-175.9500000000003</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.65618e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-66.33199999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2373477672530448</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.792187500000004</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.410830564784058</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.747711340206129</v>
+      </c>
+      <c r="J5" t="n">
+        <v>32.58256966503075</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.52692118623042</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 12.783x + -25998.348</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.102516286622736e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2294.508153669695</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000004148e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8233075400036555</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-163.0900000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.66848e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-66.77</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5774946921444087</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7767556874381277</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.708462104488579</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.566574037316406</v>
+      </c>
+      <c r="J6" t="n">
+        <v>18.72253390820691</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.56520778885677</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 12.894x + -25847.105</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>7.561005022350489e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2260.236937979773</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000271e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8234394011820801</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-161.72</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.68399e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-67.169</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.08157480314960862</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.09305019305018739</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.151591657519093</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.651052274270251</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18.88880736851029</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.93502674377717</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 11.283x + -22128.900</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>4.516499178642977e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2227.079988370894</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000154e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.823644715759061</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-145.96</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.69516e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-67.535</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.04660056657223897</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6382413087934158</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.525897920604922</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.053931339977845</v>
+      </c>
+      <c r="J8" t="n">
+        <v>13.56455503513303</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.17315262309545</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 11.842x + -22968.992</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>9.551461243087532e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2194.20346379568</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000023e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8239043968418819</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-140.1500000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.71144e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-67.88800000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1167400881057179</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.531403762662749</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.690322580645145</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12.94642971227228</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.71958730230838</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 10.820x + -20592.587</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.455354940667196e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2161.303038555179</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8241806170065185</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-134.99</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.72276e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-68.184</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.05263157894736913</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1687086092715229</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8568083261057844</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.683510638297869</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11.92422172197388</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.7263210322689</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 10.834x + -20336.400</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.817495786104308e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2130.387581425748</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000024e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.824483680296065</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-121.7900000000002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.73653e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-68.511</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2019036954087416</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8024060150376519</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.629750271444179</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.206484069312374</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.72152588834932</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 10.824x + -20051.697</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.378977546756153e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2099.901814899286</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000004319e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8247797665825782</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +8038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +8142,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +8171,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-217.3099999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.67715e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-65.196</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09565217391305351</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3760362694300565</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.266295979469627</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.028315217391322</v>
+      </c>
+      <c r="J2" t="n">
+        <v>30.76157683985218</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.36396841722031</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.332x + -25415.245</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.860479258100244e-12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2330.843702421264</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8203766296225971</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-145.3999999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.70687e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-67.27200000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4249999999999682</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8628468033775595</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.973017902813367</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.380555555555528</v>
+      </c>
+      <c r="J3" t="n">
+        <v>18.24815844735111</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.40269372275485</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.436x + -24266.667</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.73284888058118e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2235.560156804875</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000008756e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8205588836508823</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-130.5100000000002</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.71843e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-67.739</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6311396468699522</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.071835443037821</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.602328042328213</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.402256097561017</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.343517764773297</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.19808684191781</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 11.904x + -22851.765</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.168935081485231e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2206.961743971004</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000001023e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8203056810271685</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-129.27</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.72525e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-68.03700000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4953586497890795</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9291237113401298</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.61889999999995</v>
+      </c>
+      <c r="J5" t="n">
+        <v>13.38990426544112</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.67205111985109</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 10.723x + -20270.930</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.810032929320714e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2183.867276708726</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000014e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8201814990230871</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-125.55</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.73475e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-68.292</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03059418457648222</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4854563691073385</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.652229299363019</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10.86412025406285</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.46964869843256</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 10.328x + -19303.397</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.788368056468971e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2161.878319768788</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000071e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8202410733306622</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-114</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.74087e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-68.557</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.07424242424241982</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5051820728291012</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.389192886456758</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.13207222699904</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.32610079702669</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.54512158834066</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 10.472x + -19394.217</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.588007331900357e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2138.526822693762</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8204063357584395</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-106.73</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.74862e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-68.82299999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2285340314135975</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4889724310777098</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9429463171035998</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.031394422310729</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.34071743962127</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 10.091x + -18463.944</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.318298254907723e-12</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2114.658131670821</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8206406573280738</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-100.52</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.75641e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-69.098</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3391941391941372</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.645475638051205</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8373549883990704</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.941515151515152</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.02412406788345</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 9.553x + -17245.960</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.136616869180104e-11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2090.417843842138</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8209354191250118</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-93.62000000000012</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.76416e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-69.379</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.04947807933195218</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4847477064219801</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9733131923464232</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.865937940761754</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>83.7070182799701</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.068x + -16150.705</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.375164881893975e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2066.653463733323</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8212700572724676</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-89.28999999999996</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.76847e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-69.63800000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1564903846153702</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9706375838925765</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.119244391971689</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.10378469301945</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.55096211806342</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 8.847x + -15566.306</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.908870016520314e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2043.341897333103</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8216069672646281</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-89.04999999999995</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.77809e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-69.866</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1739932885906085</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1132379248658307</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6405815423514604</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.569369369369288</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>83.20510911841539</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 8.393x + -14565.468</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>7.322615991314992e-08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2020.16053882251</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000215e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8219646244819373</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-83.82999999999993</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.78218e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-70.121</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4521164021163669</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9412955465588009</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6748878923766799</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.931951466127305</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>82.94416941427731</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 8.079x + -13845.923</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>6.785105645371334e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1997.490241548479</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000008911e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8223245235574083</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-82.3900000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.78952e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-70.384</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1515644652222351</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.5222139229722351</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.593047566679986</v>
+      </c>
+      <c r="I14" t="n">
+        <v>164.8279800581413</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7.702394480825878</v>
+      </c>
+      <c r="K14" t="n">
+        <v>82.35141532004666</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 7.446x + -12564.124</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>9.457075084295988e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1974.89311248592</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8226886039602009</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-69.25</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.79522e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-70.627</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.204555808655929</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9003048780487891</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.356282722513064</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.783816793893121</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>81.72614278279597</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 6.877x + -11413.529</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.461366273816545e-09</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1952.456187246838</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000375e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8230478757267712</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-75.8900000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.80144e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-70.851</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.01718438594787496</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.5826787007632475</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.772797842865857</v>
+      </c>
+      <c r="I16" t="n">
+        <v>145.0816396550703</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8.281208609144949</v>
+      </c>
+      <c r="K16" t="n">
+        <v>81.72800993101737</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 6.878x + -11297.333</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>7.364805196144608e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1929.821166693281</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000034e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8234251189461679</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-67.28999999999996</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.80707e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-71.101</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0949675324675343</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.521678321678396</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.146218487394926</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.7291224686595</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>80.84340596270073</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 6.204x + -10003.088</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.090587102766822e-08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1907.316749380236</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000005716e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8238082332403217</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-55.22000000000003</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.8138e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-71.339</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9046109510085468</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7600512163892895</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.053241232731154</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.868485780169084</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>79.33274326220959</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 5.309x + -8347.900</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.8741747102887855</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2043.001623831462</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.587433214147698e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.7908331714846627</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-58.28999999999996</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.81942e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-71.55500000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1497584541062756</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.4835755813953593</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.280663780663775</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.151728553137068</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>79.67337303619779</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 5.488x + -8566.869</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.858598537852844e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1862.850944642408</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000039775e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8246121096991341</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-53.50999999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.82641e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-71.806</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.7782894736843026</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6825795644891205</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.23505535055348</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.852758620689751</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>77.64206186317803</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 4.564x + -6923.489</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>6.624299844648675e-10</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1840.576389400926</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000508e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8249970307486727</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-49.64999999999986</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.83264e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-72.03100000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1429894179894242</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7417102966841128</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.412701252235966</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.485355987055041</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>76.05685305220399</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 4.028x + -5957.660</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.354992704632171e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1818.722469865537</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000002211e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8253992353999942</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-43.68999999999983</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.83908e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-72.285</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.8309197651664135</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.326582278481058</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.007177615571756</v>
+      </c>
+      <c r="I22" t="n">
+        <v>454.6464218455981</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5.943241914527687</v>
+      </c>
+      <c r="K22" t="n">
+        <v>71.097240544453</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 2.920x + -4080.116</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>3.697873130761003e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1797.320649040756</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000001233e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8257861209646697</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +9276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +9380,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +9409,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-282</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.67718e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-66.506</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2852542372881259</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7714851485148612</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.096014492753658</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.046406882591032</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25.80996261284777</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.3613115306383</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.325x + -23546.063</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.22857215759464e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2084.168446031461</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000002262e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8220579956095682</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-196.3299999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.72726e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-69.238</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1531568228105742</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7410931174088786</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9187777777777901</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.726666666666739</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25.05202177734791</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.66532433142999</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.193x + -23123.067</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>7.982835743069414e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1952.384593254094</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000027e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.822387035401384</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-171.9399999999998</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.74296e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-69.887</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2209359605911179</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.499839486356329</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.700798722044964</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.255249999999957</v>
+      </c>
+      <c r="J4" t="n">
+        <v>25.84946700873441</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.77257657518797</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.529x + -23170.736</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.020905696240408e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1911.773568219954</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000002281e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8224192081911762</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-155.8700000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.75188e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-70.28700000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3371757925072901</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.718956043956055</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9045081967213567</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.791830708661422</v>
+      </c>
+      <c r="J5" t="n">
+        <v>24.82427040488874</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.74195647875764</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 13.431x + -22692.429</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>8.39835052292691e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1887.252671064778</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.00000000008713e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8224901751808166</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-156</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.76046e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-70.55500000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1946758238096207</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6787346603253223</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.630020923073599</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.894761539382507</v>
+      </c>
+      <c r="J6" t="n">
+        <v>26.49121766762209</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.55789911488958</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 12.872x + -21424.854</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.907067596927201e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1862.036001391821</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000029612e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8226381285534451</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-145.0899999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.76752e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-70.846</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.06146179401994146</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3204347826087292</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8577992744860031</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.351133501259423</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24.44619133088342</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.77356266450983</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 13.532x + -22272.911</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>9.615166456038347e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1834.106353993896</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8228701369842584</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-130.97</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.78237e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-71.167</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.7244274809162158</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4811111111111239</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.7914749661704583</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.827318045862494</v>
+      </c>
+      <c r="J8" t="n">
+        <v>22.36312351692236</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.70049180232654</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 13.301x + -21553.447</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.781378658722411e-12</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1805.56070717832</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8231657023917989</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-131.6099999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.79261e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-71.404</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.126560232220608</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4869639794168606</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.074228187919477</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.37984693877555</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23.63977950402403</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.80781188803128</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 13.643x + -21796.943</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>6.54342257965754e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1777.306673248712</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000001536e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.823499001339231</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-125.8899999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.80209e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-71.727</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3084636983553835</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7324676492259518</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.635679175354032</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.103264310815551</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.49453606475325</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 12.691x + -19913.253</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.14376364950672e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1750.24396193424</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000896e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8238785133233281</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-123.9200000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.81368e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-71.98699999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1387749823776312</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5792369352932712</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.282594385916409</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.426737320119038</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.172320968194426</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.31105570871897</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 12.192x + -18812.886</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.90786882155713e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1724.361446082798</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000064e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8242397079789507</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 33.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 33.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -588,19 +588,19 @@
       <c r="K2" t="n">
         <v>85.94582735578604</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 14.109x + -29859.922</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-29859.92229424242</v>
       </c>
       <c r="Y2" t="n">
         <v>4.204039583916335e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>2390.985395897151</v>
+        <v>185.25</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000386e-08</v>
@@ -640,19 +640,19 @@
       <c r="K3" t="n">
         <v>85.2948350617868</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.150x + -24355.135</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-24355.13519661768</v>
       </c>
       <c r="Y3" t="n">
         <v>2.172147360603292e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2302.662388551644</v>
+        <v>178.3899999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000003237e-08</v>
@@ -692,19 +692,19 @@
       <c r="K4" t="n">
         <v>84.8813083360975</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 11.164x + -21874.976</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-21874.97582028011</v>
       </c>
       <c r="Y4" t="n">
         <v>8.18651266872507e-12</v>
       </c>
       <c r="Z4" t="n">
-        <v>2262.444813030469</v>
+        <v>175.8700000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -744,19 +744,19 @@
       <c r="K5" t="n">
         <v>84.70529366106189</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 10.791x + -20819.546</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-20819.54562883605</v>
       </c>
       <c r="Y5" t="n">
         <v>2.100008246601336e-13</v>
       </c>
       <c r="Z5" t="n">
-        <v>2231.191228183235</v>
+        <v>172.2699999999998</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -796,19 +796,19 @@
       <c r="K6" t="n">
         <v>84.52897811928533</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 10.441x + -19865.042</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-19865.04181524135</v>
       </c>
       <c r="Y6" t="n">
         <v>3.14872799628043e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2202.656825986536</v>
+        <v>169.2700000000002</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000026e-08</v>
@@ -848,19 +848,19 @@
       <c r="K7" t="n">
         <v>84.51653384220252</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 10.417x + -19584.635</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-19584.63542263712</v>
       </c>
       <c r="Y7" t="n">
         <v>3.892303492952694e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>2174.075280317639</v>
+        <v>160.76</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000003e-08</v>
@@ -900,19 +900,19 @@
       <c r="K8" t="n">
         <v>84.04022788674311</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 9.579x + -17700.284</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-17700.28362139756</v>
       </c>
       <c r="Y8" t="n">
         <v>2.891435410634521e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>2145.9636290176</v>
+        <v>165.97</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000007962e-08</v>
@@ -952,19 +952,19 @@
       <c r="K9" t="n">
         <v>84.08656974053565</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 9.655x + -17641.887</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-17641.88651130295</v>
       </c>
       <c r="Y9" t="n">
         <v>3.926336666255582e-12</v>
       </c>
       <c r="Z9" t="n">
-        <v>2118.736673633471</v>
+        <v>153.6000000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -1004,19 +1004,19 @@
       <c r="K10" t="n">
         <v>83.80104399174131</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 9.207x + -16575.321</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-16575.32057465745</v>
       </c>
       <c r="Y10" t="n">
         <v>1.791494586579274e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>2092.45788017693</v>
+        <v>159.51</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000061e-08</v>
@@ -1056,19 +1056,19 @@
       <c r="K11" t="n">
         <v>83.65353850953689</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 8.991x + -15976.272</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-15976.27246472913</v>
       </c>
       <c r="Y11" t="n">
         <v>5.246897560617112e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2066.77760191502</v>
+        <v>153.26</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1254,19 +1254,19 @@
       <c r="K2" t="n">
         <v>85.41844920460768</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.479x + -26059.557</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-26059.5570109247</v>
       </c>
       <c r="Y2" t="n">
         <v>6.517162670059875e-12</v>
       </c>
       <c r="Z2" t="n">
-        <v>2340.098654230078</v>
+        <v>189.0099999999998</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -1306,19 +1306,19 @@
       <c r="K3" t="n">
         <v>85.38795754740228</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.396x + -24702.396</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-24702.3958322783</v>
       </c>
       <c r="Y3" t="n">
         <v>3.223984938664334e-12</v>
       </c>
       <c r="Z3" t="n">
-        <v>2250.548177932228</v>
+        <v>175.6800000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -1358,19 +1358,19 @@
       <c r="K4" t="n">
         <v>84.9718179812352</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 11.366x + -22137.283</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-22137.28255878998</v>
       </c>
       <c r="Y4" t="n">
         <v>1.269634963428622e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2213.557889513751</v>
+        <v>183.0599999999997</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000042e-08</v>
@@ -1410,19 +1410,19 @@
       <c r="K5" t="n">
         <v>84.96051487970739</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 11.340x + -21825.956</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-21825.95631522888</v>
       </c>
       <c r="Y5" t="n">
         <v>1.985164566310267e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2185.307694417118</v>
+        <v>176.0699999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -1462,19 +1462,19 @@
       <c r="K6" t="n">
         <v>84.79546621383511</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 10.979x + -20844.751</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-20844.75145816288</v>
       </c>
       <c r="Y6" t="n">
         <v>2.360509578287997e-13</v>
       </c>
       <c r="Z6" t="n">
-        <v>2159.086460870488</v>
+        <v>174.04</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -1514,19 +1514,19 @@
       <c r="K7" t="n">
         <v>84.88619344014531</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 11.174x + -21002.291</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-21002.29092656574</v>
       </c>
       <c r="Y7" t="n">
         <v>3.727758901970407e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2132.533271332957</v>
+        <v>167.1999999999998</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000028e-08</v>
@@ -1566,19 +1566,19 @@
       <c r="K8" t="n">
         <v>84.40255464874983</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 10.203x + -18847.544</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-18847.54439819363</v>
       </c>
       <c r="Y8" t="n">
         <v>1.244666819998783e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2106.050594134085</v>
+        <v>174.73</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000003e-08</v>
@@ -1618,19 +1618,19 @@
       <c r="K9" t="n">
         <v>84.62380496977696</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 10.626x + -19448.941</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-19448.94091516426</v>
       </c>
       <c r="Y9" t="n">
         <v>1.75650277969944e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>2080.535938651296</v>
+        <v>168.4099999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -1670,19 +1670,19 @@
       <c r="K10" t="n">
         <v>84.13958206467814</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 9.743x + -17551.288</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-17551.28809108364</v>
       </c>
       <c r="Y10" t="n">
         <v>4.79939967823599e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>2055.775233809128</v>
+        <v>171.46</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000003671e-08</v>
@@ -1722,19 +1722,19 @@
       <c r="K11" t="n">
         <v>84.35554874398558</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 10.118x + -18067.918</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-18067.91776146764</v>
       </c>
       <c r="Y11" t="n">
         <v>9.773633489941073e-13</v>
       </c>
       <c r="Z11" t="n">
-        <v>2030.944370319675</v>
+        <v>157.1400000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -1774,19 +1774,19 @@
       <c r="K12" t="n">
         <v>84.08605671225612</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 9.654x + -17005.346</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-17005.34640597626</v>
       </c>
       <c r="Y12" t="n">
         <v>7.235881936574009e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>2006.715501291098</v>
+        <v>152.98</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -1826,19 +1826,19 @@
       <c r="K13" t="n">
         <v>83.89811554975765</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 9.354x + -16259.351</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-16259.35119934392</v>
       </c>
       <c r="Y13" t="n">
         <v>1.401181279531593e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>1983.467222920582</v>
+        <v>155.75</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000007e-08</v>
@@ -1878,19 +1878,19 @@
       <c r="K14" t="n">
         <v>83.72793630392982</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 9.099x + -15627.051</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-15627.05089699396</v>
       </c>
       <c r="Y14" t="n">
         <v>2.139214244621695e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>1960.761275159777</v>
+        <v>147</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000013e-08</v>
@@ -1930,19 +1930,19 @@
       <c r="K15" t="n">
         <v>83.1759593932062</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 8.356x + -14130.278</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-14130.27782756219</v>
       </c>
       <c r="Y15" t="n">
         <v>1.634382466793408e-12</v>
       </c>
       <c r="Z15" t="n">
-        <v>1938.452634928891</v>
+        <v>151.05</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -1982,19 +1982,19 @@
       <c r="K16" t="n">
         <v>82.49982684944662</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 7.596x + -12626.270</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-12626.27035864673</v>
       </c>
       <c r="Y16" t="n">
         <v>1.324614760934189e-12</v>
       </c>
       <c r="Z16" t="n">
-        <v>1916.914366877109</v>
+        <v>143.98</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -2034,19 +2034,19 @@
       <c r="K17" t="n">
         <v>82.52185690839273</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 7.618x + -12538.885</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-12538.88526326918</v>
       </c>
       <c r="Y17" t="n">
         <v>1.128613551560124e-12</v>
       </c>
       <c r="Z17" t="n">
-        <v>1895.969017966253</v>
+        <v>152.3499999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -2086,19 +2086,19 @@
       <c r="K18" t="n">
         <v>81.84680826846503</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 6.980x + -11298.307</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-11298.30669920068</v>
       </c>
       <c r="Y18" t="n">
         <v>1.504780107670999e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>1874.836665168918</v>
+        <v>144.1900000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000003e-08</v>
@@ -2138,19 +2138,19 @@
       <c r="K19" t="n">
         <v>80.45896450817675</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 5.950x + -9418.730</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-9418.730443240538</v>
       </c>
       <c r="Y19" t="n">
         <v>4.961926791858e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>1854.21653397075</v>
+        <v>140.95</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000001e-08</v>
@@ -2190,19 +2190,19 @@
       <c r="K20" t="n">
         <v>78.97838886808351</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 5.134x + -7937.578</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-7937.577567431398</v>
       </c>
       <c r="Y20" t="n">
         <v>1.119806457727727e-07</v>
       </c>
       <c r="Z20" t="n">
-        <v>1833.870774858342</v>
+        <v>136.1100000000001</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000314e-08</v>
@@ -2242,19 +2242,19 @@
       <c r="K21" t="n">
         <v>78.36171159587786</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 4.855x + -7380.131</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-7380.131259702622</v>
       </c>
       <c r="Y21" t="n">
         <v>2.62179654675983e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>1813.341687290567</v>
+        <v>136.5599999999999</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000001505e-08</v>
@@ -2294,19 +2294,19 @@
       <c r="K22" t="n">
         <v>79.12113507093649</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 5.203x + -7900.013</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-7900.013300919956</v>
       </c>
       <c r="Y22" t="n">
         <v>8.991918499063288e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>1793.115291214006</v>
+        <v>143.7900000000002</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000005826e-08</v>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2492,19 +2492,19 @@
       <c r="K2" t="n">
         <v>85.50992878672422</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.734x + -26065.306</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-26065.30633022426</v>
       </c>
       <c r="Y2" t="n">
         <v>3.280095204512863e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2317.987113242924</v>
+        <v>194.9200000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000067e-08</v>
@@ -2544,19 +2544,19 @@
       <c r="K3" t="n">
         <v>85.2370321315834</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.002x + -23216.308</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-23216.30797720005</v>
       </c>
       <c r="Y3" t="n">
         <v>1.95725077814474e-12</v>
       </c>
       <c r="Z3" t="n">
-        <v>2218.99336004235</v>
+        <v>176.2700000000002</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -2596,19 +2596,19 @@
       <c r="K4" t="n">
         <v>84.92505461052374</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 11.260x + -21325.901</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-21325.90088680392</v>
       </c>
       <c r="Y4" t="n">
         <v>9.319554814802288e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2182.408812275879</v>
+        <v>167.1299999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001162e-08</v>
@@ -2648,19 +2648,19 @@
       <c r="K5" t="n">
         <v>84.4734213373351</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 10.335x + -19260.088</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-19260.08818227364</v>
       </c>
       <c r="Y5" t="n">
         <v>3.974436311851379e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2156.458503682248</v>
+        <v>170.8200000000002</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000403e-08</v>
@@ -2700,19 +2700,19 @@
       <c r="K6" t="n">
         <v>84.39960783810704</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 10.198x + -18782.084</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-18782.08376467229</v>
       </c>
       <c r="Y6" t="n">
         <v>1.036806407992319e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2132.105885280056</v>
+        <v>163.03</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000003822e-08</v>
@@ -2752,19 +2752,19 @@
       <c r="K7" t="n">
         <v>84.07618099718908</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 9.638x + -17512.347</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-17512.34656175634</v>
       </c>
       <c r="Y7" t="n">
         <v>3.275280223422031e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2107.64763762722</v>
+        <v>161.5800000000002</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000954e-08</v>
@@ -2804,19 +2804,19 @@
       <c r="K8" t="n">
         <v>83.99663404680085</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 9.509x + -17069.875</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-17069.87532735561</v>
       </c>
       <c r="Y8" t="n">
         <v>5.584913484726683e-13</v>
       </c>
       <c r="Z8" t="n">
-        <v>2082.236589874</v>
+        <v>155.95</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -2856,19 +2856,19 @@
       <c r="K9" t="n">
         <v>83.47238817139875</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 8.739x + -15432.598</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-15432.59836525563</v>
       </c>
       <c r="Y9" t="n">
         <v>3.075103827481586e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2056.856670172265</v>
+        <v>166.8999999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001008e-08</v>
@@ -2908,19 +2908,19 @@
       <c r="K10" t="n">
         <v>83.38407604161917</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 8.622x + -15040.778</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-15040.77787025728</v>
       </c>
       <c r="Y10" t="n">
         <v>3.080420979594384e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>2032.25573188414</v>
+        <v>160.03</v>
       </c>
       <c r="AA10" t="n">
         <v>1.00000000000003e-08</v>
@@ -2960,19 +2960,19 @@
       <c r="K11" t="n">
         <v>83.59096702059908</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 8.903x + -15376.035</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-15376.03455005842</v>
       </c>
       <c r="Y11" t="n">
         <v>5.373398823314694e-12</v>
       </c>
       <c r="Z11" t="n">
-        <v>2008.241206799612</v>
+        <v>155.6999999999998</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -3012,19 +3012,19 @@
       <c r="K12" t="n">
         <v>83.05696024543155</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 8.212x + -13960.519</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-13960.51888178542</v>
       </c>
       <c r="Y12" t="n">
         <v>3.893378595722602e-12</v>
       </c>
       <c r="Z12" t="n">
-        <v>1984.466328154522</v>
+        <v>153.8300000000002</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -3064,19 +3064,19 @@
       <c r="K13" t="n">
         <v>82.61312021248209</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 7.713x + -12920.975</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-12920.97525885741</v>
       </c>
       <c r="Y13" t="n">
         <v>2.110579714385463e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>1961.263994443591</v>
+        <v>151.1400000000001</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000012e-08</v>
@@ -3116,19 +3116,19 @@
       <c r="K14" t="n">
         <v>82.48480152314912</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 7.580x + -12542.358</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-12542.35796933517</v>
       </c>
       <c r="Y14" t="n">
         <v>1.002837192826697e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>1938.507873288195</v>
+        <v>153.9400000000001</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000001e-08</v>
@@ -3168,19 +3168,19 @@
       <c r="K15" t="n">
         <v>82.09753003249165</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 7.204x + -11738.957</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-11738.95732576838</v>
       </c>
       <c r="Y15" t="n">
         <v>2.850922014780705e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>1916.077332681858</v>
+        <v>142.21</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000009e-08</v>
@@ -3220,19 +3220,19 @@
       <c r="K16" t="n">
         <v>81.84520404063061</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 6.979x + -11227.009</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-11227.0086366115</v>
       </c>
       <c r="Y16" t="n">
         <v>9.432620631498664e-09</v>
       </c>
       <c r="Z16" t="n">
-        <v>1894.06110208856</v>
+        <v>143.6900000000001</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000002523e-08</v>
@@ -3272,19 +3272,19 @@
       <c r="K17" t="n">
         <v>81.8250895427506</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 6.961x + -11077.095</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-11077.09485966097</v>
       </c>
       <c r="Y17" t="n">
         <v>3.853713705324117e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>1872.683521897972</v>
+        <v>145.8</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000131e-08</v>
@@ -3324,19 +3324,19 @@
       <c r="K18" t="n">
         <v>81.03643831979308</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 6.340x + -9920.344</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-9920.344163946565</v>
       </c>
       <c r="Y18" t="n">
         <v>7.070886380029249e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>1851.661623058608</v>
+        <v>146.9699999999998</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000128e-08</v>
@@ -3376,19 +3376,19 @@
       <c r="K19" t="n">
         <v>79.37238831340754</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 5.329x + -8122.600</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-8122.600467169436</v>
       </c>
       <c r="Y19" t="n">
         <v>3.113456246604454e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>1831.170759546947</v>
+        <v>136.3700000000001</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000915e-08</v>
@@ -3428,19 +3428,19 @@
       <c r="K20" t="n">
         <v>79.3740569682499</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 5.330x + -8055.102</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-8055.101954908589</v>
       </c>
       <c r="Y20" t="n">
         <v>1.263184852026903e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>1810.825821371916</v>
+        <v>142.95</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000006e-08</v>
@@ -3480,19 +3480,19 @@
       <c r="K21" t="n">
         <v>78.08299783233819</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 4.738x + -6998.014</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-6998.014253918594</v>
       </c>
       <c r="Y21" t="n">
         <v>7.600141770234294e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>1790.89786862746</v>
+        <v>135.23</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000504e-08</v>
@@ -3532,19 +3532,19 @@
       <c r="K22" t="n">
         <v>74.91059589705391</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 3.709x + -5270.136</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-5270.136166751174</v>
       </c>
       <c r="Y22" t="n">
         <v>9.852978614820137e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>1771.232181134933</v>
+        <v>131.49</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000012479e-08</v>
@@ -3670,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -3730,19 +3730,19 @@
       <c r="K2" t="n">
         <v>84.74625765654378</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.875x + -26749.093</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-26749.09270856584</v>
       </c>
       <c r="Y2" t="n">
         <v>5.382119852803023e-14</v>
       </c>
       <c r="Z2" t="n">
-        <v>2762.790328834013</v>
+        <v>327.0500000000002</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -3782,19 +3782,19 @@
       <c r="K3" t="n">
         <v>85.31455811676005</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.201x + -27066.494</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-27066.49417195981</v>
       </c>
       <c r="Y3" t="n">
         <v>3.811649962108427e-12</v>
       </c>
       <c r="Z3" t="n">
-        <v>2539.555963231845</v>
+        <v>200.21</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -3834,19 +3834,19 @@
       <c r="K4" t="n">
         <v>85.01066443356866</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 11.455x + -24587.768</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-24587.76846220544</v>
       </c>
       <c r="Y4" t="n">
         <v>2.715798711589326e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2473.256688502569</v>
+        <v>187.8600000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -3886,19 +3886,19 @@
       <c r="K5" t="n">
         <v>84.7079322811538</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 10.796x + -22734.586</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-22734.58597698457</v>
       </c>
       <c r="Y5" t="n">
         <v>3.327850201614981e-11</v>
       </c>
       <c r="Z5" t="n">
-        <v>2431.40922110609</v>
+        <v>169.6900000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.00000000019688e-08</v>
@@ -3938,19 +3938,19 @@
       <c r="K6" t="n">
         <v>83.69587766788189</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 9.052x + -18601.303</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-18601.30345305698</v>
       </c>
       <c r="Y6" t="n">
         <v>1.873416580058254e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>2393.262113320538</v>
+        <v>181.8700000000003</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000241e-08</v>
@@ -3990,19 +3990,19 @@
       <c r="K7" t="n">
         <v>83.03470530347117</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 8.185x + -16492.848</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-16492.84802676491</v>
       </c>
       <c r="Y7" t="n">
         <v>4.961029159219708e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>2356.403134490525</v>
+        <v>169</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000014953e-08</v>
@@ -4042,19 +4042,19 @@
       <c r="K8" t="n">
         <v>82.87920329466156</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 8.005x + -15867.965</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-15867.96524100771</v>
       </c>
       <c r="Y8" t="n">
         <v>9.657881295270694e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>2320.550811716739</v>
+        <v>172.3299999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000001489e-08</v>
@@ -4094,19 +4094,19 @@
       <c r="K9" t="n">
         <v>81.76779421434706</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 6.912x + -13392.606</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-13392.60553694756</v>
       </c>
       <c r="Y9" t="n">
         <v>1.090463821237727e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>2285.336101852824</v>
+        <v>168.2000000000003</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000002e-08</v>
@@ -4146,19 +4146,19 @@
       <c r="K10" t="n">
         <v>81.19911037390143</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 6.459x + -12272.749</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-12272.7489078232</v>
       </c>
       <c r="Y10" t="n">
         <v>8.07705365690651e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>2250.767494666186</v>
+        <v>166.5500000000002</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000053e-08</v>
@@ -4198,19 +4198,19 @@
       <c r="K11" t="n">
         <v>80.22474139061949</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 5.804x + -10794.562</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-10794.5618610638</v>
       </c>
       <c r="Y11" t="n">
         <v>5.047978207424955e-12</v>
       </c>
       <c r="Z11" t="n">
-        <v>2218.54949805969</v>
+        <v>161.4299999999998</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -4336,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4396,19 +4396,19 @@
       <c r="K2" t="n">
         <v>85.56228544008681</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.885x + -26604.875</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-26604.87470843148</v>
       </c>
       <c r="Y2" t="n">
         <v>4.459750480210157e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>2301.280264219839</v>
+        <v>218.0700000000002</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000002e-08</v>
@@ -4448,19 +4448,19 @@
       <c r="K3" t="n">
         <v>85.32959225175115</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.241x + -23930.420</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-23930.41968659493</v>
       </c>
       <c r="Y3" t="n">
         <v>2.397427979873818e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>2235.785445240768</v>
+        <v>175.2500000000002</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000024e-08</v>
@@ -4500,19 +4500,19 @@
       <c r="K4" t="n">
         <v>84.76062942108304</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 10.905x + -20799.784</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-20799.78435183375</v>
       </c>
       <c r="Y4" t="n">
         <v>1.973598942241607e-12</v>
       </c>
       <c r="Z4" t="n">
-        <v>2200.995743445253</v>
+        <v>177.2700000000002</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -4552,19 +4552,19 @@
       <c r="K5" t="n">
         <v>84.74273982432568</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 10.868x + -20488.700</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-20488.69997991271</v>
       </c>
       <c r="Y5" t="n">
         <v>2.944714651105882e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2174.548673782294</v>
+        <v>164.52</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000003598e-08</v>
@@ -4604,19 +4604,19 @@
       <c r="K6" t="n">
         <v>84.48996503234633</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 10.366x + -19278.115</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-19278.11534444883</v>
       </c>
       <c r="Y6" t="n">
         <v>7.357967015642599e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2150.073866540657</v>
+        <v>167.96</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001432e-08</v>
@@ -4656,19 +4656,19 @@
       <c r="K7" t="n">
         <v>84.41211347390004</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 10.221x + -18801.331</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-18801.33133444286</v>
       </c>
       <c r="Y7" t="n">
         <v>2.147136252978873e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2125.749199236592</v>
+        <v>159.71</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000018e-08</v>
@@ -4708,19 +4708,19 @@
       <c r="K8" t="n">
         <v>84.22639826351902</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 9.890x + -17967.859</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-17967.85918710846</v>
       </c>
       <c r="Y8" t="n">
         <v>6.343226854772491e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>2101.511587230581</v>
+        <v>156.8699999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000676e-08</v>
@@ -4760,19 +4760,19 @@
       <c r="K9" t="n">
         <v>84.01308378521934</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 9.535x + -17097.271</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-17097.27075471849</v>
       </c>
       <c r="Y9" t="n">
         <v>1.897653207837191e-15</v>
       </c>
       <c r="Z9" t="n">
-        <v>2077.385943568945</v>
+        <v>153.74</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -4812,19 +4812,19 @@
       <c r="K10" t="n">
         <v>83.2342641148764</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 8.429x + -14856.241</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-14856.2406325536</v>
       </c>
       <c r="Y10" t="n">
         <v>2.432346286854933e-11</v>
       </c>
       <c r="Z10" t="n">
-        <v>2054.491693778788</v>
+        <v>154.26</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -4864,19 +4864,19 @@
       <c r="K11" t="n">
         <v>83.46946754329267</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 8.735x + -15261.003</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-15261.00259271918</v>
       </c>
       <c r="Y11" t="n">
         <v>8.661103947393544e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2031.761843559136</v>
+        <v>154.1400000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000002e-08</v>
@@ -4916,19 +4916,19 @@
       <c r="K12" t="n">
         <v>82.69994191030902</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 7.806x + -13408.684</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-13408.68380952146</v>
       </c>
       <c r="Y12" t="n">
         <v>2.388509157290579e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>2009.651086581542</v>
+        <v>158.3799999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000001e-08</v>
@@ -4968,19 +4968,19 @@
       <c r="K13" t="n">
         <v>82.59350423339932</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 7.693x + -13069.586</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-13069.58629970245</v>
       </c>
       <c r="Y13" t="n">
         <v>1.077326304336074e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>1988.585488459867</v>
+        <v>158.05</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000005184e-08</v>
@@ -5020,19 +5020,19 @@
       <c r="K14" t="n">
         <v>82.0950520240951</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 7.202x + -12063.399</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-12063.39893161598</v>
       </c>
       <c r="Y14" t="n">
         <v>5.745777848336679e-11</v>
       </c>
       <c r="Z14" t="n">
-        <v>1967.523521816388</v>
+        <v>152.6000000000001</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -5072,19 +5072,19 @@
       <c r="K15" t="n">
         <v>81.45129944275661</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 6.652x + -10976.940</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-10976.93973333983</v>
       </c>
       <c r="Y15" t="n">
         <v>2.495153740909959e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>1946.970922529222</v>
+        <v>147.0999999999999</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -5124,19 +5124,19 @@
       <c r="K16" t="n">
         <v>80.5446591910015</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 6.005x + -9732.801</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-9732.800878275835</v>
       </c>
       <c r="Y16" t="n">
         <v>5.831367481518386e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>1926.281913312374</v>
+        <v>146.3599999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000026e-08</v>
@@ -5176,19 +5176,19 @@
       <c r="K17" t="n">
         <v>78.20205392491371</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 4.788x + -7522.883</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-7522.882911668597</v>
       </c>
       <c r="Y17" t="n">
         <v>8.449667463875538e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>1905.594758694585</v>
+        <v>140.9100000000001</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -5228,19 +5228,19 @@
       <c r="K18" t="n">
         <v>79.81499891722838</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 5.566x + -8795.637</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-8795.636872520881</v>
       </c>
       <c r="Y18" t="n">
         <v>1.613185758314617e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>1885.516390533847</v>
+        <v>145.5799999999999</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000005e-08</v>
@@ -5280,19 +5280,19 @@
       <c r="K19" t="n">
         <v>76.68177150693184</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 4.224x + -6428.456</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-6428.455628008577</v>
       </c>
       <c r="Y19" t="n">
         <v>4.754854925663405e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>1865.299388057059</v>
+        <v>137.8</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000125e-08</v>
@@ -5332,19 +5332,19 @@
       <c r="K20" t="n">
         <v>74.58129143416832</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 3.626x + -5358.523</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-5358.523427761919</v>
       </c>
       <c r="Y20" t="n">
         <v>8.397442968575009e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>1845.048278003251</v>
+        <v>137.99</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000021e-08</v>
@@ -5384,19 +5384,19 @@
       <c r="K21" t="n">
         <v>72.7319841918561</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 3.217x + -4640.011</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-4640.010902268752</v>
       </c>
       <c r="Y21" t="n">
         <v>5.1358516570408e-11</v>
       </c>
       <c r="Z21" t="n">
-        <v>1824.420477384447</v>
+        <v>138.3499999999999</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -5436,19 +5436,19 @@
       <c r="K22" t="n">
         <v>56.62122742932809</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 1.518x + -1761.508</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-1761.507980488734</v>
       </c>
       <c r="Y22" t="n">
         <v>2.263197602822182e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>1803.789355113339</v>
+        <v>127.5600000000002</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000001634e-08</v>
@@ -5574,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5634,19 +5634,19 @@
       <c r="K2" t="n">
         <v>83.80765960470836</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.217x + -24610.888</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-24610.88784398716</v>
       </c>
       <c r="Y2" t="n">
         <v>1.30217154712413e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2956.937998599872</v>
+        <v>413.0799999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000002e-08</v>
@@ -5686,19 +5686,19 @@
       <c r="K3" t="n">
         <v>85.06810833982642</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 11.589x + -25885.726</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-25885.72601678587</v>
       </c>
       <c r="Y3" t="n">
         <v>8.913567043653538e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>2557.221942423093</v>
+        <v>234.1900000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000201e-08</v>
@@ -5738,19 +5738,19 @@
       <c r="K4" t="n">
         <v>85.09578309874748</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 11.654x + -24952.472</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-24952.47167301413</v>
       </c>
       <c r="Y4" t="n">
         <v>2.71801248566196e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2467.479528630048</v>
+        <v>199.0599999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000000012e-08</v>
@@ -5790,19 +5790,19 @@
       <c r="K5" t="n">
         <v>85.34465363018386</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 12.280x + -25876.234</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-25876.23364109322</v>
       </c>
       <c r="Y5" t="n">
         <v>7.712620956868486e-11</v>
       </c>
       <c r="Z5" t="n">
-        <v>2424.155405503865</v>
+        <v>184.7399999999998</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000314e-08</v>
@@ -5842,19 +5842,19 @@
       <c r="K6" t="n">
         <v>84.89622426258084</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 11.196x + -23152.450</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-23152.4503518414</v>
       </c>
       <c r="Y6" t="n">
         <v>5.699170757619234e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>2389.607794254967</v>
+        <v>184.1500000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000003e-08</v>
@@ -5894,19 +5894,19 @@
       <c r="K7" t="n">
         <v>84.68915754534621</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 10.758x + -21908.664</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-21908.66417864332</v>
       </c>
       <c r="Y7" t="n">
         <v>4.539782532175464e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>2356.375305165897</v>
+        <v>182.3499999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000108e-08</v>
@@ -5946,19 +5946,19 @@
       <c r="K8" t="n">
         <v>84.67237947613681</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 10.723x + -21553.714</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-21553.71420906695</v>
       </c>
       <c r="Y8" t="n">
         <v>3.237800321216792e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>2322.96340590222</v>
+        <v>171.23</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000139e-08</v>
@@ -5998,19 +5998,19 @@
       <c r="K9" t="n">
         <v>84.05347696306657</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 9.601x + -18920.234</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-18920.23360691632</v>
       </c>
       <c r="Y9" t="n">
         <v>2.176184117052209e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>2290.390876427691</v>
+        <v>180.6099999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000144e-08</v>
@@ -6050,19 +6050,19 @@
       <c r="K10" t="n">
         <v>84.25065353894558</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 9.932x + -19355.013</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-19355.01344117668</v>
       </c>
       <c r="Y10" t="n">
         <v>1.230642257829192e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2258.123496609084</v>
+        <v>171.7</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000007e-08</v>
@@ -6102,19 +6102,19 @@
       <c r="K11" t="n">
         <v>83.89167338657766</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 9.344x + -17907.335</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-17907.33525987165</v>
       </c>
       <c r="Y11" t="n">
         <v>1.590275806571983e-11</v>
       </c>
       <c r="Z11" t="n">
-        <v>2227.137972494579</v>
+        <v>172.79</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000297e-08</v>
@@ -6240,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6300,19 +6300,19 @@
       <c r="K2" t="n">
         <v>85.11404348831725</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 11.698x + -23620.800</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-23620.79989265063</v>
       </c>
       <c r="Y2" t="n">
         <v>4.750412073314734e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2285.751530651358</v>
+        <v>288.8999999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000508e-08</v>
@@ -6352,19 +6352,19 @@
       <c r="K3" t="n">
         <v>85.68576719638271</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.256x + -25690.897</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-25690.8969326318</v>
       </c>
       <c r="Y3" t="n">
         <v>2.374154993122139e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2209.635421278826</v>
+        <v>181.2999999999997</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000296e-08</v>
@@ -6404,19 +6404,19 @@
       <c r="K4" t="n">
         <v>85.58964852361886</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 12.966x + -24674.245</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-24674.24474221483</v>
       </c>
       <c r="Y4" t="n">
         <v>5.196231976292161e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2174.993664999086</v>
+        <v>175.3400000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000000007e-08</v>
@@ -6456,19 +6456,19 @@
       <c r="K5" t="n">
         <v>85.3194994772585</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 12.214x + -22867.404</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-22867.40411278554</v>
       </c>
       <c r="Y5" t="n">
         <v>3.664984294725045e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2146.383493230952</v>
+        <v>176.0899999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000369e-08</v>
@@ -6508,19 +6508,19 @@
       <c r="K6" t="n">
         <v>85.370899357526</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 12.350x + -22849.579</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-22849.57908735387</v>
       </c>
       <c r="Y6" t="n">
         <v>3.503533905028396e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2118.771618117882</v>
+        <v>172.8199999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000001e-08</v>
@@ -6560,19 +6560,19 @@
       <c r="K7" t="n">
         <v>85.16055918361722</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 11.811x + -21523.632</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-21523.63167762938</v>
       </c>
       <c r="Y7" t="n">
         <v>1.211580991380278e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2091.723620345841</v>
+        <v>175.55</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000114e-08</v>
@@ -6612,19 +6612,19 @@
       <c r="K8" t="n">
         <v>85.33776379585787</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 12.262x + -22142.381</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-22142.38100978825</v>
       </c>
       <c r="Y8" t="n">
         <v>1.280687187380231e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2065.374477437337</v>
+        <v>162.3299999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000784e-08</v>
@@ -6664,19 +6664,19 @@
       <c r="K9" t="n">
         <v>85.13304476401103</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 11.744x + -20908.723</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-20908.72258690815</v>
       </c>
       <c r="Y9" t="n">
         <v>2.162138625882955e-12</v>
       </c>
       <c r="Z9" t="n">
-        <v>2040.539887676406</v>
+        <v>164.27</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -6716,19 +6716,19 @@
       <c r="K10" t="n">
         <v>85.17625381144693</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 11.850x + -20853.774</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-20853.77385718287</v>
       </c>
       <c r="Y10" t="n">
         <v>4.669281048614839e-12</v>
       </c>
       <c r="Z10" t="n">
-        <v>2015.913478467688</v>
+        <v>161.23</v>
       </c>
       <c r="AA10" t="n">
         <v>1.00000000000128e-08</v>
@@ -6768,19 +6768,19 @@
       <c r="K11" t="n">
         <v>84.97806591274967</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 11.380x + -19764.409</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-19764.40946694198</v>
       </c>
       <c r="Y11" t="n">
         <v>3.752490992783068e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>1991.670976810645</v>
+        <v>156.98</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000005e-08</v>
@@ -6820,19 +6820,19 @@
       <c r="K12" t="n">
         <v>84.73535267549072</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 10.852x + -18589.918</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-18589.9176031032</v>
       </c>
       <c r="Y12" t="n">
         <v>1.706400667419449e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>1968.324983783407</v>
+        <v>160.9100000000001</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000010839e-08</v>
@@ -6872,19 +6872,19 @@
       <c r="K13" t="n">
         <v>84.52678892630873</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 10.437x + -17643.119</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-17643.11913838646</v>
       </c>
       <c r="Y13" t="n">
         <v>6.884180004263952e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>1945.471008717886</v>
+        <v>157.8100000000002</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000047e-08</v>
@@ -6924,19 +6924,19 @@
       <c r="K14" t="n">
         <v>84.36149186208348</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 10.129x + -16908.978</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-16908.97798759751</v>
       </c>
       <c r="Y14" t="n">
         <v>4.56634905634774e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>1922.492970663477</v>
+        <v>156.77</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000004e-08</v>
@@ -6976,19 +6976,19 @@
       <c r="K15" t="n">
         <v>84.31767378985994</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 10.050x + -16587.382</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-16587.38220079639</v>
       </c>
       <c r="Y15" t="n">
         <v>1.691081942066405e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>1899.672234094086</v>
+        <v>148.5</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000019e-08</v>
@@ -7028,19 +7028,19 @@
       <c r="K16" t="n">
         <v>84.01873278681242</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 9.544x + -15529.555</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-15529.55453338808</v>
       </c>
       <c r="Y16" t="n">
         <v>2.013786200246354e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>1877.628540771008</v>
+        <v>149.6499999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000004754e-08</v>
@@ -7080,19 +7080,19 @@
       <c r="K17" t="n">
         <v>83.59985721293998</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 8.915x + -14299.698</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-14299.69784118015</v>
       </c>
       <c r="Y17" t="n">
         <v>2.448334698901164e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>1856.200708671826</v>
+        <v>146.8299999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000352e-08</v>
@@ -7132,19 +7132,19 @@
       <c r="K18" t="n">
         <v>83.48341894311713</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 8.754x + -13869.471</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-13869.47120063771</v>
       </c>
       <c r="Y18" t="n">
         <v>3.497192290068686e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>1834.692257238707</v>
+        <v>146.1600000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000137e-08</v>
@@ -7184,19 +7184,19 @@
       <c r="K19" t="n">
         <v>82.93010656660049</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 8.063x + -12577.835</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-12577.83482922228</v>
       </c>
       <c r="Y19" t="n">
         <v>1.24225376749655e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>1813.426360493051</v>
+        <v>146.5699999999999</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000008e-08</v>
@@ -7236,19 +7236,19 @@
       <c r="K20" t="n">
         <v>82.63846008968149</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 7.740x + -11912.078</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-11912.07840534174</v>
       </c>
       <c r="Y20" t="n">
         <v>4.776005379892511e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>1792.483501758146</v>
+        <v>143.22</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000036e-08</v>
@@ -7288,19 +7288,19 @@
       <c r="K21" t="n">
         <v>82.06207163726515</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 7.172x + -10863.727</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-10863.72742988273</v>
       </c>
       <c r="Y21" t="n">
         <v>4.606707441049849e-12</v>
       </c>
       <c r="Z21" t="n">
-        <v>1771.999555216325</v>
+        <v>141.1200000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -7340,19 +7340,19 @@
       <c r="K22" t="n">
         <v>81.54512984426755</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 6.727x + -10041.348</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-10041.34775171374</v>
       </c>
       <c r="Y22" t="n">
         <v>1.996311958269129e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>1752.045499276904</v>
+        <v>141.8800000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000155e-08</v>
@@ -7478,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7538,19 +7538,19 @@
       <c r="K2" t="n">
         <v>83.54108925815363</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.833x + -21927.464</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-21927.46412757324</v>
       </c>
       <c r="Y2" t="n">
         <v>7.613250234160914e-12</v>
       </c>
       <c r="Z2" t="n">
-        <v>2724.81086859951</v>
+        <v>447.4900000000002</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000007e-08</v>
@@ -7590,19 +7590,19 @@
       <c r="K3" t="n">
         <v>85.6027742174788</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.004x + -28086.546</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-28086.54560608976</v>
       </c>
       <c r="Y3" t="n">
         <v>3.924982133438359e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2412.801406091939</v>
+        <v>245.8599999999997</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000125615e-08</v>
@@ -7642,19 +7642,19 @@
       <c r="K4" t="n">
         <v>85.56660121506683</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 12.898x + -26752.548</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-26752.54792915133</v>
       </c>
       <c r="Y4" t="n">
         <v>1.745932340444233e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2335.828889204699</v>
+        <v>204.8299999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000057e-08</v>
@@ -7694,19 +7694,19 @@
       <c r="K5" t="n">
         <v>85.52692118623042</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 12.783x + -25998.348</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-25998.34806713569</v>
       </c>
       <c r="Y5" t="n">
         <v>3.102516286622736e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2294.508153669695</v>
+        <v>187.6900000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000004148e-08</v>
@@ -7746,19 +7746,19 @@
       <c r="K6" t="n">
         <v>85.56520778885677</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 12.894x + -25847.105</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-25847.10498817057</v>
       </c>
       <c r="Y6" t="n">
         <v>7.561005022350489e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2260.236937979773</v>
+        <v>182.9300000000003</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000271e-08</v>
@@ -7798,19 +7798,19 @@
       <c r="K7" t="n">
         <v>84.93502674377717</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 11.283x + -22128.900</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-22128.90027751403</v>
       </c>
       <c r="Y7" t="n">
         <v>4.516499178642977e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>2227.079988370894</v>
+        <v>191.6400000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000154e-08</v>
@@ -7850,19 +7850,19 @@
       <c r="K8" t="n">
         <v>85.17315262309545</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 11.842x + -22968.992</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-22968.99222627899</v>
       </c>
       <c r="Y8" t="n">
         <v>9.551461243087532e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>2194.20346379568</v>
+        <v>181.3400000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000023e-08</v>
@@ -7902,19 +7902,19 @@
       <c r="K9" t="n">
         <v>84.71958730230838</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 10.820x + -20592.587</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-20592.58714415694</v>
       </c>
       <c r="Y9" t="n">
         <v>3.455354940667196e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2161.303038555179</v>
+        <v>183.7700000000002</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000001e-08</v>
@@ -7954,19 +7954,19 @@
       <c r="K10" t="n">
         <v>84.7263210322689</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 10.834x + -20336.400</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-20336.39985406741</v>
       </c>
       <c r="Y10" t="n">
         <v>1.817495786104308e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2130.387581425748</v>
+        <v>179.7499999999998</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000024e-08</v>
@@ -8006,19 +8006,19 @@
       <c r="K11" t="n">
         <v>84.72152588834932</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 10.824x + -20051.697</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-20051.69724667293</v>
       </c>
       <c r="Y11" t="n">
         <v>4.378977546756153e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2099.901814899286</v>
+        <v>172.9200000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000004319e-08</v>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -8204,19 +8204,19 @@
       <c r="K2" t="n">
         <v>85.36396841722031</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.332x + -25415.245</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-25415.24457657672</v>
       </c>
       <c r="Y2" t="n">
         <v>6.860479258100244e-12</v>
       </c>
       <c r="Z2" t="n">
-        <v>2330.843702421264</v>
+        <v>217.3099999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -8256,19 +8256,19 @@
       <c r="K3" t="n">
         <v>85.40269372275485</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.436x + -24266.667</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-24266.66695552331</v>
       </c>
       <c r="Y3" t="n">
         <v>1.73284888058118e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2235.560156804875</v>
+        <v>174.53</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000008756e-08</v>
@@ -8308,19 +8308,19 @@
       <c r="K4" t="n">
         <v>85.19808684191781</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 11.904x + -22851.765</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-22851.76486192156</v>
       </c>
       <c r="Y4" t="n">
         <v>2.168935081485231e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2206.961743971004</v>
+        <v>170.27</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001023e-08</v>
@@ -8360,19 +8360,19 @@
       <c r="K5" t="n">
         <v>84.67205111985109</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 10.723x + -20270.930</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-20270.92972786303</v>
       </c>
       <c r="Y5" t="n">
         <v>1.810032929320714e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2183.867276708726</v>
+        <v>175.22</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000014e-08</v>
@@ -8412,19 +8412,19 @@
       <c r="K6" t="n">
         <v>84.46964869843256</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 10.328x + -19303.397</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-19303.39749494659</v>
       </c>
       <c r="Y6" t="n">
         <v>1.788368056468971e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2161.878319768788</v>
+        <v>176.8499999999997</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000071e-08</v>
@@ -8464,19 +8464,19 @@
       <c r="K7" t="n">
         <v>84.54512158834066</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 10.472x + -19394.217</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-19394.21719050666</v>
       </c>
       <c r="Y7" t="n">
         <v>1.588007331900357e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>2138.526822693762</v>
+        <v>167.8100000000002</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000001e-08</v>
@@ -8516,19 +8516,19 @@
       <c r="K8" t="n">
         <v>84.34071743962127</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 10.091x + -18463.944</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-18463.94432362843</v>
       </c>
       <c r="Y8" t="n">
         <v>6.318298254907723e-12</v>
       </c>
       <c r="Z8" t="n">
-        <v>2114.658131670821</v>
+        <v>164.71</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -8568,19 +8568,19 @@
       <c r="K9" t="n">
         <v>84.02412406788345</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 9.553x + -17245.960</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-17245.96001469352</v>
       </c>
       <c r="Y9" t="n">
         <v>2.136616869180104e-11</v>
       </c>
       <c r="Z9" t="n">
-        <v>2090.417843842138</v>
+        <v>162.75</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -8620,19 +8620,19 @@
       <c r="K10" t="n">
         <v>83.7070182799701</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 9.068x + -16150.705</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-16150.70519243724</v>
       </c>
       <c r="Y10" t="n">
         <v>1.375164881893975e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>2066.653463733323</v>
+        <v>161.1400000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000003e-08</v>
@@ -8672,19 +8672,19 @@
       <c r="K11" t="n">
         <v>83.55096211806342</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 8.847x + -15566.306</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-15566.30593815601</v>
       </c>
       <c r="Y11" t="n">
         <v>2.908870016520314e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2043.341897333103</v>
+        <v>158.1600000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -8724,19 +8724,19 @@
       <c r="K12" t="n">
         <v>83.20510911841539</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 8.393x + -14565.468</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-14565.46814579631</v>
       </c>
       <c r="Y12" t="n">
         <v>7.322615991314992e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>2020.16053882251</v>
+        <v>159.8999999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000215e-08</v>
@@ -8776,19 +8776,19 @@
       <c r="K13" t="n">
         <v>82.94416941427731</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 8.079x + -13845.923</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-13845.92294194618</v>
       </c>
       <c r="Y13" t="n">
         <v>6.785105645371334e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>1997.490241548479</v>
+        <v>156.6299999999999</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000008911e-08</v>
@@ -8828,19 +8828,19 @@
       <c r="K14" t="n">
         <v>82.35141532004666</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 7.446x + -12564.124</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-12564.12392974316</v>
       </c>
       <c r="Y14" t="n">
         <v>9.457075084295988e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>1974.89311248592</v>
+        <v>159.0300000000002</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000006e-08</v>
@@ -8880,19 +8880,19 @@
       <c r="K15" t="n">
         <v>81.72614278279597</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 6.877x + -11413.529</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-11413.52851561091</v>
       </c>
       <c r="Y15" t="n">
         <v>2.461366273816545e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>1952.456187246838</v>
+        <v>147.3300000000002</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000375e-08</v>
@@ -8932,19 +8932,19 @@
       <c r="K16" t="n">
         <v>81.72800993101737</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 6.878x + -11297.333</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-11297.33283682459</v>
       </c>
       <c r="Y16" t="n">
         <v>7.364805196144608e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>1929.821166693281</v>
+        <v>155.1600000000001</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000034e-08</v>
@@ -8984,19 +8984,19 @@
       <c r="K17" t="n">
         <v>80.84340596270073</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 6.204x + -10003.088</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-10003.08752512914</v>
       </c>
       <c r="Y17" t="n">
         <v>2.090587102766822e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>1907.316749380236</v>
+        <v>149.2299999999998</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000005716e-08</v>
@@ -9036,19 +9036,19 @@
       <c r="K18" t="n">
         <v>79.33274326220959</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 5.309x + -8347.900</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-8347.899868589046</v>
       </c>
       <c r="Y18" t="n">
         <v>0.8741747102887855</v>
       </c>
       <c r="Z18" t="n">
-        <v>2043.001623831462</v>
+        <v>138.77</v>
       </c>
       <c r="AA18" t="n">
         <v>1.587433214147698e-08</v>
@@ -9088,19 +9088,19 @@
       <c r="K19" t="n">
         <v>79.67337303619779</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 5.488x + -8566.869</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-8566.868599982852</v>
       </c>
       <c r="Y19" t="n">
         <v>1.858598537852844e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>1862.850944642408</v>
+        <v>141.6399999999999</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000039775e-08</v>
@@ -9140,19 +9140,19 @@
       <c r="K20" t="n">
         <v>77.64206186317803</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 4.564x + -6923.489</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-6923.488510870208</v>
       </c>
       <c r="Y20" t="n">
         <v>6.624299844648675e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>1840.576389400926</v>
+        <v>140.7</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000508e-08</v>
@@ -9192,19 +9192,19 @@
       <c r="K21" t="n">
         <v>76.05685305220399</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 4.028x + -5957.660</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-5957.6595670581</v>
       </c>
       <c r="Y21" t="n">
         <v>2.354992704632171e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>1818.722469865537</v>
+        <v>137.3099999999999</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000002211e-08</v>
@@ -9244,19 +9244,19 @@
       <c r="K22" t="n">
         <v>71.097240544453</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 2.920x + -4080.116</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-4080.115603521277</v>
       </c>
       <c r="Y22" t="n">
         <v>3.697873130761003e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>1797.320649040756</v>
+        <v>136.01</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000001233e-08</v>
@@ -9382,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -9442,19 +9442,19 @@
       <c r="K2" t="n">
         <v>85.3613115306383</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.325x + -23546.063</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-23546.06347275934</v>
       </c>
       <c r="Y2" t="n">
         <v>6.22857215759464e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2084.168446031461</v>
+        <v>282</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000002262e-08</v>
@@ -9494,19 +9494,19 @@
       <c r="K3" t="n">
         <v>85.66532433142999</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.193x + -23123.067</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-23123.06722751787</v>
       </c>
       <c r="Y3" t="n">
         <v>7.982835743069414e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1952.384593254094</v>
+        <v>196.3299999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000027e-08</v>
@@ -9546,19 +9546,19 @@
       <c r="K4" t="n">
         <v>85.77257657518797</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.529x + -23170.736</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-23170.73634900921</v>
       </c>
       <c r="Y4" t="n">
         <v>1.020905696240408e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1911.773568219954</v>
+        <v>171.9399999999998</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000002281e-08</v>
@@ -9598,19 +9598,19 @@
       <c r="K5" t="n">
         <v>85.74195647875764</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 13.431x + -22692.429</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-22692.42861385292</v>
       </c>
       <c r="Y5" t="n">
         <v>8.39835052292691e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1887.252671064778</v>
+        <v>166.7700000000002</v>
       </c>
       <c r="AA5" t="n">
         <v>1.00000000008713e-08</v>
@@ -9650,19 +9650,19 @@
       <c r="K6" t="n">
         <v>85.55789911488958</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 12.872x + -21424.854</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-21424.85353608882</v>
       </c>
       <c r="Y6" t="n">
         <v>6.907067596927201e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1862.036001391821</v>
+        <v>169.99</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000029612e-08</v>
@@ -9702,19 +9702,19 @@
       <c r="K7" t="n">
         <v>85.77356266450983</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 13.532x + -22272.911</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-22272.91136226284</v>
       </c>
       <c r="Y7" t="n">
         <v>9.615166456038347e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1834.106353993896</v>
+        <v>161.9199999999998</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000008e-08</v>
@@ -9754,19 +9754,19 @@
       <c r="K8" t="n">
         <v>85.70049180232654</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 13.301x + -21553.447</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-21553.44727666653</v>
       </c>
       <c r="Y8" t="n">
         <v>1.781378658722411e-12</v>
       </c>
       <c r="Z8" t="n">
-        <v>1805.56070717832</v>
+        <v>155.04</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -9806,19 +9806,19 @@
       <c r="K9" t="n">
         <v>85.80781188803128</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 13.643x + -21796.943</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-21796.94330786216</v>
       </c>
       <c r="Y9" t="n">
         <v>6.54342257965754e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>1777.306673248712</v>
+        <v>153.6399999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001536e-08</v>
@@ -9858,19 +9858,19 @@
       <c r="K10" t="n">
         <v>85.49453606475325</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 12.691x + -19913.253</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-19913.25335132917</v>
       </c>
       <c r="Y10" t="n">
         <v>1.14376364950672e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>1750.24396193424</v>
+        <v>154.26</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000896e-08</v>
@@ -9910,19 +9910,19 @@
       <c r="K11" t="n">
         <v>85.31105570871897</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 12.192x + -18812.886</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-18812.88591572936</v>
       </c>
       <c r="Y11" t="n">
         <v>1.90786882155713e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>1724.361446082798</v>
+        <v>154.97</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000064e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 33.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 33.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>85.94582735578604</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 14.109x + -29859.922</t>
-        </is>
+      <c r="W2" t="n">
+        <v>14.10895144108921</v>
       </c>
       <c r="X2" t="n">
         <v>-29859.92229424242</v>
@@ -600,7 +598,7 @@
         <v>4.204039583916335e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>185.25</v>
+        <v>2390.985395897151</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000386e-08</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>85.2948350617868</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.150x + -24355.135</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.14982371510846</v>
       </c>
       <c r="X3" t="n">
         <v>-24355.13519661768</v>
@@ -652,7 +648,7 @@
         <v>2.172147360603292e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>178.3899999999999</v>
+        <v>2302.662388551644</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000003237e-08</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>84.8813083360975</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 11.164x + -21874.976</t>
-        </is>
+      <c r="W4" t="n">
+        <v>11.16364704744479</v>
       </c>
       <c r="X4" t="n">
         <v>-21874.97582028011</v>
@@ -704,7 +698,7 @@
         <v>8.18651266872507e-12</v>
       </c>
       <c r="Z4" t="n">
-        <v>175.8700000000001</v>
+        <v>2262.444813030469</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>84.70529366106189</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 10.791x + -20819.546</t>
-        </is>
+      <c r="W5" t="n">
+        <v>10.7905119229467</v>
       </c>
       <c r="X5" t="n">
         <v>-20819.54562883605</v>
@@ -756,7 +748,7 @@
         <v>2.100008246601336e-13</v>
       </c>
       <c r="Z5" t="n">
-        <v>172.2699999999998</v>
+        <v>2231.191228183235</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>84.52897811928533</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 10.441x + -19865.042</t>
-        </is>
+      <c r="W6" t="n">
+        <v>10.44074343528423</v>
       </c>
       <c r="X6" t="n">
         <v>-19865.04181524135</v>
@@ -808,7 +798,7 @@
         <v>3.14872799628043e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>169.2700000000002</v>
+        <v>2202.656825986536</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000026e-08</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>84.51653384220252</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 10.417x + -19584.635</t>
-        </is>
+      <c r="W7" t="n">
+        <v>10.41690421576354</v>
       </c>
       <c r="X7" t="n">
         <v>-19584.63542263712</v>
@@ -860,7 +848,7 @@
         <v>3.892303492952694e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>160.76</v>
+        <v>2174.075280317639</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000003e-08</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>84.04022788674311</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 9.579x + -17700.284</t>
-        </is>
+      <c r="W8" t="n">
+        <v>9.579055831929072</v>
       </c>
       <c r="X8" t="n">
         <v>-17700.28362139756</v>
@@ -912,7 +898,7 @@
         <v>2.891435410634521e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>165.97</v>
+        <v>2145.9636290176</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000007962e-08</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>84.08656974053565</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 9.655x + -17641.887</t>
-        </is>
+      <c r="W9" t="n">
+        <v>9.654666240907856</v>
       </c>
       <c r="X9" t="n">
         <v>-17641.88651130295</v>
@@ -964,7 +948,7 @@
         <v>3.926336666255582e-12</v>
       </c>
       <c r="Z9" t="n">
-        <v>153.6000000000001</v>
+        <v>2118.736673633471</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>83.80104399174131</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 9.207x + -16575.321</t>
-        </is>
+      <c r="W10" t="n">
+        <v>9.206718879089721</v>
       </c>
       <c r="X10" t="n">
         <v>-16575.32057465745</v>
@@ -1016,7 +998,7 @@
         <v>1.791494586579274e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>159.51</v>
+        <v>2092.45788017693</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000061e-08</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>83.65353850953689</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 8.991x + -15976.272</t>
-        </is>
+      <c r="W11" t="n">
+        <v>8.991035758161958</v>
       </c>
       <c r="X11" t="n">
         <v>-15976.27246472913</v>
@@ -1068,7 +1048,7 @@
         <v>5.246897560617112e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>153.26</v>
+        <v>2066.77760191502</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>85.41844920460768</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.479x + -26059.557</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.47909530493556</v>
       </c>
       <c r="X2" t="n">
         <v>-26059.5570109247</v>
@@ -1266,7 +1244,7 @@
         <v>6.517162670059875e-12</v>
       </c>
       <c r="Z2" t="n">
-        <v>189.0099999999998</v>
+        <v>2340.098654230078</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>85.38795754740228</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.396x + -24702.396</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.39623817975668</v>
       </c>
       <c r="X3" t="n">
         <v>-24702.3958322783</v>
@@ -1318,7 +1294,7 @@
         <v>3.223984938664334e-12</v>
       </c>
       <c r="Z3" t="n">
-        <v>175.6800000000001</v>
+        <v>2250.548177932228</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>84.9718179812352</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 11.366x + -22137.283</t>
-        </is>
+      <c r="W4" t="n">
+        <v>11.36566167170466</v>
       </c>
       <c r="X4" t="n">
         <v>-22137.28255878998</v>
@@ -1370,7 +1344,7 @@
         <v>1.269634963428622e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>183.0599999999997</v>
+        <v>2213.557889513751</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000042e-08</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>84.96051487970739</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 11.340x + -21825.956</t>
-        </is>
+      <c r="W5" t="n">
+        <v>11.34003803271538</v>
       </c>
       <c r="X5" t="n">
         <v>-21825.95631522888</v>
@@ -1422,7 +1394,7 @@
         <v>1.985164566310267e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>176.0699999999999</v>
+        <v>2185.307694417118</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>84.79546621383511</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 10.979x + -20844.751</t>
-        </is>
+      <c r="W6" t="n">
+        <v>10.97852532589656</v>
       </c>
       <c r="X6" t="n">
         <v>-20844.75145816288</v>
@@ -1474,7 +1444,7 @@
         <v>2.360509578287997e-13</v>
       </c>
       <c r="Z6" t="n">
-        <v>174.04</v>
+        <v>2159.086460870488</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>84.88619344014531</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.174x + -21002.291</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.1743683560806</v>
       </c>
       <c r="X7" t="n">
         <v>-21002.29092656574</v>
@@ -1526,7 +1494,7 @@
         <v>3.727758901970407e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>167.1999999999998</v>
+        <v>2132.533271332957</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000028e-08</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>84.40255464874983</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 10.203x + -18847.544</t>
-        </is>
+      <c r="W8" t="n">
+        <v>10.20347340268368</v>
       </c>
       <c r="X8" t="n">
         <v>-18847.54439819363</v>
@@ -1578,7 +1544,7 @@
         <v>1.244666819998783e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>174.73</v>
+        <v>2106.050594134085</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000003e-08</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>84.62380496977696</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 10.626x + -19448.941</t>
-        </is>
+      <c r="W9" t="n">
+        <v>10.62601464768437</v>
       </c>
       <c r="X9" t="n">
         <v>-19448.94091516426</v>
@@ -1630,7 +1594,7 @@
         <v>1.75650277969944e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>168.4099999999999</v>
+        <v>2080.535938651296</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>84.13958206467814</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 9.743x + -17551.288</t>
-        </is>
+      <c r="W10" t="n">
+        <v>9.742621166844696</v>
       </c>
       <c r="X10" t="n">
         <v>-17551.28809108364</v>
@@ -1682,7 +1644,7 @@
         <v>4.79939967823599e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>171.46</v>
+        <v>2055.775233809128</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000003671e-08</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>84.35554874398558</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 10.118x + -18067.918</t>
-        </is>
+      <c r="W11" t="n">
+        <v>10.11795547702424</v>
       </c>
       <c r="X11" t="n">
         <v>-18067.91776146764</v>
@@ -1734,7 +1694,7 @@
         <v>9.773633489941073e-13</v>
       </c>
       <c r="Z11" t="n">
-        <v>157.1400000000001</v>
+        <v>2030.944370319675</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>84.08605671225612</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 9.654x + -17005.346</t>
-        </is>
+      <c r="W12" t="n">
+        <v>9.653822731309901</v>
       </c>
       <c r="X12" t="n">
         <v>-17005.34640597626</v>
@@ -1786,7 +1744,7 @@
         <v>7.235881936574009e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>152.98</v>
+        <v>2006.715501291098</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>83.89811554975765</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 9.354x + -16259.351</t>
-        </is>
+      <c r="W13" t="n">
+        <v>9.354323772965778</v>
       </c>
       <c r="X13" t="n">
         <v>-16259.35119934392</v>
@@ -1838,7 +1794,7 @@
         <v>1.401181279531593e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>155.75</v>
+        <v>1983.467222920582</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000007e-08</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>83.72793630392982</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 9.099x + -15627.051</t>
-        </is>
+      <c r="W14" t="n">
+        <v>9.09855758346953</v>
       </c>
       <c r="X14" t="n">
         <v>-15627.05089699396</v>
@@ -1890,7 +1844,7 @@
         <v>2.139214244621695e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>147</v>
+        <v>1960.761275159777</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000013e-08</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>83.1759593932062</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 8.356x + -14130.278</t>
-        </is>
+      <c r="W15" t="n">
+        <v>8.356428007884638</v>
       </c>
       <c r="X15" t="n">
         <v>-14130.27782756219</v>
@@ -1942,7 +1894,7 @@
         <v>1.634382466793408e-12</v>
       </c>
       <c r="Z15" t="n">
-        <v>151.05</v>
+        <v>1938.452634928891</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>82.49982684944662</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 7.596x + -12626.270</t>
-        </is>
+      <c r="W16" t="n">
+        <v>7.595576736280749</v>
       </c>
       <c r="X16" t="n">
         <v>-12626.27035864673</v>
@@ -1994,7 +1944,7 @@
         <v>1.324614760934189e-12</v>
       </c>
       <c r="Z16" t="n">
-        <v>143.98</v>
+        <v>1916.914366877109</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>82.52185690839273</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 7.618x + -12538.885</t>
-        </is>
+      <c r="W17" t="n">
+        <v>7.618210041262239</v>
       </c>
       <c r="X17" t="n">
         <v>-12538.88526326918</v>
@@ -2046,7 +1994,7 @@
         <v>1.128613551560124e-12</v>
       </c>
       <c r="Z17" t="n">
-        <v>152.3499999999999</v>
+        <v>1895.969017966253</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>81.84680826846503</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 6.980x + -11298.307</t>
-        </is>
+      <c r="W18" t="n">
+        <v>6.979907395258109</v>
       </c>
       <c r="X18" t="n">
         <v>-11298.30669920068</v>
@@ -2098,7 +2044,7 @@
         <v>1.504780107670999e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>144.1900000000001</v>
+        <v>1874.836665168918</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000003e-08</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>80.45896450817675</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 5.950x + -9418.730</t>
-        </is>
+      <c r="W19" t="n">
+        <v>5.949584712429432</v>
       </c>
       <c r="X19" t="n">
         <v>-9418.730443240538</v>
@@ -2150,7 +2094,7 @@
         <v>4.961926791858e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>140.95</v>
+        <v>1854.21653397075</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000001e-08</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>78.97838886808351</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 5.134x + -7937.578</t>
-        </is>
+      <c r="W20" t="n">
+        <v>5.134214140647314</v>
       </c>
       <c r="X20" t="n">
         <v>-7937.577567431398</v>
@@ -2202,7 +2144,7 @@
         <v>1.119806457727727e-07</v>
       </c>
       <c r="Z20" t="n">
-        <v>136.1100000000001</v>
+        <v>1833.870774858342</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000314e-08</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>78.36171159587786</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 4.855x + -7380.131</t>
-        </is>
+      <c r="W21" t="n">
+        <v>4.855145934701059</v>
       </c>
       <c r="X21" t="n">
         <v>-7380.131259702622</v>
@@ -2254,7 +2194,7 @@
         <v>2.62179654675983e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>136.5599999999999</v>
+        <v>1813.341687290567</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000001505e-08</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>79.12113507093649</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 5.203x + -7900.013</t>
-        </is>
+      <c r="W22" t="n">
+        <v>5.203262352340198</v>
       </c>
       <c r="X22" t="n">
         <v>-7900.013300919956</v>
@@ -2306,7 +2244,7 @@
         <v>8.991918499063288e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>143.7900000000002</v>
+        <v>1793.115291214006</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000005826e-08</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>85.50992878672422</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.734x + -26065.306</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.73441741119876</v>
       </c>
       <c r="X2" t="n">
         <v>-26065.30633022426</v>
@@ -2504,7 +2440,7 @@
         <v>3.280095204512863e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>194.9200000000001</v>
+        <v>2317.987113242924</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000067e-08</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>85.2370321315834</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.002x + -23216.308</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.00170550128092</v>
       </c>
       <c r="X3" t="n">
         <v>-23216.30797720005</v>
@@ -2556,7 +2490,7 @@
         <v>1.95725077814474e-12</v>
       </c>
       <c r="Z3" t="n">
-        <v>176.2700000000002</v>
+        <v>2218.99336004235</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>84.92505461052374</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 11.260x + -21325.901</t>
-        </is>
+      <c r="W4" t="n">
+        <v>11.26038996916219</v>
       </c>
       <c r="X4" t="n">
         <v>-21325.90088680392</v>
@@ -2608,7 +2540,7 @@
         <v>9.319554814802288e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>167.1299999999999</v>
+        <v>2182.408812275879</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001162e-08</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>84.4734213373351</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 10.335x + -19260.088</t>
-        </is>
+      <c r="W5" t="n">
+        <v>10.33514228192132</v>
       </c>
       <c r="X5" t="n">
         <v>-19260.08818227364</v>
@@ -2660,7 +2590,7 @@
         <v>3.974436311851379e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>170.8200000000002</v>
+        <v>2156.458503682248</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000403e-08</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>84.39960783810704</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 10.198x + -18782.084</t>
-        </is>
+      <c r="W6" t="n">
+        <v>10.19807022341702</v>
       </c>
       <c r="X6" t="n">
         <v>-18782.08376467229</v>
@@ -2712,7 +2640,7 @@
         <v>1.036806407992319e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>163.03</v>
+        <v>2132.105885280056</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000003822e-08</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>84.07618099718908</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 9.638x + -17512.347</t>
-        </is>
+      <c r="W7" t="n">
+        <v>9.637613676733936</v>
       </c>
       <c r="X7" t="n">
         <v>-17512.34656175634</v>
@@ -2764,7 +2690,7 @@
         <v>3.275280223422031e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>161.5800000000002</v>
+        <v>2107.64763762722</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000954e-08</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>83.99663404680085</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 9.509x + -17069.875</t>
-        </is>
+      <c r="W8" t="n">
+        <v>9.508990751549737</v>
       </c>
       <c r="X8" t="n">
         <v>-17069.87532735561</v>
@@ -2816,7 +2740,7 @@
         <v>5.584913484726683e-13</v>
       </c>
       <c r="Z8" t="n">
-        <v>155.95</v>
+        <v>2082.236589874</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>83.47238817139875</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 8.739x + -15432.598</t>
-        </is>
+      <c r="W9" t="n">
+        <v>8.739439930026473</v>
       </c>
       <c r="X9" t="n">
         <v>-15432.59836525563</v>
@@ -2868,7 +2790,7 @@
         <v>3.075103827481586e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>166.8999999999999</v>
+        <v>2056.856670172265</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001008e-08</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>83.38407604161917</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 8.622x + -15040.778</t>
-        </is>
+      <c r="W10" t="n">
+        <v>8.621759723765363</v>
       </c>
       <c r="X10" t="n">
         <v>-15040.77787025728</v>
@@ -2920,7 +2840,7 @@
         <v>3.080420979594384e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>160.03</v>
+        <v>2032.25573188414</v>
       </c>
       <c r="AA10" t="n">
         <v>1.00000000000003e-08</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>83.59096702059908</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 8.903x + -15376.035</t>
-        </is>
+      <c r="W11" t="n">
+        <v>8.902530438412152</v>
       </c>
       <c r="X11" t="n">
         <v>-15376.03455005842</v>
@@ -2972,7 +2890,7 @@
         <v>5.373398823314694e-12</v>
       </c>
       <c r="Z11" t="n">
-        <v>155.6999999999998</v>
+        <v>2008.241206799612</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>83.05696024543155</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 8.212x + -13960.519</t>
-        </is>
+      <c r="W12" t="n">
+        <v>8.211828912674969</v>
       </c>
       <c r="X12" t="n">
         <v>-13960.51888178542</v>
@@ -3024,7 +2940,7 @@
         <v>3.893378595722602e-12</v>
       </c>
       <c r="Z12" t="n">
-        <v>153.8300000000002</v>
+        <v>1984.466328154522</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>82.61312021248209</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 7.713x + -12920.975</t>
-        </is>
+      <c r="W13" t="n">
+        <v>7.713402240341975</v>
       </c>
       <c r="X13" t="n">
         <v>-12920.97525885741</v>
@@ -3076,7 +2990,7 @@
         <v>2.110579714385463e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>151.1400000000001</v>
+        <v>1961.263994443591</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000012e-08</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>82.48480152314912</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 7.580x + -12542.358</t>
-        </is>
+      <c r="W14" t="n">
+        <v>7.580215654036945</v>
       </c>
       <c r="X14" t="n">
         <v>-12542.35796933517</v>
@@ -3128,7 +3040,7 @@
         <v>1.002837192826697e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>153.9400000000001</v>
+        <v>1938.507873288195</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000001e-08</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>82.09753003249165</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 7.204x + -11738.957</t>
-        </is>
+      <c r="W15" t="n">
+        <v>7.204330344332525</v>
       </c>
       <c r="X15" t="n">
         <v>-11738.95732576838</v>
@@ -3180,7 +3090,7 @@
         <v>2.850922014780705e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>142.21</v>
+        <v>1916.077332681858</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000009e-08</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>81.84520404063061</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 6.979x + -11227.009</t>
-        </is>
+      <c r="W16" t="n">
+        <v>6.978515579110808</v>
       </c>
       <c r="X16" t="n">
         <v>-11227.0086366115</v>
@@ -3232,7 +3140,7 @@
         <v>9.432620631498664e-09</v>
       </c>
       <c r="Z16" t="n">
-        <v>143.6900000000001</v>
+        <v>1894.06110208856</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000002523e-08</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>81.8250895427506</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 6.961x + -11077.095</t>
-        </is>
+      <c r="W17" t="n">
+        <v>6.961110440313986</v>
       </c>
       <c r="X17" t="n">
         <v>-11077.09485966097</v>
@@ -3284,7 +3190,7 @@
         <v>3.853713705324117e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>145.8</v>
+        <v>1872.683521897972</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000131e-08</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>81.03643831979308</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 6.340x + -9920.344</t>
-        </is>
+      <c r="W18" t="n">
+        <v>6.339844167790614</v>
       </c>
       <c r="X18" t="n">
         <v>-9920.344163946565</v>
@@ -3336,7 +3240,7 @@
         <v>7.070886380029249e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>146.9699999999998</v>
+        <v>1851.661623058608</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000128e-08</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>79.37238831340754</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 5.329x + -8122.600</t>
-        </is>
+      <c r="W19" t="n">
+        <v>5.329247540081708</v>
       </c>
       <c r="X19" t="n">
         <v>-8122.600467169436</v>
@@ -3388,7 +3290,7 @@
         <v>3.113456246604454e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>136.3700000000001</v>
+        <v>1831.170759546947</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000915e-08</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>79.3740569682499</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 5.330x + -8055.102</t>
-        </is>
+      <c r="W20" t="n">
+        <v>5.330103930128508</v>
       </c>
       <c r="X20" t="n">
         <v>-8055.101954908589</v>
@@ -3440,7 +3340,7 @@
         <v>1.263184852026903e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>142.95</v>
+        <v>1810.825821371916</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000006e-08</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>78.08299783233819</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 4.738x + -6998.014</t>
-        </is>
+      <c r="W21" t="n">
+        <v>4.738370995031646</v>
       </c>
       <c r="X21" t="n">
         <v>-6998.014253918594</v>
@@ -3492,7 +3390,7 @@
         <v>7.600141770234294e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>135.23</v>
+        <v>1790.89786862746</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000504e-08</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>74.91059589705391</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 3.709x + -5270.136</t>
-        </is>
+      <c r="W22" t="n">
+        <v>3.708891747000915</v>
       </c>
       <c r="X22" t="n">
         <v>-5270.136166751174</v>
@@ -3544,7 +3440,7 @@
         <v>9.852978614820137e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>131.49</v>
+        <v>1771.232181134933</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000012479e-08</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>84.74625765654378</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.875x + -26749.093</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.87512574499219</v>
       </c>
       <c r="X2" t="n">
         <v>-26749.09270856584</v>
@@ -3742,7 +3636,7 @@
         <v>5.382119852803023e-14</v>
       </c>
       <c r="Z2" t="n">
-        <v>327.0500000000002</v>
+        <v>2762.790328834013</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>85.31455811676005</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.201x + -27066.494</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.20119776463443</v>
       </c>
       <c r="X3" t="n">
         <v>-27066.49417195981</v>
@@ -3794,7 +3686,7 @@
         <v>3.811649962108427e-12</v>
       </c>
       <c r="Z3" t="n">
-        <v>200.21</v>
+        <v>2539.555963231845</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>85.01066443356866</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 11.455x + -24587.768</t>
-        </is>
+      <c r="W4" t="n">
+        <v>11.45460776318867</v>
       </c>
       <c r="X4" t="n">
         <v>-24587.76846220544</v>
@@ -3846,7 +3736,7 @@
         <v>2.715798711589326e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>187.8600000000001</v>
+        <v>2473.256688502569</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>84.7079322811538</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 10.796x + -22734.586</t>
-        </is>
+      <c r="W5" t="n">
+        <v>10.79592280664031</v>
       </c>
       <c r="X5" t="n">
         <v>-22734.58597698457</v>
@@ -3898,7 +3786,7 @@
         <v>3.327850201614981e-11</v>
       </c>
       <c r="Z5" t="n">
-        <v>169.6900000000001</v>
+        <v>2431.40922110609</v>
       </c>
       <c r="AA5" t="n">
         <v>1.00000000019688e-08</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>83.69587766788189</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 9.052x + -18601.303</t>
-        </is>
+      <c r="W6" t="n">
+        <v>9.051915611239215</v>
       </c>
       <c r="X6" t="n">
         <v>-18601.30345305698</v>
@@ -3950,7 +3836,7 @@
         <v>1.873416580058254e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>181.8700000000003</v>
+        <v>2393.262113320538</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000241e-08</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>83.03470530347117</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 8.185x + -16492.848</t>
-        </is>
+      <c r="W7" t="n">
+        <v>8.185332102970408</v>
       </c>
       <c r="X7" t="n">
         <v>-16492.84802676491</v>
@@ -4002,7 +3886,7 @@
         <v>4.961029159219708e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>169</v>
+        <v>2356.403134490525</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000014953e-08</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>82.87920329466156</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 8.005x + -15867.965</t>
-        </is>
+      <c r="W8" t="n">
+        <v>8.004789855837927</v>
       </c>
       <c r="X8" t="n">
         <v>-15867.96524100771</v>
@@ -4054,7 +3936,7 @@
         <v>9.657881295270694e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>172.3299999999999</v>
+        <v>2320.550811716739</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000001489e-08</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>81.76779421434706</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 6.912x + -13392.606</t>
-        </is>
+      <c r="W9" t="n">
+        <v>6.911995645591436</v>
       </c>
       <c r="X9" t="n">
         <v>-13392.60553694756</v>
@@ -4106,7 +3986,7 @@
         <v>1.090463821237727e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>168.2000000000003</v>
+        <v>2285.336101852824</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000002e-08</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>81.19911037390143</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 6.459x + -12272.749</t>
-        </is>
+      <c r="W10" t="n">
+        <v>6.458943672136752</v>
       </c>
       <c r="X10" t="n">
         <v>-12272.7489078232</v>
@@ -4158,7 +4036,7 @@
         <v>8.07705365690651e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>166.5500000000002</v>
+        <v>2250.767494666186</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000053e-08</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>80.22474139061949</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 5.804x + -10794.562</t>
-        </is>
+      <c r="W11" t="n">
+        <v>5.804324937575564</v>
       </c>
       <c r="X11" t="n">
         <v>-10794.5618610638</v>
@@ -4210,7 +4086,7 @@
         <v>5.047978207424955e-12</v>
       </c>
       <c r="Z11" t="n">
-        <v>161.4299999999998</v>
+        <v>2218.54949805969</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>85.56228544008681</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.885x + -26604.875</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.8852727813639</v>
       </c>
       <c r="X2" t="n">
         <v>-26604.87470843148</v>
@@ -4408,7 +4282,7 @@
         <v>4.459750480210157e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>218.0700000000002</v>
+        <v>2301.280264219839</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000002e-08</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>85.32959225175115</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.241x + -23930.420</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.24064902928935</v>
       </c>
       <c r="X3" t="n">
         <v>-23930.41968659493</v>
@@ -4460,7 +4332,7 @@
         <v>2.397427979873818e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>175.2500000000002</v>
+        <v>2235.785445240768</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000024e-08</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>84.76062942108304</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 10.905x + -20799.784</t>
-        </is>
+      <c r="W4" t="n">
+        <v>10.90512420979309</v>
       </c>
       <c r="X4" t="n">
         <v>-20799.78435183375</v>
@@ -4512,7 +4382,7 @@
         <v>1.973598942241607e-12</v>
       </c>
       <c r="Z4" t="n">
-        <v>177.2700000000002</v>
+        <v>2200.995743445253</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>84.74273982432568</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 10.868x + -20488.700</t>
-        </is>
+      <c r="W5" t="n">
+        <v>10.86780782170767</v>
       </c>
       <c r="X5" t="n">
         <v>-20488.69997991271</v>
@@ -4564,7 +4432,7 @@
         <v>2.944714651105882e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>164.52</v>
+        <v>2174.548673782294</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000003598e-08</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>84.48996503234633</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 10.366x + -19278.115</t>
-        </is>
+      <c r="W6" t="n">
+        <v>10.36636622202483</v>
       </c>
       <c r="X6" t="n">
         <v>-19278.11534444883</v>
@@ -4616,7 +4482,7 @@
         <v>7.357967015642599e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>167.96</v>
+        <v>2150.073866540657</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001432e-08</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>84.41211347390004</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 10.221x + -18801.331</t>
-        </is>
+      <c r="W7" t="n">
+        <v>10.22103926347767</v>
       </c>
       <c r="X7" t="n">
         <v>-18801.33133444286</v>
@@ -4668,7 +4532,7 @@
         <v>2.147136252978873e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>159.71</v>
+        <v>2125.749199236592</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000018e-08</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>84.22639826351902</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 9.890x + -17967.859</t>
-        </is>
+      <c r="W8" t="n">
+        <v>9.890137661658422</v>
       </c>
       <c r="X8" t="n">
         <v>-17967.85918710846</v>
@@ -4720,7 +4582,7 @@
         <v>6.343226854772491e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>156.8699999999999</v>
+        <v>2101.511587230581</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000676e-08</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>84.01308378521934</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 9.535x + -17097.271</t>
-        </is>
+      <c r="W9" t="n">
+        <v>9.535309737974229</v>
       </c>
       <c r="X9" t="n">
         <v>-17097.27075471849</v>
@@ -4772,7 +4632,7 @@
         <v>1.897653207837191e-15</v>
       </c>
       <c r="Z9" t="n">
-        <v>153.74</v>
+        <v>2077.385943568945</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>83.2342641148764</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 8.429x + -14856.241</t>
-        </is>
+      <c r="W10" t="n">
+        <v>8.429123361941482</v>
       </c>
       <c r="X10" t="n">
         <v>-14856.2406325536</v>
@@ -4824,7 +4682,7 @@
         <v>2.432346286854933e-11</v>
       </c>
       <c r="Z10" t="n">
-        <v>154.26</v>
+        <v>2054.491693778788</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>83.46946754329267</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 8.735x + -15261.003</t>
-        </is>
+      <c r="W11" t="n">
+        <v>8.735497385260576</v>
       </c>
       <c r="X11" t="n">
         <v>-15261.00259271918</v>
@@ -4876,7 +4732,7 @@
         <v>8.661103947393544e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>154.1400000000001</v>
+        <v>2031.761843559136</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000002e-08</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>82.69994191030902</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 7.806x + -13408.684</t>
-        </is>
+      <c r="W12" t="n">
+        <v>7.806158414285634</v>
       </c>
       <c r="X12" t="n">
         <v>-13408.68380952146</v>
@@ -4928,7 +4782,7 @@
         <v>2.388509157290579e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>158.3799999999999</v>
+        <v>2009.651086581542</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000001e-08</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>82.59350423339932</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 7.693x + -13069.586</t>
-        </is>
+      <c r="W13" t="n">
+        <v>7.692744976888316</v>
       </c>
       <c r="X13" t="n">
         <v>-13069.58629970245</v>
@@ -4980,7 +4832,7 @@
         <v>1.077326304336074e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>158.05</v>
+        <v>1988.585488459867</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000005184e-08</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>82.0950520240951</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 7.202x + -12063.399</t>
-        </is>
+      <c r="W14" t="n">
+        <v>7.202043060715459</v>
       </c>
       <c r="X14" t="n">
         <v>-12063.39893161598</v>
@@ -5032,7 +4882,7 @@
         <v>5.745777848336679e-11</v>
       </c>
       <c r="Z14" t="n">
-        <v>152.6000000000001</v>
+        <v>1967.523521816388</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>81.45129944275661</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 6.652x + -10976.940</t>
-        </is>
+      <c r="W15" t="n">
+        <v>6.652471093500997</v>
       </c>
       <c r="X15" t="n">
         <v>-10976.93973333983</v>
@@ -5084,7 +4932,7 @@
         <v>2.495153740909959e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>147.0999999999999</v>
+        <v>1946.970922529222</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>80.5446591910015</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 6.005x + -9732.801</t>
-        </is>
+      <c r="W16" t="n">
+        <v>6.0045116892535</v>
       </c>
       <c r="X16" t="n">
         <v>-9732.800878275835</v>
@@ -5136,7 +4982,7 @@
         <v>5.831367481518386e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>146.3599999999999</v>
+        <v>1926.281913312374</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000026e-08</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>78.20205392491371</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 4.788x + -7522.883</t>
-        </is>
+      <c r="W17" t="n">
+        <v>4.787587379052066</v>
       </c>
       <c r="X17" t="n">
         <v>-7522.882911668597</v>
@@ -5188,7 +5032,7 @@
         <v>8.449667463875538e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>140.9100000000001</v>
+        <v>1905.594758694585</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>79.81499891722838</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 5.566x + -8795.637</t>
-        </is>
+      <c r="W18" t="n">
+        <v>5.566126354006498</v>
       </c>
       <c r="X18" t="n">
         <v>-8795.636872520881</v>
@@ -5240,7 +5082,7 @@
         <v>1.613185758314617e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>145.5799999999999</v>
+        <v>1885.516390533847</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000005e-08</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>76.68177150693184</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 4.224x + -6428.456</t>
-        </is>
+      <c r="W19" t="n">
+        <v>4.224294248849631</v>
       </c>
       <c r="X19" t="n">
         <v>-6428.455628008577</v>
@@ -5292,7 +5132,7 @@
         <v>4.754854925663405e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>137.8</v>
+        <v>1865.299388057059</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000125e-08</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>74.58129143416832</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 3.626x + -5358.523</t>
-        </is>
+      <c r="W20" t="n">
+        <v>3.625852327212794</v>
       </c>
       <c r="X20" t="n">
         <v>-5358.523427761919</v>
@@ -5344,7 +5182,7 @@
         <v>8.397442968575009e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>137.99</v>
+        <v>1845.048278003251</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000021e-08</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>72.7319841918561</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 3.217x + -4640.011</t>
-        </is>
+      <c r="W21" t="n">
+        <v>3.216954237310666</v>
       </c>
       <c r="X21" t="n">
         <v>-4640.010902268752</v>
@@ -5396,7 +5232,7 @@
         <v>5.1358516570408e-11</v>
       </c>
       <c r="Z21" t="n">
-        <v>138.3499999999999</v>
+        <v>1824.420477384447</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>56.62122742932809</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 1.518x + -1761.508</t>
-        </is>
+      <c r="W22" t="n">
+        <v>1.517802909463928</v>
       </c>
       <c r="X22" t="n">
         <v>-1761.507980488734</v>
@@ -5448,7 +5282,7 @@
         <v>2.263197602822182e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>127.5600000000002</v>
+        <v>1803.789355113339</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000001634e-08</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>83.80765960470836</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.217x + -24610.888</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.216632053565732</v>
       </c>
       <c r="X2" t="n">
         <v>-24610.88784398716</v>
@@ -5646,7 +5478,7 @@
         <v>1.30217154712413e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>413.0799999999999</v>
+        <v>2956.937998599872</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000002e-08</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>85.06810833982642</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.589x + -25885.726</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.58869756141384</v>
       </c>
       <c r="X3" t="n">
         <v>-25885.72601678587</v>
@@ -5698,7 +5528,7 @@
         <v>8.913567043653538e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>234.1900000000001</v>
+        <v>2557.221942423093</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000201e-08</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>85.09578309874748</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 11.654x + -24952.472</t>
-        </is>
+      <c r="W4" t="n">
+        <v>11.65441643966845</v>
       </c>
       <c r="X4" t="n">
         <v>-24952.47167301413</v>
@@ -5750,7 +5578,7 @@
         <v>2.71801248566196e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>199.0599999999999</v>
+        <v>2467.479528630048</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000000012e-08</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>85.34465363018386</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 12.280x + -25876.234</t>
-        </is>
+      <c r="W5" t="n">
+        <v>12.28042671939983</v>
       </c>
       <c r="X5" t="n">
         <v>-25876.23364109322</v>
@@ -5802,7 +5628,7 @@
         <v>7.712620956868486e-11</v>
       </c>
       <c r="Z5" t="n">
-        <v>184.7399999999998</v>
+        <v>2424.155405503865</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000314e-08</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>84.89622426258084</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 11.196x + -23152.450</t>
-        </is>
+      <c r="W6" t="n">
+        <v>11.196447109231</v>
       </c>
       <c r="X6" t="n">
         <v>-23152.4503518414</v>
@@ -5854,7 +5678,7 @@
         <v>5.699170757619234e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>184.1500000000001</v>
+        <v>2389.607794254967</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000003e-08</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>84.68915754534621</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 10.758x + -21908.664</t>
-        </is>
+      <c r="W7" t="n">
+        <v>10.75753905720819</v>
       </c>
       <c r="X7" t="n">
         <v>-21908.66417864332</v>
@@ -5906,7 +5728,7 @@
         <v>4.539782532175464e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>182.3499999999999</v>
+        <v>2356.375305165897</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000108e-08</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>84.67237947613681</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 10.723x + -21553.714</t>
-        </is>
+      <c r="W8" t="n">
+        <v>10.72346561705794</v>
       </c>
       <c r="X8" t="n">
         <v>-21553.71420906695</v>
@@ -5958,7 +5778,7 @@
         <v>3.237800321216792e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>171.23</v>
+        <v>2322.96340590222</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000139e-08</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>84.05347696306657</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 9.601x + -18920.234</t>
-        </is>
+      <c r="W9" t="n">
+        <v>9.600552881772764</v>
       </c>
       <c r="X9" t="n">
         <v>-18920.23360691632</v>
@@ -6010,7 +5828,7 @@
         <v>2.176184117052209e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>180.6099999999999</v>
+        <v>2290.390876427691</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000144e-08</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>84.25065353894558</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 9.932x + -19355.013</t>
-        </is>
+      <c r="W10" t="n">
+        <v>9.932145258561153</v>
       </c>
       <c r="X10" t="n">
         <v>-19355.01344117668</v>
@@ -6062,7 +5878,7 @@
         <v>1.230642257829192e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>171.7</v>
+        <v>2258.123496609084</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000007e-08</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>83.89167338657766</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 9.344x + -17907.335</t>
-        </is>
+      <c r="W11" t="n">
+        <v>9.344383178060468</v>
       </c>
       <c r="X11" t="n">
         <v>-17907.33525987165</v>
@@ -6114,7 +5928,7 @@
         <v>1.590275806571983e-11</v>
       </c>
       <c r="Z11" t="n">
-        <v>172.79</v>
+        <v>2227.137972494579</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000297e-08</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>85.11404348831725</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 11.698x + -23620.800</t>
-        </is>
+      <c r="W2" t="n">
+        <v>11.69818581270852</v>
       </c>
       <c r="X2" t="n">
         <v>-23620.79989265063</v>
@@ -6312,7 +6124,7 @@
         <v>4.750412073314734e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>288.8999999999999</v>
+        <v>2285.751530651358</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000508e-08</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>85.68576719638271</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.256x + -25690.897</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.25553288850296</v>
       </c>
       <c r="X3" t="n">
         <v>-25690.8969326318</v>
@@ -6364,7 +6174,7 @@
         <v>2.374154993122139e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>181.2999999999997</v>
+        <v>2209.635421278826</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000296e-08</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>85.58964852361886</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 12.966x + -24674.245</t>
-        </is>
+      <c r="W4" t="n">
+        <v>12.96553632930162</v>
       </c>
       <c r="X4" t="n">
         <v>-24674.24474221483</v>
@@ -6416,7 +6224,7 @@
         <v>5.196231976292161e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>175.3400000000001</v>
+        <v>2174.993664999086</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000000007e-08</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>85.3194994772585</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 12.214x + -22867.404</t>
-        </is>
+      <c r="W5" t="n">
+        <v>12.21413655300717</v>
       </c>
       <c r="X5" t="n">
         <v>-22867.40411278554</v>
@@ -6468,7 +6274,7 @@
         <v>3.664984294725045e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>176.0899999999999</v>
+        <v>2146.383493230952</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000369e-08</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>85.370899357526</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 12.350x + -22849.579</t>
-        </is>
+      <c r="W6" t="n">
+        <v>12.35035987792007</v>
       </c>
       <c r="X6" t="n">
         <v>-22849.57908735387</v>
@@ -6520,7 +6324,7 @@
         <v>3.503533905028396e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>172.8199999999999</v>
+        <v>2118.771618117882</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000001e-08</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>85.16055918361722</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.811x + -21523.632</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.8111706923796</v>
       </c>
       <c r="X7" t="n">
         <v>-21523.63167762938</v>
@@ -6572,7 +6374,7 @@
         <v>1.211580991380278e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>175.55</v>
+        <v>2091.723620345841</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000114e-08</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>85.33776379585787</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 12.262x + -22142.381</t>
-        </is>
+      <c r="W8" t="n">
+        <v>12.26219857478057</v>
       </c>
       <c r="X8" t="n">
         <v>-22142.38100978825</v>
@@ -6624,7 +6424,7 @@
         <v>1.280687187380231e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>162.3299999999999</v>
+        <v>2065.374477437337</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000784e-08</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>85.13304476401103</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 11.744x + -20908.723</t>
-        </is>
+      <c r="W9" t="n">
+        <v>11.74407890610036</v>
       </c>
       <c r="X9" t="n">
         <v>-20908.72258690815</v>
@@ -6676,7 +6474,7 @@
         <v>2.162138625882955e-12</v>
       </c>
       <c r="Z9" t="n">
-        <v>164.27</v>
+        <v>2040.539887676406</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>85.17625381144693</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 11.850x + -20853.774</t>
-        </is>
+      <c r="W10" t="n">
+        <v>11.8497828169039</v>
       </c>
       <c r="X10" t="n">
         <v>-20853.77385718287</v>
@@ -6728,7 +6524,7 @@
         <v>4.669281048614839e-12</v>
       </c>
       <c r="Z10" t="n">
-        <v>161.23</v>
+        <v>2015.913478467688</v>
       </c>
       <c r="AA10" t="n">
         <v>1.00000000000128e-08</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>84.97806591274967</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 11.380x + -19764.409</t>
-        </is>
+      <c r="W11" t="n">
+        <v>11.37987483363913</v>
       </c>
       <c r="X11" t="n">
         <v>-19764.40946694198</v>
@@ -6780,7 +6574,7 @@
         <v>3.752490992783068e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>156.98</v>
+        <v>1991.670976810645</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000005e-08</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>84.73535267549072</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 10.852x + -18589.918</t>
-        </is>
+      <c r="W12" t="n">
+        <v>10.85247254574038</v>
       </c>
       <c r="X12" t="n">
         <v>-18589.9176031032</v>
@@ -6832,7 +6624,7 @@
         <v>1.706400667419449e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>160.9100000000001</v>
+        <v>1968.324983783407</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000010839e-08</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>84.52678892630873</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 10.437x + -17643.119</t>
-        </is>
+      <c r="W13" t="n">
+        <v>10.43654181402999</v>
       </c>
       <c r="X13" t="n">
         <v>-17643.11913838646</v>
@@ -6884,7 +6674,7 @@
         <v>6.884180004263952e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>157.8100000000002</v>
+        <v>1945.471008717886</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000047e-08</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>84.36149186208348</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 10.129x + -16908.978</t>
-        </is>
+      <c r="W14" t="n">
+        <v>10.12868931363004</v>
       </c>
       <c r="X14" t="n">
         <v>-16908.97798759751</v>
@@ -6936,7 +6724,7 @@
         <v>4.56634905634774e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>156.77</v>
+        <v>1922.492970663477</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000004e-08</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>84.31767378985994</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 10.050x + -16587.382</t>
-        </is>
+      <c r="W15" t="n">
+        <v>10.05007549814596</v>
       </c>
       <c r="X15" t="n">
         <v>-16587.38220079639</v>
@@ -6988,7 +6774,7 @@
         <v>1.691081942066405e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>148.5</v>
+        <v>1899.672234094086</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000019e-08</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>84.01873278681242</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 9.544x + -15529.555</t>
-        </is>
+      <c r="W16" t="n">
+        <v>9.544381207279393</v>
       </c>
       <c r="X16" t="n">
         <v>-15529.55453338808</v>
@@ -7040,7 +6824,7 @@
         <v>2.013786200246354e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>149.6499999999999</v>
+        <v>1877.628540771008</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000004754e-08</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>83.59985721293998</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 8.915x + -14299.698</t>
-        </is>
+      <c r="W17" t="n">
+        <v>8.915000287946038</v>
       </c>
       <c r="X17" t="n">
         <v>-14299.69784118015</v>
@@ -7092,7 +6874,7 @@
         <v>2.448334698901164e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>146.8299999999999</v>
+        <v>1856.200708671826</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000352e-08</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>83.48341894311713</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 8.754x + -13869.471</t>
-        </is>
+      <c r="W18" t="n">
+        <v>8.754362067652787</v>
       </c>
       <c r="X18" t="n">
         <v>-13869.47120063771</v>
@@ -7144,7 +6924,7 @@
         <v>3.497192290068686e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>146.1600000000001</v>
+        <v>1834.692257238707</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000137e-08</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>82.93010656660049</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 8.063x + -12577.835</t>
-        </is>
+      <c r="W19" t="n">
+        <v>8.063020024023471</v>
       </c>
       <c r="X19" t="n">
         <v>-12577.83482922228</v>
@@ -7196,7 +6974,7 @@
         <v>1.24225376749655e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>146.5699999999999</v>
+        <v>1813.426360493051</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000008e-08</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>82.63846008968149</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 7.740x + -11912.078</t>
-        </is>
+      <c r="W20" t="n">
+        <v>7.740249301497883</v>
       </c>
       <c r="X20" t="n">
         <v>-11912.07840534174</v>
@@ -7248,7 +7024,7 @@
         <v>4.776005379892511e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>143.22</v>
+        <v>1792.483501758146</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000036e-08</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>82.06207163726515</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 7.172x + -10863.727</t>
-        </is>
+      <c r="W21" t="n">
+        <v>7.171736193512427</v>
       </c>
       <c r="X21" t="n">
         <v>-10863.72742988273</v>
@@ -7300,7 +7074,7 @@
         <v>4.606707441049849e-12</v>
       </c>
       <c r="Z21" t="n">
-        <v>141.1200000000001</v>
+        <v>1771.999555216325</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>81.54512984426755</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 6.727x + -10041.348</t>
-        </is>
+      <c r="W22" t="n">
+        <v>6.727399900304138</v>
       </c>
       <c r="X22" t="n">
         <v>-10041.34775171374</v>
@@ -7352,7 +7124,7 @@
         <v>1.996311958269129e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>141.8800000000001</v>
+        <v>1752.045499276904</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000155e-08</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>83.54108925815363</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.833x + -21927.464</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.833203180643856</v>
       </c>
       <c r="X2" t="n">
         <v>-21927.46412757324</v>
@@ -7550,7 +7320,7 @@
         <v>7.613250234160914e-12</v>
       </c>
       <c r="Z2" t="n">
-        <v>447.4900000000002</v>
+        <v>2724.81086859951</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000007e-08</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>85.6027742174788</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.004x + -28086.546</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.00439145413499</v>
       </c>
       <c r="X3" t="n">
         <v>-28086.54560608976</v>
@@ -7602,7 +7370,7 @@
         <v>3.924982133438359e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>245.8599999999997</v>
+        <v>2412.801406091939</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000125615e-08</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>85.56660121506683</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 12.898x + -26752.548</t>
-        </is>
+      <c r="W4" t="n">
+        <v>12.89786647213452</v>
       </c>
       <c r="X4" t="n">
         <v>-26752.54792915133</v>
@@ -7654,7 +7420,7 @@
         <v>1.745932340444233e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>204.8299999999999</v>
+        <v>2335.828889204699</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000057e-08</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>85.52692118623042</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 12.783x + -25998.348</t>
-        </is>
+      <c r="W5" t="n">
+        <v>12.78299136164219</v>
       </c>
       <c r="X5" t="n">
         <v>-25998.34806713569</v>
@@ -7706,7 +7470,7 @@
         <v>3.102516286622736e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>187.6900000000001</v>
+        <v>2294.508153669695</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000004148e-08</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>85.56520778885677</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 12.894x + -25847.105</t>
-        </is>
+      <c r="W6" t="n">
+        <v>12.89379769666671</v>
       </c>
       <c r="X6" t="n">
         <v>-25847.10498817057</v>
@@ -7758,7 +7520,7 @@
         <v>7.561005022350489e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>182.9300000000003</v>
+        <v>2260.236937979773</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000271e-08</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>84.93502674377717</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.283x + -22128.900</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.28267616714277</v>
       </c>
       <c r="X7" t="n">
         <v>-22128.90027751403</v>
@@ -7810,7 +7570,7 @@
         <v>4.516499178642977e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>191.6400000000001</v>
+        <v>2227.079988370894</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000154e-08</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>85.17315262309545</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 11.842x + -22968.992</t>
-        </is>
+      <c r="W8" t="n">
+        <v>11.84213337489338</v>
       </c>
       <c r="X8" t="n">
         <v>-22968.99222627899</v>
@@ -7862,7 +7620,7 @@
         <v>9.551461243087532e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>181.3400000000001</v>
+        <v>2194.20346379568</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000023e-08</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>84.71958730230838</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 10.820x + -20592.587</t>
-        </is>
+      <c r="W9" t="n">
+        <v>10.81988767641835</v>
       </c>
       <c r="X9" t="n">
         <v>-20592.58714415694</v>
@@ -7914,7 +7670,7 @@
         <v>3.455354940667196e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>183.7700000000002</v>
+        <v>2161.303038555179</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000001e-08</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>84.7263210322689</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 10.834x + -20336.400</t>
-        </is>
+      <c r="W10" t="n">
+        <v>10.83378160695113</v>
       </c>
       <c r="X10" t="n">
         <v>-20336.39985406741</v>
@@ -7966,7 +7720,7 @@
         <v>1.817495786104308e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>179.7499999999998</v>
+        <v>2130.387581425748</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000024e-08</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>84.72152588834932</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 10.824x + -20051.697</t>
-        </is>
+      <c r="W11" t="n">
+        <v>10.82388400250907</v>
       </c>
       <c r="X11" t="n">
         <v>-20051.69724667293</v>
@@ -8018,7 +7770,7 @@
         <v>4.378977546756153e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>172.9200000000001</v>
+        <v>2099.901814899286</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000004319e-08</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>85.36396841722031</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.332x + -25415.245</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.33181524001659</v>
       </c>
       <c r="X2" t="n">
         <v>-25415.24457657672</v>
@@ -8216,7 +7966,7 @@
         <v>6.860479258100244e-12</v>
       </c>
       <c r="Z2" t="n">
-        <v>217.3099999999999</v>
+        <v>2330.843702421264</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>85.40269372275485</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.436x + -24266.667</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.43614488624027</v>
       </c>
       <c r="X3" t="n">
         <v>-24266.66695552331</v>
@@ -8268,7 +8016,7 @@
         <v>1.73284888058118e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>174.53</v>
+        <v>2235.560156804875</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000008756e-08</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>85.19808684191781</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 11.904x + -22851.765</t>
-        </is>
+      <c r="W4" t="n">
+        <v>11.90391550482903</v>
       </c>
       <c r="X4" t="n">
         <v>-22851.76486192156</v>
@@ -8320,7 +8066,7 @@
         <v>2.168935081485231e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>170.27</v>
+        <v>2206.961743971004</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001023e-08</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>84.67205111985109</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 10.723x + -20270.930</t>
-        </is>
+      <c r="W5" t="n">
+        <v>10.72280091545431</v>
       </c>
       <c r="X5" t="n">
         <v>-20270.92972786303</v>
@@ -8372,7 +8116,7 @@
         <v>1.810032929320714e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>175.22</v>
+        <v>2183.867276708726</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000014e-08</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>84.46964869843256</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 10.328x + -19303.397</t>
-        </is>
+      <c r="W6" t="n">
+        <v>10.32804802326924</v>
       </c>
       <c r="X6" t="n">
         <v>-19303.39749494659</v>
@@ -8424,7 +8166,7 @@
         <v>1.788368056468971e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>176.8499999999997</v>
+        <v>2161.878319768788</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000071e-08</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>84.54512158834066</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 10.472x + -19394.217</t>
-        </is>
+      <c r="W7" t="n">
+        <v>10.47183069327585</v>
       </c>
       <c r="X7" t="n">
         <v>-19394.21719050666</v>
@@ -8476,7 +8216,7 @@
         <v>1.588007331900357e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>167.8100000000002</v>
+        <v>2138.526822693762</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000001e-08</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>84.34071743962127</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 10.091x + -18463.944</t>
-        </is>
+      <c r="W8" t="n">
+        <v>10.09126674292746</v>
       </c>
       <c r="X8" t="n">
         <v>-18463.94432362843</v>
@@ -8528,7 +8266,7 @@
         <v>6.318298254907723e-12</v>
       </c>
       <c r="Z8" t="n">
-        <v>164.71</v>
+        <v>2114.658131670821</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>84.02412406788345</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 9.553x + -17245.960</t>
-        </is>
+      <c r="W9" t="n">
+        <v>9.553054751683643</v>
       </c>
       <c r="X9" t="n">
         <v>-17245.96001469352</v>
@@ -8580,7 +8316,7 @@
         <v>2.136616869180104e-11</v>
       </c>
       <c r="Z9" t="n">
-        <v>162.75</v>
+        <v>2090.417843842138</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>83.7070182799701</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 9.068x + -16150.705</t>
-        </is>
+      <c r="W10" t="n">
+        <v>9.068070379306514</v>
       </c>
       <c r="X10" t="n">
         <v>-16150.70519243724</v>
@@ -8632,7 +8366,7 @@
         <v>1.375164881893975e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>161.1400000000001</v>
+        <v>2066.653463733323</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000003e-08</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>83.55096211806342</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 8.847x + -15566.306</t>
-        </is>
+      <c r="W11" t="n">
+        <v>8.846841128214962</v>
       </c>
       <c r="X11" t="n">
         <v>-15566.30593815601</v>
@@ -8684,7 +8416,7 @@
         <v>2.908870016520314e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>158.1600000000001</v>
+        <v>2043.341897333103</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>83.20510911841539</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 8.393x + -14565.468</t>
-        </is>
+      <c r="W12" t="n">
+        <v>8.392617186799223</v>
       </c>
       <c r="X12" t="n">
         <v>-14565.46814579631</v>
@@ -8736,7 +8466,7 @@
         <v>7.322615991314992e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>159.8999999999999</v>
+        <v>2020.16053882251</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000215e-08</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>82.94416941427731</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 8.079x + -13845.923</t>
-        </is>
+      <c r="W13" t="n">
+        <v>8.079254406962169</v>
       </c>
       <c r="X13" t="n">
         <v>-13845.92294194618</v>
@@ -8788,7 +8516,7 @@
         <v>6.785105645371334e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>156.6299999999999</v>
+        <v>1997.490241548479</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000008911e-08</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>82.35141532004666</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 7.446x + -12564.124</t>
-        </is>
+      <c r="W14" t="n">
+        <v>7.44647967384027</v>
       </c>
       <c r="X14" t="n">
         <v>-12564.12392974316</v>
@@ -8840,7 +8566,7 @@
         <v>9.457075084295988e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>159.0300000000002</v>
+        <v>1974.89311248592</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000006e-08</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>81.72614278279597</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 6.877x + -11413.529</t>
-        </is>
+      <c r="W15" t="n">
+        <v>6.876715204637087</v>
       </c>
       <c r="X15" t="n">
         <v>-11413.52851561091</v>
@@ -8892,7 +8616,7 @@
         <v>2.461366273816545e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>147.3300000000002</v>
+        <v>1952.456187246838</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000375e-08</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>81.72800993101737</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 6.878x + -11297.333</t>
-        </is>
+      <c r="W16" t="n">
+        <v>6.878289200609808</v>
       </c>
       <c r="X16" t="n">
         <v>-11297.33283682459</v>
@@ -8944,7 +8666,7 @@
         <v>7.364805196144608e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>155.1600000000001</v>
+        <v>1929.821166693281</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000034e-08</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>80.84340596270073</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 6.204x + -10003.088</t>
-        </is>
+      <c r="W17" t="n">
+        <v>6.203962595418215</v>
       </c>
       <c r="X17" t="n">
         <v>-10003.08752512914</v>
@@ -8996,7 +8716,7 @@
         <v>2.090587102766822e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>149.2299999999998</v>
+        <v>1907.316749380236</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000005716e-08</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>79.33274326220959</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 5.309x + -8347.900</t>
-        </is>
+      <c r="W18" t="n">
+        <v>5.308978731405515</v>
       </c>
       <c r="X18" t="n">
         <v>-8347.899868589046</v>
@@ -9048,7 +8766,7 @@
         <v>0.8741747102887855</v>
       </c>
       <c r="Z18" t="n">
-        <v>138.77</v>
+        <v>2043.001623831462</v>
       </c>
       <c r="AA18" t="n">
         <v>1.587433214147698e-08</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>79.67337303619779</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 5.488x + -8566.869</t>
-        </is>
+      <c r="W19" t="n">
+        <v>5.488145367605095</v>
       </c>
       <c r="X19" t="n">
         <v>-8566.868599982852</v>
@@ -9100,7 +8816,7 @@
         <v>1.858598537852844e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>141.6399999999999</v>
+        <v>1862.850944642408</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000039775e-08</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>77.64206186317803</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 4.564x + -6923.489</t>
-        </is>
+      <c r="W20" t="n">
+        <v>4.564234753341464</v>
       </c>
       <c r="X20" t="n">
         <v>-6923.488510870208</v>
@@ -9152,7 +8866,7 @@
         <v>6.624299844648675e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>140.7</v>
+        <v>1840.576389400926</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000508e-08</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>76.05685305220399</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 4.028x + -5957.660</t>
-        </is>
+      <c r="W21" t="n">
+        <v>4.027803019965535</v>
       </c>
       <c r="X21" t="n">
         <v>-5957.6595670581</v>
@@ -9204,7 +8916,7 @@
         <v>2.354992704632171e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>137.3099999999999</v>
+        <v>1818.722469865537</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000002211e-08</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>71.097240544453</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 2.920x + -4080.116</t>
-        </is>
+      <c r="W22" t="n">
+        <v>2.920302033270598</v>
       </c>
       <c r="X22" t="n">
         <v>-4080.115603521277</v>
@@ -9256,7 +8966,7 @@
         <v>3.697873130761003e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>136.01</v>
+        <v>1797.320649040756</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000001233e-08</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>85.3613115306383</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.325x + -23546.063</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.32472105366688</v>
       </c>
       <c r="X2" t="n">
         <v>-23546.06347275934</v>
@@ -9454,7 +9162,7 @@
         <v>6.22857215759464e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>282</v>
+        <v>2084.168446031461</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000002262e-08</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>85.66532433142999</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.193x + -23123.067</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.19278067786018</v>
       </c>
       <c r="X3" t="n">
         <v>-23123.06722751787</v>
@@ -9506,7 +9212,7 @@
         <v>7.982835743069414e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>196.3299999999999</v>
+        <v>1952.384593254094</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000027e-08</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>85.77257657518797</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.529x + -23170.736</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.52875406994632</v>
       </c>
       <c r="X4" t="n">
         <v>-23170.73634900921</v>
@@ -9558,7 +9262,7 @@
         <v>1.020905696240408e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>171.9399999999998</v>
+        <v>1911.773568219954</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000002281e-08</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>85.74195647875764</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 13.431x + -22692.429</t>
-        </is>
+      <c r="W5" t="n">
+        <v>13.43111193371858</v>
       </c>
       <c r="X5" t="n">
         <v>-22692.42861385292</v>
@@ -9610,7 +9312,7 @@
         <v>8.39835052292691e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>166.7700000000002</v>
+        <v>1887.252671064778</v>
       </c>
       <c r="AA5" t="n">
         <v>1.00000000008713e-08</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>85.55789911488958</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 12.872x + -21424.854</t>
-        </is>
+      <c r="W6" t="n">
+        <v>12.87249824511795</v>
       </c>
       <c r="X6" t="n">
         <v>-21424.85353608882</v>
@@ -9662,7 +9362,7 @@
         <v>6.907067596927201e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>169.99</v>
+        <v>1862.036001391821</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000029612e-08</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>85.77356266450983</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 13.532x + -22272.911</t>
-        </is>
+      <c r="W7" t="n">
+        <v>13.53192200844641</v>
       </c>
       <c r="X7" t="n">
         <v>-22272.91136226284</v>
@@ -9714,7 +9412,7 @@
         <v>9.615166456038347e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>161.9199999999998</v>
+        <v>1834.106353993896</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000008e-08</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>85.70049180232654</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 13.301x + -21553.447</t>
-        </is>
+      <c r="W8" t="n">
+        <v>13.30110111065315</v>
       </c>
       <c r="X8" t="n">
         <v>-21553.44727666653</v>
@@ -9766,7 +9462,7 @@
         <v>1.781378658722411e-12</v>
       </c>
       <c r="Z8" t="n">
-        <v>155.04</v>
+        <v>1805.56070717832</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>85.80781188803128</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 13.643x + -21796.943</t>
-        </is>
+      <c r="W9" t="n">
+        <v>13.64287515778695</v>
       </c>
       <c r="X9" t="n">
         <v>-21796.94330786216</v>
@@ -9818,7 +9512,7 @@
         <v>6.54342257965754e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>153.6399999999999</v>
+        <v>1777.306673248712</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001536e-08</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>85.49453606475325</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 12.691x + -19913.253</t>
-        </is>
+      <c r="W10" t="n">
+        <v>12.69073188331934</v>
       </c>
       <c r="X10" t="n">
         <v>-19913.25335132917</v>
@@ -9870,7 +9562,7 @@
         <v>1.14376364950672e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>154.26</v>
+        <v>1750.24396193424</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000896e-08</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>85.31105570871897</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 12.192x + -18812.886</t>
-        </is>
+      <c r="W11" t="n">
+        <v>12.19204330356146</v>
       </c>
       <c r="X11" t="n">
         <v>-18812.88591572936</v>
@@ -9922,7 +9612,7 @@
         <v>1.90786882155713e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>154.97</v>
+        <v>1724.361446082798</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000064e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 33.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 33.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-185.25</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-145.29</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-130.3100000000002</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-120.72</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-114.3900000000001</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-102.4100000000001</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-104.9400000000001</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-89.81000000000017</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-94.31000000000017</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-86.44000000000005</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-327.0500000000002</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-192.8899999999999</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-149</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-113.5500000000002</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-114.3600000000001</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-92.5</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-95.29999999999973</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-83.73000000000002</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-80.49000000000001</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-71.93000000000006</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-413.0799999999999</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-234.1900000000001</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-180.3900000000003</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-155.0599999999999</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-142.4100000000003</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-133.0100000000002</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-115.71</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-120.1000000000001</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-110.3300000000002</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-108.3200000000002</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-447.4900000000002</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-245.8599999999997</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-204.8299999999999</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-175.9500000000003</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-163.0900000000001</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-161.72</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-145.96</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-140.1500000000001</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-134.99</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-121.7900000000002</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-282</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-196.3299999999999</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-171.9399999999998</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-155.8700000000001</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-156</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-145.0899999999999</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-130.97</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-131.6099999999999</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-125.8899999999999</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-123.9200000000001</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 33.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 33.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-185.25</v>
+        <v>1702.875</v>
       </c>
       <c r="D2" t="n">
         <v>2.64227e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-145.29</v>
+        <v>1595.431</v>
       </c>
       <c r="D3" t="n">
         <v>2.65191e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-130.3100000000002</v>
+        <v>1554.83</v>
       </c>
       <c r="D4" t="n">
         <v>2.65466e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-120.72</v>
+        <v>1525.224</v>
       </c>
       <c r="D5" t="n">
         <v>2.65669e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-114.3900000000001</v>
+        <v>1499.3</v>
       </c>
       <c r="D6" t="n">
         <v>2.65641e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-102.4100000000001</v>
+        <v>1480.618</v>
       </c>
       <c r="D7" t="n">
         <v>2.65833e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-104.9400000000001</v>
+        <v>1447.972</v>
       </c>
       <c r="D8" t="n">
         <v>2.66245e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-89.81000000000017</v>
+        <v>1435.485</v>
       </c>
       <c r="D9" t="n">
         <v>2.66563e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-94.31000000000017</v>
+        <v>1405.035</v>
       </c>
       <c r="D10" t="n">
         <v>2.66705e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-86.44000000000005</v>
+        <v>1386.906</v>
       </c>
       <c r="D11" t="n">
         <v>2.67083e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-166.79</v>
+        <v>1676.785</v>
       </c>
       <c r="D2" t="n">
         <v>2.59517e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-138.5699999999999</v>
+        <v>1583.639</v>
       </c>
       <c r="D3" t="n">
         <v>2.63148e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-144.4399999999998</v>
+        <v>1534.87</v>
       </c>
       <c r="D4" t="n">
         <v>2.64489e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-129.6000000000001</v>
+        <v>1514.008</v>
       </c>
       <c r="D5" t="n">
         <v>2.65485e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-126.0500000000002</v>
+        <v>1490.245</v>
       </c>
       <c r="D6" t="n">
         <v>2.66196e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-115.6499999999999</v>
+        <v>1472.704</v>
       </c>
       <c r="D7" t="n">
         <v>2.67142e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-122.6800000000001</v>
+        <v>1439.099</v>
       </c>
       <c r="D8" t="n">
         <v>2.67993e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-115.76</v>
+        <v>1421.501</v>
       </c>
       <c r="D9" t="n">
         <v>2.68604e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-113.03</v>
+        <v>1395.551</v>
       </c>
       <c r="D10" t="n">
         <v>2.69371e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-96.42000000000007</v>
+        <v>1387.541</v>
       </c>
       <c r="D11" t="n">
         <v>2.70096e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-89.90999999999985</v>
+        <v>1369.782</v>
       </c>
       <c r="D12" t="n">
         <v>2.70871e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-91.46000000000004</v>
+        <v>1349.203</v>
       </c>
       <c r="D13" t="n">
         <v>2.71297e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-81.08999999999992</v>
+        <v>1337.807</v>
       </c>
       <c r="D14" t="n">
         <v>2.7203e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-81.00999999999999</v>
+        <v>1312.425</v>
       </c>
       <c r="D15" t="n">
         <v>2.72673e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-71.17000000000007</v>
+        <v>1300.218</v>
       </c>
       <c r="D16" t="n">
         <v>2.73212e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-78.63999999999987</v>
+        <v>1274.406</v>
       </c>
       <c r="D17" t="n">
         <v>2.73692e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-68.59999999999991</v>
+        <v>1264.397</v>
       </c>
       <c r="D18" t="n">
         <v>2.74213e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-61.29999999999995</v>
+        <v>1246.777</v>
       </c>
       <c r="D19" t="n">
         <v>2.74817e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-53.86000000000013</v>
+        <v>1235.158</v>
       </c>
       <c r="D20" t="n">
         <v>2.7531e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-53.40000000000009</v>
+        <v>1214.839</v>
       </c>
       <c r="D21" t="n">
         <v>2.75968e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-60.09000000000015</v>
+        <v>1192.154</v>
       </c>
       <c r="D22" t="n">
         <v>2.7627e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-194.9200000000001</v>
+        <v>1643.652</v>
       </c>
       <c r="D2" t="n">
         <v>2.62418e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-136.8599999999999</v>
+        <v>1538.112</v>
       </c>
       <c r="D3" t="n">
         <v>2.6527e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-116.29</v>
+        <v>1504.796</v>
       </c>
       <c r="D4" t="n">
         <v>2.66039e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-112.6900000000001</v>
+        <v>1474.565</v>
       </c>
       <c r="D5" t="n">
         <v>2.66399e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-103.22</v>
+        <v>1456.875</v>
       </c>
       <c r="D6" t="n">
         <v>2.66739e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-97.26999999999998</v>
+        <v>1436.339</v>
       </c>
       <c r="D7" t="n">
         <v>2.67021e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-90.00999999999999</v>
+        <v>1419.34</v>
       </c>
       <c r="D8" t="n">
         <v>2.67316e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-98.52999999999997</v>
+        <v>1384.283</v>
       </c>
       <c r="D9" t="n">
         <v>2.67727e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-89.64999999999986</v>
+        <v>1368.206</v>
       </c>
       <c r="D10" t="n">
         <v>2.68281e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-87.29999999999995</v>
+        <v>1355.843</v>
       </c>
       <c r="D11" t="n">
         <v>2.68569e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-81.05000000000018</v>
+        <v>1336.551</v>
       </c>
       <c r="D12" t="n">
         <v>2.69017e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-75.99000000000001</v>
+        <v>1316.726</v>
       </c>
       <c r="D13" t="n">
         <v>2.69528e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-78.23000000000002</v>
+        <v>1292.945</v>
       </c>
       <c r="D14" t="n">
         <v>2.69888e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-66.96000000000004</v>
+        <v>1286.538</v>
       </c>
       <c r="D15" t="n">
         <v>2.70251e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-67.56999999999994</v>
+        <v>1264.156</v>
       </c>
       <c r="D16" t="n">
         <v>2.70732e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-69.18000000000006</v>
+        <v>1243.506</v>
       </c>
       <c r="D17" t="n">
         <v>2.71091e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-66.79999999999995</v>
+        <v>1222.46</v>
       </c>
       <c r="D18" t="n">
         <v>2.71498e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-54.61000000000013</v>
+        <v>1214.631</v>
       </c>
       <c r="D19" t="n">
         <v>2.71864e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-58.73000000000002</v>
+        <v>1190.607</v>
       </c>
       <c r="D20" t="n">
         <v>2.72255e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-51.47000000000003</v>
+        <v>1178.969</v>
       </c>
       <c r="D21" t="n">
         <v>2.72595e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-44.11000000000013</v>
+        <v>1166.267</v>
       </c>
       <c r="D22" t="n">
         <v>2.73001e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-327.0500000000002</v>
+        <v>2064.958</v>
       </c>
       <c r="D2" t="n">
         <v>2.47098e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-192.8899999999999</v>
+        <v>1826.03</v>
       </c>
       <c r="D3" t="n">
         <v>2.59225e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-149</v>
+        <v>1762.934</v>
       </c>
       <c r="D4" t="n">
         <v>2.61657e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-113.5500000000002</v>
+        <v>1736.608</v>
       </c>
       <c r="D5" t="n">
         <v>2.62951e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-114.3600000000001</v>
+        <v>1687.32</v>
       </c>
       <c r="D6" t="n">
         <v>2.64183e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-92.5</v>
+        <v>1665.352</v>
       </c>
       <c r="D7" t="n">
         <v>2.65391e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-95.29999999999973</v>
+        <v>1628.198</v>
       </c>
       <c r="D8" t="n">
         <v>2.66435e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-83.73000000000002</v>
+        <v>1598.827</v>
       </c>
       <c r="D9" t="n">
         <v>2.67776e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-80.49000000000001</v>
+        <v>1569.12</v>
       </c>
       <c r="D10" t="n">
         <v>2.68876e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-71.93000000000006</v>
+        <v>1543.351</v>
       </c>
       <c r="D11" t="n">
         <v>2.69876e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-218.0700000000002</v>
+        <v>1653.006</v>
       </c>
       <c r="D2" t="n">
         <v>2.65784e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-139.2900000000002</v>
+        <v>1560.377</v>
       </c>
       <c r="D3" t="n">
         <v>2.68056e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-131.01</v>
+        <v>1512.67</v>
       </c>
       <c r="D4" t="n">
         <v>2.69365e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-110.6700000000001</v>
+        <v>1497.537</v>
       </c>
       <c r="D5" t="n">
         <v>2.70344e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-112.96</v>
+        <v>1470.086</v>
       </c>
       <c r="D6" t="n">
         <v>2.71011e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-101.21</v>
+        <v>1454.206</v>
       </c>
       <c r="D7" t="n">
         <v>2.71684e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-95.14999999999986</v>
+        <v>1434.165</v>
       </c>
       <c r="D8" t="n">
         <v>2.72394e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-90.19000000000005</v>
+        <v>1414.712</v>
       </c>
       <c r="D9" t="n">
         <v>2.73011e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-83.03999999999996</v>
+        <v>1393.566</v>
       </c>
       <c r="D10" t="n">
         <v>2.738e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-86.18000000000006</v>
+        <v>1372.689</v>
       </c>
       <c r="D11" t="n">
         <v>2.73995e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-84.56999999999994</v>
+        <v>1352.863</v>
       </c>
       <c r="D12" t="n">
         <v>2.74768e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-84.16000000000008</v>
+        <v>1332.451</v>
       </c>
       <c r="D13" t="n">
         <v>2.75174e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-77.10000000000014</v>
+        <v>1319.375</v>
       </c>
       <c r="D14" t="n">
         <v>2.7566e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-67.98000000000002</v>
+        <v>1305.521</v>
       </c>
       <c r="D15" t="n">
         <v>2.7625e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-64.84999999999991</v>
+        <v>1287.448</v>
       </c>
       <c r="D16" t="n">
         <v>2.76572e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-55.42000000000007</v>
+        <v>1277.658</v>
       </c>
       <c r="D17" t="n">
         <v>2.77116e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-61.5</v>
+        <v>1253.345</v>
       </c>
       <c r="D18" t="n">
         <v>2.77452e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-49.51999999999998</v>
+        <v>1246.089</v>
       </c>
       <c r="D19" t="n">
         <v>2.78037e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-48.67999999999984</v>
+        <v>1225.326</v>
       </c>
       <c r="D20" t="n">
         <v>2.78435e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-45.74000000000001</v>
+        <v>1206.616</v>
       </c>
       <c r="D21" t="n">
         <v>2.7898e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-35.18000000000006</v>
+        <v>1200.128</v>
       </c>
       <c r="D22" t="n">
         <v>2.79508e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-413.0799999999999</v>
+        <v>2260.513</v>
       </c>
       <c r="D2" t="n">
         <v>2.33552e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-234.1900000000001</v>
+        <v>1824.185</v>
       </c>
       <c r="D3" t="n">
         <v>2.57134e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-180.3900000000003</v>
+        <v>1734.85</v>
       </c>
       <c r="D4" t="n">
         <v>2.61433e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-155.0599999999999</v>
+        <v>1701.509</v>
       </c>
       <c r="D5" t="n">
         <v>2.62997e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-142.4100000000003</v>
+        <v>1666.333</v>
       </c>
       <c r="D6" t="n">
         <v>2.64377e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-133.0100000000002</v>
+        <v>1636.368</v>
       </c>
       <c r="D7" t="n">
         <v>2.65565e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-115.71</v>
+        <v>1616.489</v>
       </c>
       <c r="D8" t="n">
         <v>2.66743e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-120.1000000000001</v>
+        <v>1576.785</v>
       </c>
       <c r="D9" t="n">
         <v>2.68108e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-110.3300000000002</v>
+        <v>1556.787</v>
       </c>
       <c r="D10" t="n">
         <v>2.69206e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-108.3200000000002</v>
+        <v>1526.186</v>
       </c>
       <c r="D11" t="n">
         <v>2.70435e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-288.8999999999999</v>
+        <v>1609.91</v>
       </c>
       <c r="D2" t="n">
         <v>2.70776e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-181.2999999999997</v>
+        <v>1533.943</v>
       </c>
       <c r="D3" t="n">
         <v>2.70426e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-156.1700000000001</v>
+        <v>1501.203</v>
       </c>
       <c r="D4" t="n">
         <v>2.71258e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-149.24</v>
+        <v>1470.704</v>
       </c>
       <c r="D5" t="n">
         <v>2.72158e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-143.55</v>
+        <v>1447.689</v>
       </c>
       <c r="D6" t="n">
         <v>2.73062e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-143.8099999999999</v>
+        <v>1420.083</v>
       </c>
       <c r="D7" t="n">
         <v>2.7394e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-122.28</v>
+        <v>1407.208</v>
       </c>
       <c r="D8" t="n">
         <v>2.75028e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-122.72</v>
+        <v>1387.607</v>
       </c>
       <c r="D9" t="n">
         <v>2.75623e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-119.55</v>
+        <v>1366.414</v>
       </c>
       <c r="D10" t="n">
         <v>2.76358e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-108.6500000000001</v>
+        <v>1347.876</v>
       </c>
       <c r="D11" t="n">
         <v>2.77004e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-111.8200000000002</v>
+        <v>1323.162</v>
       </c>
       <c r="D12" t="n">
         <v>2.77827e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-105.2700000000002</v>
+        <v>1305.796</v>
       </c>
       <c r="D13" t="n">
         <v>2.78304e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-99.87999999999988</v>
+        <v>1286.966</v>
       </c>
       <c r="D14" t="n">
         <v>2.78987e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-88.95000000000005</v>
+        <v>1274.237</v>
       </c>
       <c r="D15" t="n">
         <v>2.79545e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-87.98000000000002</v>
+        <v>1255.979</v>
       </c>
       <c r="D16" t="n">
         <v>2.80233e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-82.00999999999999</v>
+        <v>1236.098</v>
       </c>
       <c r="D17" t="n">
         <v>2.80835e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-80.80999999999995</v>
+        <v>1218.23</v>
       </c>
       <c r="D18" t="n">
         <v>2.81236e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-76.11000000000013</v>
+        <v>1200.111</v>
       </c>
       <c r="D19" t="n">
         <v>2.81805e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-72.76000000000022</v>
+        <v>1182.871</v>
       </c>
       <c r="D20" t="n">
         <v>2.82349e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-67.81999999999994</v>
+        <v>1166.748</v>
       </c>
       <c r="D21" t="n">
         <v>2.82974e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-66.72000000000003</v>
+        <v>1147.86</v>
       </c>
       <c r="D22" t="n">
         <v>2.83504e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-447.4900000000002</v>
+        <v>2080.499</v>
       </c>
       <c r="D2" t="n">
         <v>2.42018e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-245.8599999999997</v>
+        <v>1752.981</v>
       </c>
       <c r="D3" t="n">
         <v>2.60505e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-204.8299999999999</v>
+        <v>1667.415</v>
       </c>
       <c r="D4" t="n">
         <v>2.63961e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-175.9500000000003</v>
+        <v>1631.705</v>
       </c>
       <c r="D5" t="n">
         <v>2.65618e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-163.0900000000001</v>
+        <v>1600.884</v>
       </c>
       <c r="D6" t="n">
         <v>2.66848e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-161.72</v>
+        <v>1560.339</v>
       </c>
       <c r="D7" t="n">
         <v>2.68399e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-145.96</v>
+        <v>1539.223</v>
       </c>
       <c r="D8" t="n">
         <v>2.69516e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-140.1500000000001</v>
+        <v>1505.867</v>
       </c>
       <c r="D9" t="n">
         <v>2.71144e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-134.99</v>
+        <v>1480.734</v>
       </c>
       <c r="D10" t="n">
         <v>2.72276e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-121.7900000000002</v>
+        <v>1463.063</v>
       </c>
       <c r="D11" t="n">
         <v>2.73653e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-217.3099999999999</v>
+        <v>1641.585</v>
       </c>
       <c r="D2" t="n">
         <v>2.67715e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-145.3999999999999</v>
+        <v>1541.11</v>
       </c>
       <c r="D3" t="n">
         <v>2.70687e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-130.5100000000002</v>
+        <v>1509.271</v>
       </c>
       <c r="D4" t="n">
         <v>2.71843e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-129.27</v>
+        <v>1482.039</v>
       </c>
       <c r="D5" t="n">
         <v>2.72525e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-125.55</v>
+        <v>1458.855</v>
       </c>
       <c r="D6" t="n">
         <v>2.73475e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-114</v>
+        <v>1445.709</v>
       </c>
       <c r="D7" t="n">
         <v>2.74087e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-106.73</v>
+        <v>1426.926</v>
       </c>
       <c r="D8" t="n">
         <v>2.74862e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-100.52</v>
+        <v>1407.073</v>
       </c>
       <c r="D9" t="n">
         <v>2.75641e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-93.62000000000012</v>
+        <v>1388.039</v>
       </c>
       <c r="D10" t="n">
         <v>2.76416e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-89.28999999999996</v>
+        <v>1370.136</v>
       </c>
       <c r="D11" t="n">
         <v>2.76847e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-89.04999999999995</v>
+        <v>1347.418</v>
       </c>
       <c r="D12" t="n">
         <v>2.77809e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-83.82999999999993</v>
+        <v>1331.037</v>
       </c>
       <c r="D13" t="n">
         <v>2.78218e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-82.3900000000001</v>
+        <v>1308.014</v>
       </c>
       <c r="D14" t="n">
         <v>2.78952e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-69.25</v>
+        <v>1304.887</v>
       </c>
       <c r="D15" t="n">
         <v>2.79522e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-75.8900000000001</v>
+        <v>1276.011</v>
       </c>
       <c r="D16" t="n">
         <v>2.80144e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-67.28999999999996</v>
+        <v>1263.615</v>
       </c>
       <c r="D17" t="n">
         <v>2.80707e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-55.22000000000003</v>
+        <v>1253.506</v>
       </c>
       <c r="D18" t="n">
         <v>2.8138e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-58.28999999999996</v>
+        <v>1231.156</v>
       </c>
       <c r="D19" t="n">
         <v>2.81942e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-53.50999999999999</v>
+        <v>1212.164</v>
       </c>
       <c r="D20" t="n">
         <v>2.82641e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-49.64999999999986</v>
+        <v>1195.068</v>
       </c>
       <c r="D21" t="n">
         <v>2.83264e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-43.68999999999983</v>
+        <v>1179.113</v>
       </c>
       <c r="D22" t="n">
         <v>2.83908e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-282</v>
+        <v>1458.226</v>
       </c>
       <c r="D2" t="n">
         <v>2.67718e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-196.3299999999999</v>
+        <v>1300.667</v>
       </c>
       <c r="D3" t="n">
         <v>2.72726e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-171.9399999999998</v>
+        <v>1261.579</v>
       </c>
       <c r="D4" t="n">
         <v>2.74296e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-155.8700000000001</v>
+        <v>1238.778</v>
       </c>
       <c r="D5" t="n">
         <v>2.75188e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-156</v>
+        <v>1211.349</v>
       </c>
       <c r="D6" t="n">
         <v>2.76046e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-145.0899999999999</v>
+        <v>1197.885</v>
       </c>
       <c r="D7" t="n">
         <v>2.76752e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-130.97</v>
+        <v>1176.457</v>
       </c>
       <c r="D8" t="n">
         <v>2.78237e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-131.6099999999999</v>
+        <v>1151.93</v>
       </c>
       <c r="D9" t="n">
         <v>2.79261e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-125.8899999999999</v>
+        <v>1126.673</v>
       </c>
       <c r="D10" t="n">
         <v>2.80209e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-123.9200000000001</v>
+        <v>1101.556</v>
       </c>
       <c r="D11" t="n">
         <v>2.81368e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 33.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 33.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>1702.875</v>
       </c>
+      <c r="C2" t="n">
+        <v>2147.703941961174</v>
+      </c>
       <c r="D2" t="n">
         <v>2.64227e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>1595.431</v>
       </c>
+      <c r="C3" t="n">
+        <v>2034.573746936335</v>
+      </c>
       <c r="D3" t="n">
         <v>2.65191e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>1554.83</v>
       </c>
+      <c r="C4" t="n">
+        <v>1993.494989208164</v>
+      </c>
       <c r="D4" t="n">
         <v>2.65466e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>1525.224</v>
       </c>
+      <c r="C5" t="n">
+        <v>1967.353731151327</v>
+      </c>
       <c r="D5" t="n">
         <v>2.65669e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>1499.3</v>
       </c>
+      <c r="C6" t="n">
+        <v>1946.641241504192</v>
+      </c>
       <c r="D6" t="n">
         <v>2.65641e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>1480.618</v>
       </c>
+      <c r="C7" t="n">
+        <v>1925.927501267209</v>
+      </c>
       <c r="D7" t="n">
         <v>2.65833e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>1447.972</v>
       </c>
+      <c r="C8" t="n">
+        <v>1897.462823105808</v>
+      </c>
       <c r="D8" t="n">
         <v>2.66245e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>1435.485</v>
       </c>
+      <c r="C9" t="n">
+        <v>1882.879533269484</v>
+      </c>
       <c r="D9" t="n">
         <v>2.66563e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>1405.035</v>
       </c>
+      <c r="C10" t="n">
+        <v>1854.805642539455</v>
+      </c>
       <c r="D10" t="n">
         <v>2.66705e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>1386.906</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1837.98101779564</v>
       </c>
       <c r="D11" t="n">
         <v>2.67083e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>1676.785</v>
       </c>
+      <c r="C2" t="n">
+        <v>2226.178872977625</v>
+      </c>
       <c r="D2" t="n">
         <v>2.59517e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>1583.639</v>
       </c>
+      <c r="C3" t="n">
+        <v>2112.788697144857</v>
+      </c>
       <c r="D3" t="n">
         <v>2.63148e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>1534.87</v>
       </c>
+      <c r="C4" t="n">
+        <v>2065.8435516544</v>
+      </c>
       <c r="D4" t="n">
         <v>2.64489e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>1514.008</v>
       </c>
+      <c r="C5" t="n">
+        <v>2044.887980060815</v>
+      </c>
       <c r="D5" t="n">
         <v>2.65485e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>1490.245</v>
       </c>
+      <c r="C6" t="n">
+        <v>2021.708966634912</v>
+      </c>
       <c r="D6" t="n">
         <v>2.66196e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>1472.704</v>
       </c>
+      <c r="C7" t="n">
+        <v>2005.084484741772</v>
+      </c>
       <c r="D7" t="n">
         <v>2.67142e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>1439.099</v>
       </c>
+      <c r="C8" t="n">
+        <v>1977.325832680681</v>
+      </c>
       <c r="D8" t="n">
         <v>2.67993e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>1421.501</v>
       </c>
+      <c r="C9" t="n">
+        <v>1960.68107682527</v>
+      </c>
       <c r="D9" t="n">
         <v>2.68604e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>1395.551</v>
       </c>
+      <c r="C10" t="n">
+        <v>1937.424287375647</v>
+      </c>
       <c r="D10" t="n">
         <v>2.69371e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>1387.541</v>
       </c>
+      <c r="C11" t="n">
+        <v>1925.152072152474</v>
+      </c>
       <c r="D11" t="n">
         <v>2.70096e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>1369.782</v>
       </c>
+      <c r="C12" t="n">
+        <v>1906.243953772524</v>
+      </c>
       <c r="D12" t="n">
         <v>2.70871e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>1349.203</v>
       </c>
+      <c r="C13" t="n">
+        <v>1884.48404618861</v>
+      </c>
       <c r="D13" t="n">
         <v>2.71297e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>1337.807</v>
       </c>
+      <c r="C14" t="n">
+        <v>1872.736410747223</v>
+      </c>
       <c r="D14" t="n">
         <v>2.7203e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>1312.425</v>
       </c>
+      <c r="C15" t="n">
+        <v>1849.585881106584</v>
+      </c>
       <c r="D15" t="n">
         <v>2.72673e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>1300.218</v>
       </c>
+      <c r="C16" t="n">
+        <v>1838.347656313046</v>
+      </c>
       <c r="D16" t="n">
         <v>2.73212e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>1274.406</v>
       </c>
+      <c r="C17" t="n">
+        <v>1815.279501449214</v>
+      </c>
       <c r="D17" t="n">
         <v>2.73692e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>1264.397</v>
       </c>
+      <c r="C18" t="n">
+        <v>1803.136923461276</v>
+      </c>
       <c r="D18" t="n">
         <v>2.74213e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>1246.777</v>
       </c>
+      <c r="C19" t="n">
+        <v>1789.133361620432</v>
+      </c>
       <c r="D19" t="n">
         <v>2.74817e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>1235.158</v>
       </c>
+      <c r="C20" t="n">
+        <v>1773.711561880646</v>
+      </c>
       <c r="D20" t="n">
         <v>2.7531e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>1214.839</v>
       </c>
+      <c r="C21" t="n">
+        <v>1759.943161463561</v>
+      </c>
       <c r="D21" t="n">
         <v>2.75968e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>1192.154</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1735.460339037389</v>
       </c>
       <c r="D22" t="n">
         <v>2.7627e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>1643.652</v>
       </c>
+      <c r="C2" t="n">
+        <v>2091.404410564804</v>
+      </c>
       <c r="D2" t="n">
         <v>2.62418e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>1538.112</v>
       </c>
+      <c r="C3" t="n">
+        <v>1967.31306644053</v>
+      </c>
       <c r="D3" t="n">
         <v>2.6527e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>1504.796</v>
       </c>
+      <c r="C4" t="n">
+        <v>1930.61715316485</v>
+      </c>
       <c r="D4" t="n">
         <v>2.66039e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>1474.565</v>
       </c>
+      <c r="C5" t="n">
+        <v>1903.994522340445</v>
+      </c>
       <c r="D5" t="n">
         <v>2.66399e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>1456.875</v>
       </c>
+      <c r="C6" t="n">
+        <v>1885.252497554885</v>
+      </c>
       <c r="D6" t="n">
         <v>2.66739e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>1436.339</v>
       </c>
+      <c r="C7" t="n">
+        <v>1866.651845284745</v>
+      </c>
       <c r="D7" t="n">
         <v>2.67021e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>1419.34</v>
       </c>
+      <c r="C8" t="n">
+        <v>1848.634761008779</v>
+      </c>
       <c r="D8" t="n">
         <v>2.67316e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>1384.283</v>
       </c>
+      <c r="C9" t="n">
+        <v>1819.614680105183</v>
+      </c>
       <c r="D9" t="n">
         <v>2.67727e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>1368.206</v>
       </c>
+      <c r="C10" t="n">
+        <v>1803.709941023973</v>
+      </c>
       <c r="D10" t="n">
         <v>2.68281e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>1355.843</v>
       </c>
+      <c r="C11" t="n">
+        <v>1785.714396081117</v>
+      </c>
       <c r="D11" t="n">
         <v>2.68569e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>1336.551</v>
       </c>
+      <c r="C12" t="n">
+        <v>1765.302482505542</v>
+      </c>
       <c r="D12" t="n">
         <v>2.69017e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>1316.726</v>
       </c>
+      <c r="C13" t="n">
+        <v>1748.482881939796</v>
+      </c>
       <c r="D13" t="n">
         <v>2.69528e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>1292.945</v>
       </c>
+      <c r="C14" t="n">
+        <v>1728.205893254752</v>
+      </c>
       <c r="D14" t="n">
         <v>2.69888e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>1286.538</v>
       </c>
+      <c r="C15" t="n">
+        <v>1717.336519238626</v>
+      </c>
       <c r="D15" t="n">
         <v>2.70251e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>1264.156</v>
       </c>
+      <c r="C16" t="n">
+        <v>1698.756847496746</v>
+      </c>
       <c r="D16" t="n">
         <v>2.70732e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>1243.506</v>
       </c>
+      <c r="C17" t="n">
+        <v>1678.371641483611</v>
+      </c>
       <c r="D17" t="n">
         <v>2.71091e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>1222.46</v>
       </c>
+      <c r="C18" t="n">
+        <v>1660.63406828308</v>
+      </c>
       <c r="D18" t="n">
         <v>2.71498e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>1214.631</v>
       </c>
+      <c r="C19" t="n">
+        <v>1649.259854298811</v>
+      </c>
       <c r="D19" t="n">
         <v>2.71864e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>1190.607</v>
       </c>
+      <c r="C20" t="n">
+        <v>1628.872371835343</v>
+      </c>
       <c r="D20" t="n">
         <v>2.72255e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>1178.969</v>
       </c>
+      <c r="C21" t="n">
+        <v>1617.392580275306</v>
+      </c>
       <c r="D21" t="n">
         <v>2.72595e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>1166.267</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1600.633082554917</v>
       </c>
       <c r="D22" t="n">
         <v>2.73001e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>2064.958</v>
       </c>
+      <c r="C2" t="n">
+        <v>2522.300651127119</v>
+      </c>
       <c r="D2" t="n">
         <v>2.47098e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>1826.03</v>
       </c>
+      <c r="C3" t="n">
+        <v>2238.671427085753</v>
+      </c>
       <c r="D3" t="n">
         <v>2.59225e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>1762.934</v>
       </c>
+      <c r="C4" t="n">
+        <v>2169.310274572266</v>
+      </c>
       <c r="D4" t="n">
         <v>2.61657e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>1736.608</v>
       </c>
+      <c r="C5" t="n">
+        <v>2138.700858034375</v>
+      </c>
       <c r="D5" t="n">
         <v>2.62951e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>1687.32</v>
       </c>
+      <c r="C6" t="n">
+        <v>2099.513952056333</v>
+      </c>
       <c r="D6" t="n">
         <v>2.64183e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>1665.352</v>
       </c>
+      <c r="C7" t="n">
+        <v>2074.796833415422</v>
+      </c>
       <c r="D7" t="n">
         <v>2.65391e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>1628.198</v>
       </c>
+      <c r="C8" t="n">
+        <v>2042.621561436311</v>
+      </c>
       <c r="D8" t="n">
         <v>2.66435e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>1598.827</v>
       </c>
+      <c r="C9" t="n">
+        <v>2013.796845888897</v>
+      </c>
       <c r="D9" t="n">
         <v>2.67776e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>1569.12</v>
       </c>
+      <c r="C10" t="n">
+        <v>1986.713228762256</v>
+      </c>
       <c r="D10" t="n">
         <v>2.68876e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>1543.351</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1961.255725124438</v>
       </c>
       <c r="D11" t="n">
         <v>2.69876e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>1653.006</v>
       </c>
+      <c r="C2" t="n">
+        <v>2171.528545421851</v>
+      </c>
       <c r="D2" t="n">
         <v>2.65784e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>1560.377</v>
       </c>
+      <c r="C3" t="n">
+        <v>1984.619477324907</v>
+      </c>
       <c r="D3" t="n">
         <v>2.68056e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>1512.67</v>
       </c>
+      <c r="C4" t="n">
+        <v>1940.918155614015</v>
+      </c>
       <c r="D4" t="n">
         <v>2.69365e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>1497.537</v>
       </c>
+      <c r="C5" t="n">
+        <v>1921.773307914347</v>
+      </c>
       <c r="D5" t="n">
         <v>2.70344e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>1470.086</v>
       </c>
+      <c r="C6" t="n">
+        <v>1899.835777132294</v>
+      </c>
       <c r="D6" t="n">
         <v>2.71011e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>1454.206</v>
       </c>
+      <c r="C7" t="n">
+        <v>1881.928038377901</v>
+      </c>
       <c r="D7" t="n">
         <v>2.71684e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>1434.165</v>
       </c>
+      <c r="C8" t="n">
+        <v>1864.141521129716</v>
+      </c>
       <c r="D8" t="n">
         <v>2.72394e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>1414.712</v>
       </c>
+      <c r="C9" t="n">
+        <v>1844.192554933649</v>
+      </c>
       <c r="D9" t="n">
         <v>2.73011e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>1393.566</v>
       </c>
+      <c r="C10" t="n">
+        <v>1824.613600836207</v>
+      </c>
       <c r="D10" t="n">
         <v>2.738e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>1372.689</v>
       </c>
+      <c r="C11" t="n">
+        <v>1803.282789824251</v>
+      </c>
       <c r="D11" t="n">
         <v>2.73995e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>1352.863</v>
       </c>
+      <c r="C12" t="n">
+        <v>1783.123078108059</v>
+      </c>
       <c r="D12" t="n">
         <v>2.74768e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>1332.451</v>
       </c>
+      <c r="C13" t="n">
+        <v>1765.861584025642</v>
+      </c>
       <c r="D13" t="n">
         <v>2.75174e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>1319.375</v>
       </c>
+      <c r="C14" t="n">
+        <v>1750.488402691555</v>
+      </c>
       <c r="D14" t="n">
         <v>2.7566e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>1305.521</v>
       </c>
+      <c r="C15" t="n">
+        <v>1736.601393675771</v>
+      </c>
       <c r="D15" t="n">
         <v>2.7625e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>1287.448</v>
       </c>
+      <c r="C16" t="n">
+        <v>1721.435783203664</v>
+      </c>
       <c r="D16" t="n">
         <v>2.76572e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>1277.658</v>
       </c>
+      <c r="C17" t="n">
+        <v>1709.928727618283</v>
+      </c>
       <c r="D17" t="n">
         <v>2.77116e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>1253.345</v>
       </c>
+      <c r="C18" t="n">
+        <v>1688.917405678917</v>
+      </c>
       <c r="D18" t="n">
         <v>2.77452e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>1246.089</v>
       </c>
+      <c r="C19" t="n">
+        <v>1677.69205382667</v>
+      </c>
       <c r="D19" t="n">
         <v>2.78037e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>1225.326</v>
       </c>
+      <c r="C20" t="n">
+        <v>1662.145567905007</v>
+      </c>
       <c r="D20" t="n">
         <v>2.78435e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>1206.616</v>
       </c>
+      <c r="C21" t="n">
+        <v>1643.482729415482</v>
+      </c>
       <c r="D21" t="n">
         <v>2.7898e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>1200.128</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1633.987000610123</v>
       </c>
       <c r="D22" t="n">
         <v>2.79508e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>2260.513</v>
       </c>
+      <c r="C2" t="n">
+        <v>2817.925704685616</v>
+      </c>
       <c r="D2" t="n">
         <v>2.33552e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>1824.185</v>
       </c>
+      <c r="C3" t="n">
+        <v>2267.726490849258</v>
+      </c>
       <c r="D3" t="n">
         <v>2.57134e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>1734.85</v>
       </c>
+      <c r="C4" t="n">
+        <v>2166.205129657921</v>
+      </c>
       <c r="D4" t="n">
         <v>2.61433e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>1701.509</v>
       </c>
+      <c r="C5" t="n">
+        <v>2129.38513939821</v>
+      </c>
       <c r="D5" t="n">
         <v>2.62997e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>1666.333</v>
       </c>
+      <c r="C6" t="n">
+        <v>2099.045872079224</v>
+      </c>
       <c r="D6" t="n">
         <v>2.64377e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>1636.368</v>
       </c>
+      <c r="C7" t="n">
+        <v>2071.50507943784</v>
+      </c>
       <c r="D7" t="n">
         <v>2.65565e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>1616.489</v>
       </c>
+      <c r="C8" t="n">
+        <v>2049.383737797438</v>
+      </c>
       <c r="D8" t="n">
         <v>2.66743e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>1576.785</v>
       </c>
+      <c r="C9" t="n">
+        <v>2015.032427139511</v>
+      </c>
       <c r="D9" t="n">
         <v>2.68108e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>1556.787</v>
       </c>
+      <c r="C10" t="n">
+        <v>1994.727424438989</v>
+      </c>
       <c r="D10" t="n">
         <v>2.69206e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>1526.186</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1963.440411562988</v>
       </c>
       <c r="D11" t="n">
         <v>2.70435e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>1609.91</v>
       </c>
+      <c r="C2" t="n">
+        <v>2050.43948283109</v>
+      </c>
       <c r="D2" t="n">
         <v>2.70776e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>1533.943</v>
       </c>
+      <c r="C3" t="n">
+        <v>1957.161824224932</v>
+      </c>
       <c r="D3" t="n">
         <v>2.70426e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>1501.203</v>
       </c>
+      <c r="C4" t="n">
+        <v>1924.796641779799</v>
+      </c>
       <c r="D4" t="n">
         <v>2.71258e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>1470.704</v>
       </c>
+      <c r="C5" t="n">
+        <v>1896.900712036074</v>
+      </c>
       <c r="D5" t="n">
         <v>2.72158e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>1447.689</v>
       </c>
+      <c r="C6" t="n">
+        <v>1874.374467754752</v>
+      </c>
       <c r="D6" t="n">
         <v>2.73062e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>1420.083</v>
       </c>
+      <c r="C7" t="n">
+        <v>1849.852691953568</v>
+      </c>
       <c r="D7" t="n">
         <v>2.7394e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>1407.208</v>
       </c>
+      <c r="C8" t="n">
+        <v>1835.72893932643</v>
+      </c>
       <c r="D8" t="n">
         <v>2.75028e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>1387.607</v>
       </c>
+      <c r="C9" t="n">
+        <v>1813.460599256315</v>
+      </c>
       <c r="D9" t="n">
         <v>2.75623e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>1366.414</v>
       </c>
+      <c r="C10" t="n">
+        <v>1795.23975517223</v>
+      </c>
       <c r="D10" t="n">
         <v>2.76358e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>1347.876</v>
       </c>
+      <c r="C11" t="n">
+        <v>1774.975521704621</v>
+      </c>
       <c r="D11" t="n">
         <v>2.77004e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>1323.162</v>
       </c>
+      <c r="C12" t="n">
+        <v>1754.343389100499</v>
+      </c>
       <c r="D12" t="n">
         <v>2.77827e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>1305.796</v>
       </c>
+      <c r="C13" t="n">
+        <v>1736.602182211189</v>
+      </c>
       <c r="D13" t="n">
         <v>2.78304e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>1286.966</v>
       </c>
+      <c r="C14" t="n">
+        <v>1719.450077306784</v>
+      </c>
       <c r="D14" t="n">
         <v>2.78987e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>1274.237</v>
       </c>
+      <c r="C15" t="n">
+        <v>1707.511456789598</v>
+      </c>
       <c r="D15" t="n">
         <v>2.79545e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>1255.979</v>
       </c>
+      <c r="C16" t="n">
+        <v>1687.558421438096</v>
+      </c>
       <c r="D16" t="n">
         <v>2.80233e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>1236.098</v>
       </c>
+      <c r="C17" t="n">
+        <v>1670.375425036866</v>
+      </c>
       <c r="D17" t="n">
         <v>2.80835e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>1218.23</v>
       </c>
+      <c r="C18" t="n">
+        <v>1653.616600913153</v>
+      </c>
       <c r="D18" t="n">
         <v>2.81236e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>1200.111</v>
       </c>
+      <c r="C19" t="n">
+        <v>1632.960057407249</v>
+      </c>
       <c r="D19" t="n">
         <v>2.81805e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>1182.871</v>
       </c>
+      <c r="C20" t="n">
+        <v>1618.365625867356</v>
+      </c>
       <c r="D20" t="n">
         <v>2.82349e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>1166.748</v>
       </c>
+      <c r="C21" t="n">
+        <v>1602.758865858035</v>
+      </c>
       <c r="D21" t="n">
         <v>2.82974e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>1147.86</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1585.013543688154</v>
       </c>
       <c r="D22" t="n">
         <v>2.83504e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>2080.499</v>
       </c>
+      <c r="C2" t="n">
+        <v>2671.844294075562</v>
+      </c>
       <c r="D2" t="n">
         <v>2.42018e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>1752.981</v>
       </c>
+      <c r="C3" t="n">
+        <v>2251.733009204009</v>
+      </c>
       <c r="D3" t="n">
         <v>2.60505e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>1667.415</v>
       </c>
+      <c r="C4" t="n">
+        <v>2159.066167090395</v>
+      </c>
       <c r="D4" t="n">
         <v>2.63961e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>1631.705</v>
       </c>
+      <c r="C5" t="n">
+        <v>2122.236885460613</v>
+      </c>
       <c r="D5" t="n">
         <v>2.65618e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>1600.884</v>
       </c>
+      <c r="C6" t="n">
+        <v>2095.515842247793</v>
+      </c>
       <c r="D6" t="n">
         <v>2.66848e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>1560.339</v>
       </c>
+      <c r="C7" t="n">
+        <v>2058.758702827764</v>
+      </c>
       <c r="D7" t="n">
         <v>2.68399e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>1539.223</v>
       </c>
+      <c r="C8" t="n">
+        <v>2037.515834860949</v>
+      </c>
       <c r="D8" t="n">
         <v>2.69516e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>1505.867</v>
       </c>
+      <c r="C9" t="n">
+        <v>2007.208742633907</v>
+      </c>
       <c r="D9" t="n">
         <v>2.71144e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>1480.734</v>
       </c>
+      <c r="C10" t="n">
+        <v>1983.469722943864</v>
+      </c>
       <c r="D10" t="n">
         <v>2.72276e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>1463.063</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1963.548315061728</v>
       </c>
       <c r="D11" t="n">
         <v>2.73653e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>1641.585</v>
       </c>
+      <c r="C2" t="n">
+        <v>2109.825246182789</v>
+      </c>
       <c r="D2" t="n">
         <v>2.67715e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>1541.11</v>
       </c>
+      <c r="C3" t="n">
+        <v>1980.179204683424</v>
+      </c>
       <c r="D3" t="n">
         <v>2.70687e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>1509.271</v>
       </c>
+      <c r="C4" t="n">
+        <v>1955.448016017084</v>
+      </c>
       <c r="D4" t="n">
         <v>2.71843e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>1482.039</v>
       </c>
+      <c r="C5" t="n">
+        <v>1933.238527441983</v>
+      </c>
       <c r="D5" t="n">
         <v>2.72525e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>1458.855</v>
       </c>
+      <c r="C6" t="n">
+        <v>1915.159427429956</v>
+      </c>
       <c r="D6" t="n">
         <v>2.73475e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>1445.709</v>
       </c>
+      <c r="C7" t="n">
+        <v>1902.377474202877</v>
+      </c>
       <c r="D7" t="n">
         <v>2.74087e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>1426.926</v>
       </c>
+      <c r="C8" t="n">
+        <v>1881.38132175755</v>
+      </c>
       <c r="D8" t="n">
         <v>2.74862e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>1407.073</v>
       </c>
+      <c r="C9" t="n">
+        <v>1862.992165898949</v>
+      </c>
       <c r="D9" t="n">
         <v>2.75641e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>1388.039</v>
       </c>
+      <c r="C10" t="n">
+        <v>1845.220739450489</v>
+      </c>
       <c r="D10" t="n">
         <v>2.76416e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>1370.136</v>
       </c>
+      <c r="C11" t="n">
+        <v>1824.856579972031</v>
+      </c>
       <c r="D11" t="n">
         <v>2.76847e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>1347.418</v>
       </c>
+      <c r="C12" t="n">
+        <v>1802.115801761572</v>
+      </c>
       <c r="D12" t="n">
         <v>2.77809e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>1331.037</v>
       </c>
+      <c r="C13" t="n">
+        <v>1785.036959759623</v>
+      </c>
       <c r="D13" t="n">
         <v>2.78218e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>1308.014</v>
       </c>
+      <c r="C14" t="n">
+        <v>1762.603608455876</v>
+      </c>
       <c r="D14" t="n">
         <v>2.78952e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>1304.887</v>
       </c>
+      <c r="C15" t="n">
+        <v>1751.952203538874</v>
+      </c>
       <c r="D15" t="n">
         <v>2.79522e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>1276.011</v>
       </c>
+      <c r="C16" t="n">
+        <v>1726.789581511011</v>
+      </c>
       <c r="D16" t="n">
         <v>2.80144e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>1263.615</v>
       </c>
+      <c r="C17" t="n">
+        <v>1715.214797710403</v>
+      </c>
       <c r="D17" t="n">
         <v>2.80707e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>1253.506</v>
       </c>
+      <c r="C18" t="n">
+        <v>1708.109454342685</v>
+      </c>
       <c r="D18" t="n">
         <v>2.8138e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>1231.156</v>
       </c>
+      <c r="C19" t="n">
+        <v>1687.033824412345</v>
+      </c>
       <c r="D19" t="n">
         <v>2.81942e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>1212.164</v>
       </c>
+      <c r="C20" t="n">
+        <v>1664.07109894983</v>
+      </c>
       <c r="D20" t="n">
         <v>2.82641e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>1195.068</v>
       </c>
+      <c r="C21" t="n">
+        <v>1647.186222846969</v>
+      </c>
       <c r="D21" t="n">
         <v>2.83264e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>1179.113</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1634.216112632073</v>
       </c>
       <c r="D22" t="n">
         <v>2.83908e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>1458.226</v>
       </c>
+      <c r="C2" t="n">
+        <v>2099.300351889218</v>
+      </c>
       <c r="D2" t="n">
         <v>2.67718e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>1300.667</v>
       </c>
+      <c r="C3" t="n">
+        <v>1884.336018938228</v>
+      </c>
       <c r="D3" t="n">
         <v>2.72726e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>1261.579</v>
       </c>
+      <c r="C4" t="n">
+        <v>1839.079660424648</v>
+      </c>
       <c r="D4" t="n">
         <v>2.74296e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>1238.778</v>
       </c>
+      <c r="C5" t="n">
+        <v>1814.636973393718</v>
+      </c>
       <c r="D5" t="n">
         <v>2.75188e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>1211.349</v>
       </c>
+      <c r="C6" t="n">
+        <v>1794.443503119097</v>
+      </c>
       <c r="D6" t="n">
         <v>2.76046e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>1197.885</v>
       </c>
+      <c r="C7" t="n">
+        <v>1780.830079525871</v>
+      </c>
       <c r="D7" t="n">
         <v>2.76752e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>1176.457</v>
       </c>
+      <c r="C8" t="n">
+        <v>1758.906633415103</v>
+      </c>
       <c r="D8" t="n">
         <v>2.78237e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>1151.93</v>
       </c>
+      <c r="C9" t="n">
+        <v>1739.93632970659</v>
+      </c>
       <c r="D9" t="n">
         <v>2.79261e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>1126.673</v>
       </c>
+      <c r="C10" t="n">
+        <v>1724.666420304016</v>
+      </c>
       <c r="D10" t="n">
         <v>2.80209e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>1101.556</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1701.951978644532</v>
       </c>
       <c r="D11" t="n">
         <v>2.81368e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 33.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 33.xlsx
@@ -565,7 +565,7 @@
         <v>1702.875</v>
       </c>
       <c r="C2" t="n">
-        <v>2147.703941961174</v>
+        <v>760.2798982774809</v>
       </c>
       <c r="D2" t="n">
         <v>2.64227e-07</v>
@@ -598,16 +598,13 @@
         <v>-29859.92229424242</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.204039583916335e-11</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2390.985395897151</v>
+        <v>515.5947475129656</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000386e-08</v>
+        <v>1.08161962392795e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.81982275423088</v>
+        <v>0.9955483858372666</v>
       </c>
     </row>
     <row r="3">
@@ -618,7 +615,7 @@
         <v>1595.431</v>
       </c>
       <c r="C3" t="n">
-        <v>2034.573746936335</v>
+        <v>732.3842703171223</v>
       </c>
       <c r="D3" t="n">
         <v>2.65191e-07</v>
@@ -651,16 +648,13 @@
         <v>-24355.13519661768</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.172147360603292e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2302.662388551644</v>
+        <v>521.5701246650309</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000003237e-08</v>
+        <v>1.425212483700457e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8199731307578405</v>
+        <v>0.9838214974735541</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +665,7 @@
         <v>1554.83</v>
       </c>
       <c r="C4" t="n">
-        <v>1993.494989208164</v>
+        <v>720.8502577260859</v>
       </c>
       <c r="D4" t="n">
         <v>2.65466e-07</v>
@@ -704,16 +698,13 @@
         <v>-21874.97582028011</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.18651266872507e-12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2262.444813030469</v>
+        <v>522.999667999995</v>
       </c>
       <c r="AA4" t="n">
-        <v>1e-08</v>
+        <v>1.20614526020916e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8199645705086693</v>
+        <v>0.9913788416756338</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +715,7 @@
         <v>1525.224</v>
       </c>
       <c r="C5" t="n">
-        <v>1967.353731151327</v>
+        <v>711.5935956440798</v>
       </c>
       <c r="D5" t="n">
         <v>2.65669e-07</v>
@@ -757,16 +748,13 @@
         <v>-20819.54562883605</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.100008246601336e-13</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2231.191228183235</v>
+        <v>521.4515793812474</v>
       </c>
       <c r="AA5" t="n">
-        <v>1e-08</v>
+        <v>1.502406302464268e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8199906873213119</v>
+        <v>0.9807614625077435</v>
       </c>
     </row>
     <row r="6">
@@ -777,7 +765,7 @@
         <v>1499.3</v>
       </c>
       <c r="C6" t="n">
-        <v>1946.641241504192</v>
+        <v>703.374068247882</v>
       </c>
       <c r="D6" t="n">
         <v>2.65641e-07</v>
@@ -810,16 +798,13 @@
         <v>-19865.04181524135</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.14872799628043e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2202.656825986536</v>
+        <v>516.2452280967732</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000026e-08</v>
+        <v>1.140833646776233e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8200850499410226</v>
+        <v>0.9962136874687008</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +815,7 @@
         <v>1480.618</v>
       </c>
       <c r="C7" t="n">
-        <v>1925.927501267209</v>
+        <v>695.7866016926691</v>
       </c>
       <c r="D7" t="n">
         <v>2.65833e-07</v>
@@ -863,16 +848,13 @@
         <v>-19584.63542263712</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.892303492952694e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2174.075280317639</v>
+        <v>506.9682857066134</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000003e-08</v>
+        <v>1.044071044141361e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8202484572555447</v>
+        <v>0.999556878916963</v>
       </c>
     </row>
     <row r="8">
@@ -883,7 +865,7 @@
         <v>1447.972</v>
       </c>
       <c r="C8" t="n">
-        <v>1897.462823105808</v>
+        <v>1271.549795879638</v>
       </c>
       <c r="D8" t="n">
         <v>2.66245e-07</v>
@@ -916,16 +898,13 @@
         <v>-17700.28362139756</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.891435410634521e-11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2145.9636290176</v>
+        <v>2.251711846368785</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000007962e-08</v>
+        <v>2.639765937462106e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8204383417175178</v>
+        <v>0.8735278517121631</v>
       </c>
     </row>
     <row r="9">
@@ -936,7 +915,7 @@
         <v>1435.485</v>
       </c>
       <c r="C9" t="n">
-        <v>1882.879533269484</v>
+        <v>581.8336538297546</v>
       </c>
       <c r="D9" t="n">
         <v>2.66563e-07</v>
@@ -969,16 +948,13 @@
         <v>-17641.88651130295</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.926336666255582e-12</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2118.736673633471</v>
+        <v>721.0656301470798</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>1.615204196566546e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8206714947602654</v>
+        <v>0.8580600514967366</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +965,7 @@
         <v>1405.035</v>
       </c>
       <c r="C10" t="n">
-        <v>1854.805642539455</v>
+        <v>582.6066441891792</v>
       </c>
       <c r="D10" t="n">
         <v>2.66705e-07</v>
@@ -1022,16 +998,13 @@
         <v>-16575.32057465745</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.791494586579274e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2092.45788017693</v>
+        <v>609.9228065134964</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000061e-08</v>
+        <v>1.807805203430356e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8209176843098924</v>
+        <v>0.9915203294299775</v>
       </c>
     </row>
     <row r="11">
@@ -1042,7 +1015,7 @@
         <v>1386.906</v>
       </c>
       <c r="C11" t="n">
-        <v>1837.98101779564</v>
+        <v>583.8016828004877</v>
       </c>
       <c r="D11" t="n">
         <v>2.67083e-07</v>
@@ -1075,16 +1048,13 @@
         <v>-15976.27246472913</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.246897560617112e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2066.77760191502</v>
+        <v>610.0695327586088</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>1.669836855661879e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8211914455797964</v>
+        <v>0.993993409491474</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1211,7 @@
         <v>1676.785</v>
       </c>
       <c r="C2" t="n">
-        <v>2226.178872977625</v>
+        <v>737.5889807823363</v>
       </c>
       <c r="D2" t="n">
         <v>2.59517e-07</v>
@@ -1274,16 +1244,13 @@
         <v>-26059.5570109247</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.517162670059875e-12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2340.098654230078</v>
+        <v>512.0713185300581</v>
       </c>
       <c r="AA2" t="n">
-        <v>1e-08</v>
+        <v>1.46085193361506e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8216355947521953</v>
+        <v>0.9751497197012049</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1261,7 @@
         <v>1583.639</v>
       </c>
       <c r="C3" t="n">
-        <v>2112.788697144857</v>
+        <v>710.8639184077904</v>
       </c>
       <c r="D3" t="n">
         <v>2.63148e-07</v>
@@ -1327,16 +1294,13 @@
         <v>-24702.3958322783</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.223984938664334e-12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2250.548177932228</v>
+        <v>514.0078131132809</v>
       </c>
       <c r="AA3" t="n">
-        <v>1e-08</v>
+        <v>1.498539800362404e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8218353998585043</v>
+        <v>0.9818133904197985</v>
       </c>
     </row>
     <row r="4">
@@ -1347,7 +1311,7 @@
         <v>1534.87</v>
       </c>
       <c r="C4" t="n">
-        <v>2065.8435516544</v>
+        <v>699.3585615281283</v>
       </c>
       <c r="D4" t="n">
         <v>2.64489e-07</v>
@@ -1380,16 +1344,13 @@
         <v>-22137.28255878998</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.269634963428622e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2213.557889513751</v>
+        <v>538.2333344422985</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000042e-08</v>
+        <v>2.133859882601462e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.821907509895526</v>
+        <v>0.9586728402688873</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1361,7 @@
         <v>1514.008</v>
       </c>
       <c r="C5" t="n">
-        <v>2044.887980060815</v>
+        <v>691.4586171251755</v>
       </c>
       <c r="D5" t="n">
         <v>2.65485e-07</v>
@@ -1433,16 +1394,13 @@
         <v>-21825.95631522888</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.985164566310267e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2185.307694417118</v>
+        <v>545.9116586720201</v>
       </c>
       <c r="AA5" t="n">
-        <v>1e-08</v>
+        <v>2.435960992293044e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8220211664326268</v>
+        <v>0.9517962972949784</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1411,7 @@
         <v>1490.245</v>
       </c>
       <c r="C6" t="n">
-        <v>2021.708966634912</v>
+        <v>683.7138740083694</v>
       </c>
       <c r="D6" t="n">
         <v>2.66196e-07</v>
@@ -1486,16 +1444,13 @@
         <v>-20844.75145816288</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.360509578287997e-13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2159.086460870488</v>
+        <v>548.9230735331963</v>
       </c>
       <c r="AA6" t="n">
-        <v>1e-08</v>
+        <v>2.681816727850399e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8221677501227233</v>
+        <v>0.9471118395783698</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1461,7 @@
         <v>1472.704</v>
       </c>
       <c r="C7" t="n">
-        <v>2005.084484741772</v>
+        <v>676.4955283360573</v>
       </c>
       <c r="D7" t="n">
         <v>2.67142e-07</v>
@@ -1539,16 +1494,13 @@
         <v>-21002.29092656574</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.727758901970407e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2132.533271332957</v>
+        <v>514.1492171069904</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000028e-08</v>
+        <v>1.404657255613209e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.822371698426117</v>
+        <v>0.9860528255889521</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1511,7 @@
         <v>1439.099</v>
       </c>
       <c r="C8" t="n">
-        <v>1977.325832680681</v>
+        <v>669.4890158208052</v>
       </c>
       <c r="D8" t="n">
         <v>2.67993e-07</v>
@@ -1592,16 +1544,13 @@
         <v>-18847.54439819363</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.244666819998783e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2106.050594134085</v>
+        <v>506.4795716996347</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000003e-08</v>
+        <v>1.148962988630253e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8225854250764777</v>
+        <v>0.9978876060128505</v>
       </c>
     </row>
     <row r="9">
@@ -1612,7 +1561,7 @@
         <v>1421.501</v>
       </c>
       <c r="C9" t="n">
-        <v>1960.68107682527</v>
+        <v>662.7014128239947</v>
       </c>
       <c r="D9" t="n">
         <v>2.68604e-07</v>
@@ -1645,16 +1594,13 @@
         <v>-19448.94091516426</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.75650277969944e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2080.535938651296</v>
+        <v>514.0923263701249</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>1.263353415349998e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8228326258450532</v>
+        <v>0.9976837339201159</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1611,7 @@
         <v>1395.551</v>
       </c>
       <c r="C10" t="n">
-        <v>1937.424287375647</v>
+        <v>655.9574572977718</v>
       </c>
       <c r="D10" t="n">
         <v>2.69371e-07</v>
@@ -1698,16 +1644,13 @@
         <v>-17551.28809108364</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.79939967823599e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2055.775233809128</v>
+        <v>512.3224052289938</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000003671e-08</v>
+        <v>1.575721800274374e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8231242008609685</v>
+        <v>0.9828343410325663</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1661,7 @@
         <v>1387.541</v>
       </c>
       <c r="C11" t="n">
-        <v>1925.152072152474</v>
+        <v>650.1349309008546</v>
       </c>
       <c r="D11" t="n">
         <v>2.70096e-07</v>
@@ -1751,16 +1694,13 @@
         <v>-18067.91776146764</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.773633489941073e-13</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2030.944370319675</v>
+        <v>509.5091008701351</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>1.637543343414545e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8234233849416606</v>
+        <v>0.9799108914673442</v>
       </c>
     </row>
     <row r="12">
@@ -1771,7 +1711,7 @@
         <v>1369.782</v>
       </c>
       <c r="C12" t="n">
-        <v>1906.243953772524</v>
+        <v>568.1865524083677</v>
       </c>
       <c r="D12" t="n">
         <v>2.70871e-07</v>
@@ -1804,16 +1744,13 @@
         <v>-17005.34640597626</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.235881936574009e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2006.715501291098</v>
+        <v>573.0229916965496</v>
       </c>
       <c r="AA12" t="n">
-        <v>1e-08</v>
+        <v>1.396530586404284e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8237496713461573</v>
+        <v>0.9993013979755521</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1761,7 @@
         <v>1349.203</v>
       </c>
       <c r="C13" t="n">
-        <v>1884.48404618861</v>
+        <v>27.11310003471999</v>
       </c>
       <c r="D13" t="n">
         <v>2.71297e-07</v>
@@ -1857,10 +1794,7 @@
         <v>-16259.35119934392</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.401181279531593e-08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1983.467222920582</v>
+        <v>1888.368685412538</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000007e-08</v>
@@ -1877,7 +1811,7 @@
         <v>1337.807</v>
       </c>
       <c r="C14" t="n">
-        <v>1872.736410747223</v>
+        <v>569.3554587940013</v>
       </c>
       <c r="D14" t="n">
         <v>2.7203e-07</v>
@@ -1910,16 +1844,13 @@
         <v>-15627.05089699396</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.139214244621695e-08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1960.761275159777</v>
+        <v>574.2556603352856</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000013e-08</v>
+        <v>2.021449912606234e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8244141683169292</v>
+        <v>0.9827808210550583</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1861,7 @@
         <v>1312.425</v>
       </c>
       <c r="C15" t="n">
-        <v>1849.585881106584</v>
+        <v>570.6379243603055</v>
       </c>
       <c r="D15" t="n">
         <v>2.72673e-07</v>
@@ -1963,16 +1894,13 @@
         <v>-14130.27782756219</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.634382466793408e-12</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1938.452634928891</v>
+        <v>595.2136212278579</v>
       </c>
       <c r="AA15" t="n">
-        <v>1e-08</v>
+        <v>3.693048754885717e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8247686032601121</v>
+        <v>0.9440230146449106</v>
       </c>
     </row>
     <row r="16">
@@ -1983,7 +1911,7 @@
         <v>1300.218</v>
       </c>
       <c r="C16" t="n">
-        <v>1838.347656313046</v>
+        <v>571.9225671675172</v>
       </c>
       <c r="D16" t="n">
         <v>2.73212e-07</v>
@@ -2016,16 +1944,13 @@
         <v>-12626.27035864673</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.324614760934189e-12</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1916.914366877109</v>
+        <v>541.5496329865923</v>
       </c>
       <c r="AA16" t="n">
-        <v>1e-08</v>
+        <v>1.470013322142736e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8251218515212776</v>
+        <v>0.997306350963909</v>
       </c>
     </row>
     <row r="17">
@@ -2036,7 +1961,7 @@
         <v>1274.406</v>
       </c>
       <c r="C17" t="n">
-        <v>1815.279501449214</v>
+        <v>570.3561094285585</v>
       </c>
       <c r="D17" t="n">
         <v>2.73692e-07</v>
@@ -2069,16 +1994,13 @@
         <v>-12538.88526326918</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.128613551560124e-12</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1895.969017966253</v>
+        <v>529.8195514147583</v>
       </c>
       <c r="AA17" t="n">
-        <v>1e-08</v>
+        <v>1.365661819805085e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8254789231270092</v>
+        <v>0.9999435193453955</v>
       </c>
     </row>
     <row r="18">
@@ -2089,7 +2011,7 @@
         <v>1264.397</v>
       </c>
       <c r="C18" t="n">
-        <v>1803.136923461276</v>
+        <v>570.1294284270039</v>
       </c>
       <c r="D18" t="n">
         <v>2.74213e-07</v>
@@ -2122,16 +2044,13 @@
         <v>-11298.30669920068</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.504780107670999e-09</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1874.836665168918</v>
+        <v>513.5211114771707</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000000003e-08</v>
+        <v>1.30672528300397e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8258447851166493</v>
+        <v>0.9999212070998186</v>
       </c>
     </row>
     <row r="19">
@@ -2142,7 +2061,7 @@
         <v>1246.777</v>
       </c>
       <c r="C19" t="n">
-        <v>1789.133361620432</v>
+        <v>571.7191830226116</v>
       </c>
       <c r="D19" t="n">
         <v>2.74817e-07</v>
@@ -2175,16 +2094,13 @@
         <v>-9418.730443240538</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.961926791858e-10</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1854.21653397075</v>
+        <v>518.0625573753692</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.472729097717229e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8262054678320458</v>
+        <v>0.9988230071506793</v>
       </c>
     </row>
     <row r="20">
@@ -2195,7 +2111,7 @@
         <v>1235.158</v>
       </c>
       <c r="C20" t="n">
-        <v>1773.711561880646</v>
+        <v>569.3477712412898</v>
       </c>
       <c r="D20" t="n">
         <v>2.7531e-07</v>
@@ -2228,16 +2144,13 @@
         <v>-7937.577567431398</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.119806457727727e-07</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1833.870774858342</v>
+        <v>521.3459243066038</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000314e-08</v>
+        <v>1.653283417251928e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8265912400963579</v>
+        <v>0.9898196297864964</v>
       </c>
     </row>
     <row r="21">
@@ -2248,7 +2161,7 @@
         <v>1214.839</v>
       </c>
       <c r="C21" t="n">
-        <v>1759.943161463561</v>
+        <v>571.6328187109239</v>
       </c>
       <c r="D21" t="n">
         <v>2.75968e-07</v>
@@ -2281,16 +2194,13 @@
         <v>-7380.131259702622</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.62179654675983e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1813.341687290567</v>
+        <v>503.2325114898468</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000001505e-08</v>
+        <v>1.880121349117043e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8269705879571928</v>
+        <v>0.9818528919559756</v>
       </c>
     </row>
     <row r="22">
@@ -2301,7 +2211,7 @@
         <v>1192.154</v>
       </c>
       <c r="C22" t="n">
-        <v>1735.460339037389</v>
+        <v>567.4569045703373</v>
       </c>
       <c r="D22" t="n">
         <v>2.7627e-07</v>
@@ -2334,16 +2244,13 @@
         <v>-7900.013300919956</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.991918499063288e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1793.115291214006</v>
+        <v>486.2705577808699</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000005826e-08</v>
+        <v>1.466383358265786e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8273530917654275</v>
+        <v>0.9984604878133226</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2407,7 @@
         <v>1643.652</v>
       </c>
       <c r="C2" t="n">
-        <v>2091.404410564804</v>
+        <v>737.6644603318263</v>
       </c>
       <c r="D2" t="n">
         <v>2.62418e-07</v>
@@ -2533,16 +2440,13 @@
         <v>-26065.30633022426</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.280095204512863e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2317.987113242924</v>
+        <v>512.9128113328031</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000067e-08</v>
+        <v>1.737557549501264e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8219186706503709</v>
+        <v>0.964280984585096</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2457,7 @@
         <v>1538.112</v>
       </c>
       <c r="C3" t="n">
-        <v>1967.31306644053</v>
+        <v>709.1304659605833</v>
       </c>
       <c r="D3" t="n">
         <v>2.6527e-07</v>
@@ -2586,16 +2490,13 @@
         <v>-23216.30797720005</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.95725077814474e-12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2218.99336004235</v>
+        <v>519.7648488879063</v>
       </c>
       <c r="AA3" t="n">
-        <v>1e-08</v>
+        <v>2.019612000999649e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8221535652619504</v>
+        <v>0.960334117568152</v>
       </c>
     </row>
     <row r="4">
@@ -2606,7 +2507,7 @@
         <v>1504.796</v>
       </c>
       <c r="C4" t="n">
-        <v>1930.61715316485</v>
+        <v>698.8922099431682</v>
       </c>
       <c r="D4" t="n">
         <v>2.66039e-07</v>
@@ -2639,16 +2540,13 @@
         <v>-21325.90088680392</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.319554814802288e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2182.408812275879</v>
+        <v>514.0341649661516</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000001162e-08</v>
+        <v>1.929697103225654e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8222091634447025</v>
+        <v>0.9642199651530828</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2557,7 @@
         <v>1474.565</v>
       </c>
       <c r="C5" t="n">
-        <v>1903.994522340445</v>
+        <v>691.8081257393231</v>
       </c>
       <c r="D5" t="n">
         <v>2.66399e-07</v>
@@ -2692,16 +2590,13 @@
         <v>-19260.08818227364</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.974436311851379e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2156.458503682248</v>
+        <v>488.8132562750026</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000403e-08</v>
+        <v>1.171268448436032e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8222789341415548</v>
+        <v>0.9992630709368259</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2607,7 @@
         <v>1456.875</v>
       </c>
       <c r="C6" t="n">
-        <v>1885.252497554885</v>
+        <v>1456.875</v>
       </c>
       <c r="D6" t="n">
         <v>2.66739e-07</v>
@@ -2744,11 +2639,10 @@
       <c r="X6" t="n">
         <v>-18782.08376467229</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.036806407992319e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2132.105885280056</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000003822e-08</v>
@@ -2765,7 +2659,7 @@
         <v>1436.339</v>
       </c>
       <c r="C7" t="n">
-        <v>1866.651845284745</v>
+        <v>678.0716912853906</v>
       </c>
       <c r="D7" t="n">
         <v>2.67021e-07</v>
@@ -2798,16 +2692,13 @@
         <v>-17512.34656175634</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.275280223422031e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2107.64763762722</v>
+        <v>505.5585835742194</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000954e-08</v>
+        <v>1.334472046400304e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8226179925527323</v>
+        <v>0.9911725972967493</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2709,7 @@
         <v>1419.34</v>
       </c>
       <c r="C8" t="n">
-        <v>1848.634761008779</v>
+        <v>671.888674143854</v>
       </c>
       <c r="D8" t="n">
         <v>2.67316e-07</v>
@@ -2851,16 +2742,13 @@
         <v>-17069.87532735561</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.584913484726683e-13</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2082.236589874</v>
+        <v>493.8106343250532</v>
       </c>
       <c r="AA8" t="n">
-        <v>1e-08</v>
+        <v>1.195348047992315e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.822864831062158</v>
+        <v>0.9970244036019483</v>
       </c>
     </row>
     <row r="9">
@@ -2871,7 +2759,7 @@
         <v>1384.283</v>
       </c>
       <c r="C9" t="n">
-        <v>1819.614680105183</v>
+        <v>567.5395880678814</v>
       </c>
       <c r="D9" t="n">
         <v>2.67727e-07</v>
@@ -2904,16 +2792,13 @@
         <v>-15432.59836525563</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.075103827481586e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2056.856670172265</v>
+        <v>607.8712737887844</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000001008e-08</v>
+        <v>1.618964049043856e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8231360229418946</v>
+        <v>0.999193131779041</v>
       </c>
     </row>
     <row r="10">
@@ -2924,7 +2809,7 @@
         <v>1368.206</v>
       </c>
       <c r="C10" t="n">
-        <v>1803.709941023973</v>
+        <v>568.5714402200288</v>
       </c>
       <c r="D10" t="n">
         <v>2.68281e-07</v>
@@ -2957,16 +2842,13 @@
         <v>-15040.77787025728</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.080420979594384e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2032.25573188414</v>
+        <v>602.2687452513801</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.00000000000003e-08</v>
+        <v>2.256201267222367e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.823439546616572</v>
+        <v>0.9796481033239328</v>
       </c>
     </row>
     <row r="11">
@@ -2977,7 +2859,7 @@
         <v>1355.843</v>
       </c>
       <c r="C11" t="n">
-        <v>1785.714396081117</v>
+        <v>568.203860222639</v>
       </c>
       <c r="D11" t="n">
         <v>2.68569e-07</v>
@@ -3010,16 +2892,13 @@
         <v>-15376.03455005842</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.373398823314694e-12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2008.241206799612</v>
+        <v>597.8017168107122</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>2.278927377469547e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.823755846138125</v>
+        <v>0.9756697894178935</v>
       </c>
     </row>
     <row r="12">
@@ -3030,7 +2909,7 @@
         <v>1336.551</v>
       </c>
       <c r="C12" t="n">
-        <v>1765.302482505542</v>
+        <v>568.5822598392784</v>
       </c>
       <c r="D12" t="n">
         <v>2.69017e-07</v>
@@ -3063,16 +2942,13 @@
         <v>-13960.51888178542</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.893378595722602e-12</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1984.466328154522</v>
+        <v>676.1030098163598</v>
       </c>
       <c r="AA12" t="n">
-        <v>1e-08</v>
+        <v>1.591511635624069e-08</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8240940037430385</v>
+        <v>0.8575543393208211</v>
       </c>
     </row>
     <row r="13">
@@ -3083,7 +2959,7 @@
         <v>1316.726</v>
       </c>
       <c r="C13" t="n">
-        <v>1748.482881939796</v>
+        <v>571.0678159540887</v>
       </c>
       <c r="D13" t="n">
         <v>2.69528e-07</v>
@@ -3116,16 +2992,13 @@
         <v>-12920.97525885741</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.110579714385463e-09</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1961.263994443591</v>
+        <v>550.0313063818616</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000012e-08</v>
+        <v>1.506818423233809e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.824439880056978</v>
+        <v>0.9997032910101163</v>
       </c>
     </row>
     <row r="14">
@@ -3136,7 +3009,7 @@
         <v>1292.945</v>
       </c>
       <c r="C14" t="n">
-        <v>1728.205893254752</v>
+        <v>572.5224642645539</v>
       </c>
       <c r="D14" t="n">
         <v>2.69888e-07</v>
@@ -3169,16 +3042,13 @@
         <v>-12542.35796933517</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.002837192826697e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1938.507873288195</v>
+        <v>586.2352441897632</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>3.739449319365083e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8247961509654098</v>
+        <v>0.9425027216342136</v>
       </c>
     </row>
     <row r="15">
@@ -3189,7 +3059,7 @@
         <v>1286.538</v>
       </c>
       <c r="C15" t="n">
-        <v>1717.336519238626</v>
+        <v>570.3607433166428</v>
       </c>
       <c r="D15" t="n">
         <v>2.70251e-07</v>
@@ -3222,16 +3092,13 @@
         <v>-11738.95732576838</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.850922014780705e-08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1916.077332681858</v>
+        <v>546.6844978206311</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000000009e-08</v>
+        <v>1.566196316592697e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8251521473337728</v>
+        <v>0.998946433878418</v>
       </c>
     </row>
     <row r="16">
@@ -3242,7 +3109,7 @@
         <v>1264.156</v>
       </c>
       <c r="C16" t="n">
-        <v>1698.756847496746</v>
+        <v>573.3226134191332</v>
       </c>
       <c r="D16" t="n">
         <v>2.70732e-07</v>
@@ -3275,16 +3142,13 @@
         <v>-11227.0086366115</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.432620631498664e-09</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1894.06110208856</v>
+        <v>528.6336794091187</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000002523e-08</v>
+        <v>1.456587511495657e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8255125344964727</v>
+        <v>0.9997113520822101</v>
       </c>
     </row>
     <row r="17">
@@ -3295,7 +3159,7 @@
         <v>1243.506</v>
       </c>
       <c r="C17" t="n">
-        <v>1678.371641483611</v>
+        <v>573.1673194656971</v>
       </c>
       <c r="D17" t="n">
         <v>2.71091e-07</v>
@@ -3328,16 +3192,13 @@
         <v>-11077.09485966097</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.853713705324117e-08</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1872.683521897972</v>
+        <v>526.6206445709232</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000131e-08</v>
+        <v>1.877016727287183e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8258785088841245</v>
+        <v>0.9840368917524925</v>
       </c>
     </row>
     <row r="18">
@@ -3348,7 +3209,7 @@
         <v>1222.46</v>
       </c>
       <c r="C18" t="n">
-        <v>1660.63406828308</v>
+        <v>572.4575088002034</v>
       </c>
       <c r="D18" t="n">
         <v>2.71498e-07</v>
@@ -3381,16 +3242,13 @@
         <v>-9920.344163946565</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.070886380029249e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1851.661623058608</v>
+        <v>513.4103245075598</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000000128e-08</v>
+        <v>1.829887074799924e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8262411842592029</v>
+        <v>0.9825006478262703</v>
       </c>
     </row>
     <row r="19">
@@ -3401,7 +3259,7 @@
         <v>1214.631</v>
       </c>
       <c r="C19" t="n">
-        <v>1649.259854298811</v>
+        <v>573.6446405767715</v>
       </c>
       <c r="D19" t="n">
         <v>2.71864e-07</v>
@@ -3434,16 +3292,13 @@
         <v>-8122.600467169436</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.113456246604454e-09</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1831.170759546947</v>
+        <v>490.3786094642695</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000000915e-08</v>
+        <v>1.376710088496956e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8265940936078365</v>
+        <v>0.9990090541190157</v>
       </c>
     </row>
     <row r="20">
@@ -3454,7 +3309,7 @@
         <v>1190.607</v>
       </c>
       <c r="C20" t="n">
-        <v>1628.872371835343</v>
+        <v>572.1343743985688</v>
       </c>
       <c r="D20" t="n">
         <v>2.72255e-07</v>
@@ -3487,16 +3342,13 @@
         <v>-8055.101954908589</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.263184852026903e-09</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1810.825821371916</v>
+        <v>498.4804292069855</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000006e-08</v>
+        <v>1.876200276428456e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8269723034584328</v>
+        <v>0.9815913822639168</v>
       </c>
     </row>
     <row r="21">
@@ -3507,7 +3359,7 @@
         <v>1178.969</v>
       </c>
       <c r="C21" t="n">
-        <v>1617.392580275306</v>
+        <v>574.3422870028035</v>
       </c>
       <c r="D21" t="n">
         <v>2.72595e-07</v>
@@ -3540,16 +3392,13 @@
         <v>-6998.014253918594</v>
       </c>
       <c r="Y21" t="n">
-        <v>7.600141770234294e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1790.89786862746</v>
+        <v>476.2018866365405</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000000504e-08</v>
+        <v>1.497574260588324e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8273353370494128</v>
+        <v>0.9924165740679912</v>
       </c>
     </row>
     <row r="22">
@@ -3560,7 +3409,7 @@
         <v>1166.267</v>
       </c>
       <c r="C22" t="n">
-        <v>1600.633082554917</v>
+        <v>573.5527954478102</v>
       </c>
       <c r="D22" t="n">
         <v>2.73001e-07</v>
@@ -3593,16 +3442,13 @@
         <v>-5270.136166751174</v>
       </c>
       <c r="Y22" t="n">
-        <v>9.852978614820137e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1771.232181134933</v>
+        <v>458.5607670871926</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000012479e-08</v>
+        <v>1.387365111281022e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8277055231048595</v>
+        <v>0.9973096251568914</v>
       </c>
     </row>
   </sheetData>
@@ -3759,7 +3605,7 @@
         <v>2064.958</v>
       </c>
       <c r="C2" t="n">
-        <v>2522.300651127119</v>
+        <v>22026.79445072826</v>
       </c>
       <c r="D2" t="n">
         <v>2.47098e-07</v>
@@ -3792,10 +3638,7 @@
         <v>-26749.09270856584</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.382119852803023e-14</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2762.790328834013</v>
+        <v>-19128.14014461135</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -3812,7 +3655,7 @@
         <v>1826.03</v>
       </c>
       <c r="C3" t="n">
-        <v>2238.671427085753</v>
+        <v>811.0909119238364</v>
       </c>
       <c r="D3" t="n">
         <v>2.59225e-07</v>
@@ -3845,16 +3688,13 @@
         <v>-27066.49417195981</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.811649962108427e-12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2539.555963231845</v>
+        <v>485.5940329129681</v>
       </c>
       <c r="AA3" t="n">
-        <v>1e-08</v>
+        <v>9.773377108767012e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8208648474971949</v>
+        <v>0.9974111048413052</v>
       </c>
     </row>
     <row r="4">
@@ -3865,7 +3705,7 @@
         <v>1762.934</v>
       </c>
       <c r="C4" t="n">
-        <v>2169.310274572266</v>
+        <v>787.6566325791899</v>
       </c>
       <c r="D4" t="n">
         <v>2.61657e-07</v>
@@ -3898,16 +3738,13 @@
         <v>-24587.76846220544</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.715798711589326e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2473.256688502569</v>
+        <v>493.9405845982475</v>
       </c>
       <c r="AA4" t="n">
-        <v>1e-08</v>
+        <v>1.003232359746219e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8210685047357984</v>
+        <v>0.998610180120641</v>
       </c>
     </row>
     <row r="5">
@@ -3918,7 +3755,7 @@
         <v>1736.608</v>
       </c>
       <c r="C5" t="n">
-        <v>2138.700858034375</v>
+        <v>771.9250025112037</v>
       </c>
       <c r="D5" t="n">
         <v>2.62951e-07</v>
@@ -3951,16 +3788,13 @@
         <v>-22734.58597698457</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.327850201614981e-11</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2431.40922110609</v>
+        <v>493.1312743048524</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.00000000019688e-08</v>
+        <v>9.967603239769468e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8211823698758364</v>
+        <v>0.9995872206862177</v>
       </c>
     </row>
     <row r="6">
@@ -3971,7 +3805,7 @@
         <v>1687.32</v>
       </c>
       <c r="C6" t="n">
-        <v>2099.513952056333</v>
+        <v>758.9060321573319</v>
       </c>
       <c r="D6" t="n">
         <v>2.64183e-07</v>
@@ -4004,16 +3838,13 @@
         <v>-18601.30345305698</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.873416580058254e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2393.262113320538</v>
+        <v>505.8417558635625</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000241e-08</v>
+        <v>1.081025431941646e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8213723981014407</v>
+        <v>0.9963697394661319</v>
       </c>
     </row>
     <row r="7">
@@ -4024,7 +3855,7 @@
         <v>1665.352</v>
       </c>
       <c r="C7" t="n">
-        <v>2074.796833415422</v>
+        <v>746.718252895092</v>
       </c>
       <c r="D7" t="n">
         <v>2.65391e-07</v>
@@ -4057,16 +3888,13 @@
         <v>-16492.84802676491</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.961029159219708e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2356.403134490525</v>
+        <v>509.1870496231864</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000014953e-08</v>
+        <v>1.077580287171519e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8216248132197638</v>
+        <v>0.9970768570385079</v>
       </c>
     </row>
     <row r="8">
@@ -4077,7 +3905,7 @@
         <v>1628.198</v>
       </c>
       <c r="C8" t="n">
-        <v>2042.621561436311</v>
+        <v>735.422432374713</v>
       </c>
       <c r="D8" t="n">
         <v>2.66435e-07</v>
@@ -4110,16 +3938,13 @@
         <v>-15867.96524100771</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.657881295270694e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2320.550811716739</v>
+        <v>504.6927740474634</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000001489e-08</v>
+        <v>1.298124517404256e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.82188949392447</v>
+        <v>0.9858038895747683</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +3955,7 @@
         <v>1598.827</v>
       </c>
       <c r="C9" t="n">
-        <v>2013.796845888897</v>
+        <v>723.7071310885906</v>
       </c>
       <c r="D9" t="n">
         <v>2.67776e-07</v>
@@ -4163,16 +3988,13 @@
         <v>-13392.60553694756</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.090463821237727e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2285.336101852824</v>
+        <v>497.0005666737442</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>1.079488010219788e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8221916440689659</v>
+        <v>0.9972695766960429</v>
       </c>
     </row>
     <row r="10">
@@ -4183,7 +4005,7 @@
         <v>1569.12</v>
       </c>
       <c r="C10" t="n">
-        <v>1986.713228762256</v>
+        <v>713.6526128508317</v>
       </c>
       <c r="D10" t="n">
         <v>2.68876e-07</v>
@@ -4216,16 +4038,13 @@
         <v>-12272.7489078232</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.07705365690651e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2250.767494666186</v>
+        <v>489.8655583078536</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000053e-08</v>
+        <v>1.039585669587431e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8225428378599089</v>
+        <v>0.9980134251598402</v>
       </c>
     </row>
     <row r="11">
@@ -4236,7 +4055,7 @@
         <v>1543.351</v>
       </c>
       <c r="C11" t="n">
-        <v>1961.255725124438</v>
+        <v>703.5587702992591</v>
       </c>
       <c r="D11" t="n">
         <v>2.69876e-07</v>
@@ -4269,16 +4088,13 @@
         <v>-10794.5618610638</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.047978207424955e-12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2218.54949805969</v>
+        <v>504.7542339735645</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>1.631267231423093e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8228636931858677</v>
+        <v>0.9750586519256509</v>
       </c>
     </row>
   </sheetData>
@@ -4435,7 +4251,7 @@
         <v>1653.006</v>
       </c>
       <c r="C2" t="n">
-        <v>2171.528545421851</v>
+        <v>731.2196708298954</v>
       </c>
       <c r="D2" t="n">
         <v>2.65784e-07</v>
@@ -4468,16 +4284,13 @@
         <v>-26604.87470843148</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.459750480210157e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2301.280264219839</v>
+        <v>478.5097121907385</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.00000000000002e-08</v>
+        <v>9.966462337613977e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8232333125127144</v>
+        <v>0.9984182388299669</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4301,7 @@
         <v>1560.377</v>
       </c>
       <c r="C3" t="n">
-        <v>1984.619477324907</v>
+        <v>714.843365029869</v>
       </c>
       <c r="D3" t="n">
         <v>2.68056e-07</v>
@@ -4521,16 +4334,13 @@
         <v>-23930.41968659493</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.397427979873818e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2235.785445240768</v>
+        <v>500.2279495200845</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000024e-08</v>
+        <v>1.568945436530292e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8222037681080281</v>
+        <v>0.9765105307121534</v>
       </c>
     </row>
     <row r="4">
@@ -4541,7 +4351,7 @@
         <v>1512.67</v>
       </c>
       <c r="C4" t="n">
-        <v>1940.918155614015</v>
+        <v>704.2576050193455</v>
       </c>
       <c r="D4" t="n">
         <v>2.69365e-07</v>
@@ -4574,16 +4384,13 @@
         <v>-20799.78435183375</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.973598942241607e-12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2200.995743445253</v>
+        <v>510.8012799398849</v>
       </c>
       <c r="AA4" t="n">
-        <v>1e-08</v>
+        <v>1.516152876542446e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.822051624670001</v>
+        <v>0.978996983970074</v>
       </c>
     </row>
     <row r="5">
@@ -4594,7 +4401,7 @@
         <v>1497.537</v>
       </c>
       <c r="C5" t="n">
-        <v>1921.773307914347</v>
+        <v>696.8292657922151</v>
       </c>
       <c r="D5" t="n">
         <v>2.70344e-07</v>
@@ -4627,16 +4434,13 @@
         <v>-20488.69997991271</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.944714651105882e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2174.548673782294</v>
+        <v>498.1853724336659</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000003598e-08</v>
+        <v>1.136707882232196e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8220916949254755</v>
+        <v>0.9964182325126113</v>
       </c>
     </row>
     <row r="6">
@@ -4647,7 +4451,7 @@
         <v>1470.086</v>
       </c>
       <c r="C6" t="n">
-        <v>1899.835777132294</v>
+        <v>690.2740386775159</v>
       </c>
       <c r="D6" t="n">
         <v>2.71011e-07</v>
@@ -4680,16 +4484,13 @@
         <v>-19278.11534444883</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.357967015642599e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2150.073866540657</v>
+        <v>491.3523874925912</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000001432e-08</v>
+        <v>1.10124815422204e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8221880205424738</v>
+        <v>0.9987914423077456</v>
       </c>
     </row>
     <row r="7">
@@ -4700,7 +4501,7 @@
         <v>1454.206</v>
       </c>
       <c r="C7" t="n">
-        <v>1881.928038377901</v>
+        <v>683.0411064739619</v>
       </c>
       <c r="D7" t="n">
         <v>2.71684e-07</v>
@@ -4733,16 +4534,13 @@
         <v>-18801.33133444286</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.147136252978873e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2125.749199236592</v>
+        <v>507.2105229732544</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000018e-08</v>
+        <v>1.609346521914423e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8223490635523646</v>
+        <v>0.9774573903081472</v>
       </c>
     </row>
     <row r="8">
@@ -4753,7 +4551,7 @@
         <v>1434.165</v>
       </c>
       <c r="C8" t="n">
-        <v>1864.141521129716</v>
+        <v>676.8971445073598</v>
       </c>
       <c r="D8" t="n">
         <v>2.72394e-07</v>
@@ -4786,16 +4584,13 @@
         <v>-17967.85918710846</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.343226854772491e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2101.511587230581</v>
+        <v>499.8304823433683</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000676e-08</v>
+        <v>1.558710947125425e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8225627796279517</v>
+        <v>0.9806983692530957</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4601,7 @@
         <v>1414.712</v>
       </c>
       <c r="C9" t="n">
-        <v>1844.192554933649</v>
+        <v>670.9440294061959</v>
       </c>
       <c r="D9" t="n">
         <v>2.73011e-07</v>
@@ -4839,16 +4634,13 @@
         <v>-17097.27075471849</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.897653207837191e-15</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2077.385943568945</v>
+        <v>484.296637151242</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>1.198894705884894e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8228046894797199</v>
+        <v>0.9993084276002098</v>
       </c>
     </row>
     <row r="10">
@@ -4859,7 +4651,7 @@
         <v>1393.566</v>
       </c>
       <c r="C10" t="n">
-        <v>1824.613600836207</v>
+        <v>568.2903058199626</v>
       </c>
       <c r="D10" t="n">
         <v>2.738e-07</v>
@@ -4892,16 +4684,13 @@
         <v>-14856.2406325536</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.432346286854933e-11</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2054.491693778788</v>
+        <v>629.8222028455875</v>
       </c>
       <c r="AA10" t="n">
-        <v>1e-08</v>
+        <v>2.76654495293826e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8230699406618915</v>
+        <v>0.9637402819781454</v>
       </c>
     </row>
     <row r="11">
@@ -4912,7 +4701,7 @@
         <v>1372.689</v>
       </c>
       <c r="C11" t="n">
-        <v>1803.282789824251</v>
+        <v>569.6019779558042</v>
       </c>
       <c r="D11" t="n">
         <v>2.73995e-07</v>
@@ -4945,16 +4734,13 @@
         <v>-15261.00259271918</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.661103947393544e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2031.761843559136</v>
+        <v>691.544908870495</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.00000000000002e-08</v>
+        <v>1.67159302485642e-08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8233651418284813</v>
+        <v>0.8579785448078684</v>
       </c>
     </row>
     <row r="12">
@@ -4965,7 +4751,7 @@
         <v>1352.863</v>
       </c>
       <c r="C12" t="n">
-        <v>1783.123078108059</v>
+        <v>568.2583331981964</v>
       </c>
       <c r="D12" t="n">
         <v>2.74768e-07</v>
@@ -4998,16 +4784,13 @@
         <v>-13408.68380952146</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.388509157290579e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2009.651086581542</v>
+        <v>595.3299320051202</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.814632900463765e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8236660766185427</v>
+        <v>0.9906016476263658</v>
       </c>
     </row>
     <row r="13">
@@ -5018,7 +4801,7 @@
         <v>1332.451</v>
       </c>
       <c r="C13" t="n">
-        <v>1765.861584025642</v>
+        <v>571.4581627535331</v>
       </c>
       <c r="D13" t="n">
         <v>2.75174e-07</v>
@@ -5051,16 +4834,13 @@
         <v>-13069.58629970245</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.077326304336074e-09</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1988.585488459867</v>
+        <v>659.5290030199304</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000005184e-08</v>
+        <v>1.262480337252934e-08</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8239785177168746</v>
+        <v>0.8700574064195482</v>
       </c>
     </row>
     <row r="14">
@@ -5071,7 +4851,7 @@
         <v>1319.375</v>
       </c>
       <c r="C14" t="n">
-        <v>1750.488402691555</v>
+        <v>570.5984318052576</v>
       </c>
       <c r="D14" t="n">
         <v>2.7566e-07</v>
@@ -5104,16 +4884,13 @@
         <v>-12063.39893161598</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.745777848336679e-11</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1967.523521816388</v>
+        <v>554.9818459710768</v>
       </c>
       <c r="AA14" t="n">
-        <v>1e-08</v>
+        <v>1.423354308100223e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.824319895403579</v>
+        <v>0.9996044502495859</v>
       </c>
     </row>
     <row r="15">
@@ -5124,7 +4901,7 @@
         <v>1305.521</v>
       </c>
       <c r="C15" t="n">
-        <v>1736.601393675771</v>
+        <v>571.9160654186725</v>
       </c>
       <c r="D15" t="n">
         <v>2.7625e-07</v>
@@ -5157,16 +4934,13 @@
         <v>-10976.93973333983</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.495153740909959e-10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1946.970922529222</v>
+        <v>589.6566429780917</v>
       </c>
       <c r="AA15" t="n">
-        <v>1e-08</v>
+        <v>3.745295906206976e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8246568875002308</v>
+        <v>0.9426572138062801</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +4951,7 @@
         <v>1287.448</v>
       </c>
       <c r="C16" t="n">
-        <v>1721.435783203664</v>
+        <v>574.1546523688141</v>
       </c>
       <c r="D16" t="n">
         <v>2.76572e-07</v>
@@ -5210,16 +4984,13 @@
         <v>-9732.800878275835</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.831367481518386e-08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1926.281913312374</v>
+        <v>579.8549631229891</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000000026e-08</v>
+        <v>3.108500601885025e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8249424076402582</v>
+        <v>0.950606399672132</v>
       </c>
     </row>
     <row r="17">
@@ -5230,7 +5001,7 @@
         <v>1277.658</v>
       </c>
       <c r="C17" t="n">
-        <v>1709.928727618283</v>
+        <v>570.7385406062231</v>
       </c>
       <c r="D17" t="n">
         <v>2.77116e-07</v>
@@ -5263,16 +5034,13 @@
         <v>-7522.882911668597</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.449667463875538e-11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1905.594758694585</v>
+        <v>527.7500233386786</v>
       </c>
       <c r="AA17" t="n">
-        <v>1e-08</v>
+        <v>1.356415003674851e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8252732783295348</v>
+        <v>0.9999321218469894</v>
       </c>
     </row>
     <row r="18">
@@ -5283,7 +5051,7 @@
         <v>1253.345</v>
       </c>
       <c r="C18" t="n">
-        <v>1688.917405678917</v>
+        <v>573.2914069386794</v>
       </c>
       <c r="D18" t="n">
         <v>2.77452e-07</v>
@@ -5316,16 +5084,13 @@
         <v>-8795.636872520881</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.613185758314617e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1885.516390533847</v>
+        <v>545.5721838850152</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000000005e-08</v>
+        <v>2.010670804425298e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8256325459764058</v>
+        <v>0.9759335684774001</v>
       </c>
     </row>
     <row r="19">
@@ -5336,7 +5101,7 @@
         <v>1246.089</v>
       </c>
       <c r="C19" t="n">
-        <v>1677.69205382667</v>
+        <v>570.7998468379001</v>
       </c>
       <c r="D19" t="n">
         <v>2.78037e-07</v>
@@ -5369,16 +5134,13 @@
         <v>-6428.455628008577</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.754854925663405e-09</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1865.299388057059</v>
+        <v>525.3342648063259</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000000125e-08</v>
+        <v>1.88118569463517e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8260036706665999</v>
+        <v>0.9839176676906376</v>
       </c>
     </row>
     <row r="20">
@@ -5389,7 +5151,7 @@
         <v>1225.326</v>
       </c>
       <c r="C20" t="n">
-        <v>1662.145567905007</v>
+        <v>572.5737063241661</v>
       </c>
       <c r="D20" t="n">
         <v>2.78435e-07</v>
@@ -5422,16 +5184,13 @@
         <v>-5358.523427761919</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.397442968575009e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1845.048278003251</v>
+        <v>504.5034001281635</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000021e-08</v>
+        <v>1.362854629678818e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8263735995242902</v>
+        <v>0.9999441409766796</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5201,7 @@
         <v>1206.616</v>
       </c>
       <c r="C21" t="n">
-        <v>1643.482729415482</v>
+        <v>574.0208010475832</v>
       </c>
       <c r="D21" t="n">
         <v>2.7898e-07</v>
@@ -5475,16 +5234,13 @@
         <v>-4640.010902268752</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.1358516570408e-11</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1824.420477384447</v>
+        <v>491.5743037629356</v>
       </c>
       <c r="AA21" t="n">
-        <v>1e-08</v>
+        <v>1.418495530109254e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8267393185947064</v>
+        <v>0.9976805184494644</v>
       </c>
     </row>
     <row r="22">
@@ -5495,7 +5251,7 @@
         <v>1200.128</v>
       </c>
       <c r="C22" t="n">
-        <v>1633.987000610123</v>
+        <v>572.3861506430475</v>
       </c>
       <c r="D22" t="n">
         <v>2.79508e-07</v>
@@ -5528,16 +5284,13 @@
         <v>-1761.507980488734</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.263197602822182e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1803.789355113339</v>
+        <v>493.4958672324675</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000001634e-08</v>
+        <v>1.859304917374455e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8271204443236575</v>
+        <v>0.9817446741198889</v>
       </c>
     </row>
   </sheetData>
@@ -5694,7 +5447,7 @@
         <v>2260.513</v>
       </c>
       <c r="C2" t="n">
-        <v>2817.925704685616</v>
+        <v>20565.15402206938</v>
       </c>
       <c r="D2" t="n">
         <v>2.33552e-07</v>
@@ -5727,10 +5480,7 @@
         <v>-24610.88784398716</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.30217154712413e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2956.937998599872</v>
+        <v>-17380.50946665429</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000002e-08</v>
@@ -5747,7 +5497,7 @@
         <v>1824.185</v>
       </c>
       <c r="C3" t="n">
-        <v>2267.726490849258</v>
+        <v>822.8116096738445</v>
       </c>
       <c r="D3" t="n">
         <v>2.57134e-07</v>
@@ -5780,16 +5530,13 @@
         <v>-25885.72601678587</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.913567043653538e-11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2557.221942423093</v>
+        <v>485.3105258681975</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000201e-08</v>
+        <v>1.203714438874728e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8186566601939841</v>
+        <v>0.9879186966392077</v>
       </c>
     </row>
     <row r="4">
@@ -5800,7 +5547,7 @@
         <v>1734.85</v>
       </c>
       <c r="C4" t="n">
-        <v>2166.205129657921</v>
+        <v>786.5881725670723</v>
       </c>
       <c r="D4" t="n">
         <v>2.61433e-07</v>
@@ -5833,16 +5580,13 @@
         <v>-24952.47167301413</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.71801248566196e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2467.479528630048</v>
+        <v>506.6964196278819</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.00000000000012e-08</v>
+        <v>1.015525692991509e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8188875523917936</v>
+        <v>0.9933301588364196</v>
       </c>
     </row>
     <row r="5">
@@ -5853,7 +5597,7 @@
         <v>1701.509</v>
       </c>
       <c r="C5" t="n">
-        <v>2129.38513939821</v>
+        <v>771.9781074816468</v>
       </c>
       <c r="D5" t="n">
         <v>2.62997e-07</v>
@@ -5886,16 +5630,13 @@
         <v>-25876.23364109322</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.712620956868486e-11</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2424.155405503865</v>
+        <v>514.5282008216784</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000314e-08</v>
+        <v>1.215531096802408e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8189936531108708</v>
+        <v>0.9934511697561312</v>
       </c>
     </row>
     <row r="6">
@@ -5906,7 +5647,7 @@
         <v>1666.333</v>
       </c>
       <c r="C6" t="n">
-        <v>2099.045872079224</v>
+        <v>759.7462618535262</v>
       </c>
       <c r="D6" t="n">
         <v>2.64377e-07</v>
@@ -5939,16 +5680,13 @@
         <v>-23152.4503518414</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.699170757619234e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2389.607794254967</v>
+        <v>524.8184424143572</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000003e-08</v>
+        <v>1.2278532019319e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8191128686660192</v>
+        <v>0.9850383881248868</v>
       </c>
     </row>
     <row r="7">
@@ -5959,7 +5697,7 @@
         <v>1636.368</v>
       </c>
       <c r="C7" t="n">
-        <v>2071.50507943784</v>
+        <v>749.4390551615596</v>
       </c>
       <c r="D7" t="n">
         <v>2.65565e-07</v>
@@ -5992,16 +5730,13 @@
         <v>-21908.66417864332</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.539782532175464e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2356.375305165897</v>
+        <v>530.4055330092059</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000108e-08</v>
+        <v>1.797056944221876e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8192964298817575</v>
+        <v>0.9650477369166398</v>
       </c>
     </row>
     <row r="8">
@@ -6012,7 +5747,7 @@
         <v>1616.489</v>
       </c>
       <c r="C8" t="n">
-        <v>2049.383737797438</v>
+        <v>739.112970320195</v>
       </c>
       <c r="D8" t="n">
         <v>2.66743e-07</v>
@@ -6045,16 +5780,13 @@
         <v>-21553.71420906695</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.237800321216792e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2322.96340590222</v>
+        <v>519.9602309917378</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000139e-08</v>
+        <v>1.293363607566593e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8195047748476998</v>
+        <v>0.9852937870216827</v>
       </c>
     </row>
     <row r="9">
@@ -6065,7 +5797,7 @@
         <v>1576.785</v>
       </c>
       <c r="C9" t="n">
-        <v>2015.032427139511</v>
+        <v>729.2832839069745</v>
       </c>
       <c r="D9" t="n">
         <v>2.68108e-07</v>
@@ -6098,16 +5830,13 @@
         <v>-18920.23360691632</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.176184117052209e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2290.390876427691</v>
+        <v>519.8859910436305</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000144e-08</v>
+        <v>1.440919942081636e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8197871273052044</v>
+        <v>0.9843476757282263</v>
       </c>
     </row>
     <row r="10">
@@ -6118,7 +5847,7 @@
         <v>1556.787</v>
       </c>
       <c r="C10" t="n">
-        <v>1994.727424438989</v>
+        <v>719.710151618606</v>
       </c>
       <c r="D10" t="n">
         <v>2.69206e-07</v>
@@ -6151,16 +5880,13 @@
         <v>-19355.01344117668</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.230642257829192e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2258.123496609084</v>
+        <v>517.033985752866</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000007e-08</v>
+        <v>1.313382720380332e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.820086404286682</v>
+        <v>0.9857752483595688</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5897,7 @@
         <v>1526.186</v>
       </c>
       <c r="C11" t="n">
-        <v>1963.440411562988</v>
+        <v>710.4930411528265</v>
       </c>
       <c r="D11" t="n">
         <v>2.70435e-07</v>
@@ -6204,16 +5930,13 @@
         <v>-17907.33525987165</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.590275806571983e-11</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2227.137972494579</v>
+        <v>529.8975264440458</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000297e-08</v>
+        <v>1.382700947387027e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8203877992848398</v>
+        <v>0.983921653130572</v>
       </c>
     </row>
   </sheetData>
@@ -6370,7 +6093,7 @@
         <v>1609.91</v>
       </c>
       <c r="C2" t="n">
-        <v>2050.43948283109</v>
+        <v>15152.21067045977</v>
       </c>
       <c r="D2" t="n">
         <v>2.70776e-07</v>
@@ -6403,10 +6126,7 @@
         <v>-23620.79989265063</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.750412073314734e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2285.751530651358</v>
+        <v>-12640.47925889155</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000508e-08</v>
@@ -6423,7 +6143,7 @@
         <v>1533.943</v>
       </c>
       <c r="C3" t="n">
-        <v>1957.161824224932</v>
+        <v>706.9240655497696</v>
       </c>
       <c r="D3" t="n">
         <v>2.70426e-07</v>
@@ -6456,16 +6176,13 @@
         <v>-25690.8969326318</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.374154993122139e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2209.635421278826</v>
+        <v>517.5349666248679</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.00000000000296e-08</v>
+        <v>2.047918574635327e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.822687494559461</v>
+        <v>0.9593948986263202</v>
       </c>
     </row>
     <row r="4">
@@ -6476,7 +6193,7 @@
         <v>1501.203</v>
       </c>
       <c r="C4" t="n">
-        <v>1924.796641779799</v>
+        <v>697.325035328351</v>
       </c>
       <c r="D4" t="n">
         <v>2.71258e-07</v>
@@ -6509,16 +6226,13 @@
         <v>-24674.24474221483</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.196231976292161e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2174.993664999086</v>
+        <v>500.9237960839006</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.00000000000007e-08</v>
+        <v>1.474356045493759e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8227010879327041</v>
+        <v>0.9842040373329293</v>
       </c>
     </row>
     <row r="5">
@@ -6529,7 +6243,7 @@
         <v>1470.704</v>
       </c>
       <c r="C5" t="n">
-        <v>1896.900712036074</v>
+        <v>688.5957888143662</v>
       </c>
       <c r="D5" t="n">
         <v>2.72158e-07</v>
@@ -6562,16 +6276,13 @@
         <v>-22867.40411278554</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.664984294725045e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2146.383493230952</v>
+        <v>506.974677680758</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000369e-08</v>
+        <v>1.562353207667631e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8227968142890212</v>
+        <v>0.9781037304862742</v>
       </c>
     </row>
     <row r="6">
@@ -6582,7 +6293,7 @@
         <v>1447.689</v>
       </c>
       <c r="C6" t="n">
-        <v>1874.374467754752</v>
+        <v>681.5666979324047</v>
       </c>
       <c r="D6" t="n">
         <v>2.73062e-07</v>
@@ -6615,16 +6326,13 @@
         <v>-22849.57908735387</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.503533905028396e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2118.771618117882</v>
+        <v>492.2524671312074</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.17761033484129e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8229708081128672</v>
+        <v>0.9965251252552935</v>
       </c>
     </row>
     <row r="7">
@@ -6635,7 +6343,7 @@
         <v>1420.083</v>
       </c>
       <c r="C7" t="n">
-        <v>1849.852691953568</v>
+        <v>674.3469573114188</v>
       </c>
       <c r="D7" t="n">
         <v>2.7394e-07</v>
@@ -6668,16 +6376,13 @@
         <v>-21523.63167762938</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.211580991380278e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2091.723620345841</v>
+        <v>489.2144627925952</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000114e-08</v>
+        <v>1.16202314735017e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8232214068193421</v>
+        <v>0.997151215339985</v>
       </c>
     </row>
     <row r="8">
@@ -6688,7 +6393,7 @@
         <v>1407.208</v>
       </c>
       <c r="C8" t="n">
-        <v>1835.72893932643</v>
+        <v>667.2582114495256</v>
       </c>
       <c r="D8" t="n">
         <v>2.75028e-07</v>
@@ -6721,16 +6426,13 @@
         <v>-22142.38100978825</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.280687187380231e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2065.374477437337</v>
+        <v>506.9596059943732</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000784e-08</v>
+        <v>1.494215626131423e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8234818555599837</v>
+        <v>0.9827461276850903</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6443,7 @@
         <v>1387.607</v>
       </c>
       <c r="C9" t="n">
-        <v>1813.460599256315</v>
+        <v>664.4299768566158</v>
       </c>
       <c r="D9" t="n">
         <v>2.75623e-07</v>
@@ -6774,16 +6476,13 @@
         <v>-20908.72258690815</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.162138625882955e-12</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2040.539887676406</v>
+        <v>481.9589242723507</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>1.453520035885765e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8237680616765072</v>
+        <v>0.9848175650155685</v>
       </c>
     </row>
     <row r="10">
@@ -6794,7 +6493,7 @@
         <v>1366.414</v>
       </c>
       <c r="C10" t="n">
-        <v>1795.23975517223</v>
+        <v>565.7386830583538</v>
       </c>
       <c r="D10" t="n">
         <v>2.76358e-07</v>
@@ -6827,16 +6526,13 @@
         <v>-20853.77385718287</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.669281048614839e-12</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2015.913478467688</v>
+        <v>583.7559828168193</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.00000000000128e-08</v>
+        <v>1.815333048470209e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8240725341018178</v>
+        <v>0.9880758365402845</v>
       </c>
     </row>
     <row r="11">
@@ -6847,7 +6543,7 @@
         <v>1347.876</v>
       </c>
       <c r="C11" t="n">
-        <v>1774.975521704621</v>
+        <v>567.0391749414326</v>
       </c>
       <c r="D11" t="n">
         <v>2.77004e-07</v>
@@ -6880,16 +6576,13 @@
         <v>-19764.40946694198</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.752490992783068e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1991.670976810645</v>
+        <v>592.3102072953673</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000005e-08</v>
+        <v>2.195033478870559e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8243843461484566</v>
+        <v>0.9782558394441966</v>
       </c>
     </row>
     <row r="12">
@@ -6900,7 +6593,7 @@
         <v>1323.162</v>
       </c>
       <c r="C12" t="n">
-        <v>1754.343389100499</v>
+        <v>567.3005614530815</v>
       </c>
       <c r="D12" t="n">
         <v>2.77827e-07</v>
@@ -6933,16 +6626,13 @@
         <v>-18589.9176031032</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.706400667419449e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1968.324983783407</v>
+        <v>665.6450636369765</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000010839e-08</v>
+        <v>1.581569155733267e-08</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8247131982781635</v>
+        <v>0.8573318548471164</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6643,7 @@
         <v>1305.796</v>
       </c>
       <c r="C13" t="n">
-        <v>1736.602182211189</v>
+        <v>567.2645607166673</v>
       </c>
       <c r="D13" t="n">
         <v>2.78304e-07</v>
@@ -6986,16 +6676,13 @@
         <v>-17643.11913838646</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.884180004263952e-10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1945.471008717886</v>
+        <v>647.0222428604732</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000047e-08</v>
+        <v>1.074349698344548e-08</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8250518781297221</v>
+        <v>0.8813523232148203</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6693,7 @@
         <v>1286.966</v>
       </c>
       <c r="C14" t="n">
-        <v>1719.450077306784</v>
+        <v>1286.966</v>
       </c>
       <c r="D14" t="n">
         <v>2.78987e-07</v>
@@ -7038,11 +6725,10 @@
       <c r="X14" t="n">
         <v>-16908.97798759751</v>
       </c>
-      <c r="Y14" t="n">
-        <v>4.56634905634774e-08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1922.492970663477</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000004e-08</v>
@@ -7059,7 +6745,7 @@
         <v>1274.237</v>
       </c>
       <c r="C15" t="n">
-        <v>1707.511456789598</v>
+        <v>569.117788107424</v>
       </c>
       <c r="D15" t="n">
         <v>2.79545e-07</v>
@@ -7092,16 +6778,13 @@
         <v>-16587.38220079639</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.691081942066405e-09</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1899.672234094086</v>
+        <v>537.9419141092678</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000000019e-08</v>
+        <v>1.884134409398509e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8257762745721798</v>
+        <v>0.9852780265265304</v>
       </c>
     </row>
     <row r="16">
@@ -7112,7 +6795,7 @@
         <v>1255.979</v>
       </c>
       <c r="C16" t="n">
-        <v>1687.558421438096</v>
+        <v>565.5593729697709</v>
       </c>
       <c r="D16" t="n">
         <v>2.80233e-07</v>
@@ -7145,16 +6828,13 @@
         <v>-15529.55453338808</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.013786200246354e-08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1877.628540771008</v>
+        <v>531.0105000671987</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000004754e-08</v>
+        <v>1.862753939538945e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8261421362313737</v>
+        <v>0.9864531040184314</v>
       </c>
     </row>
     <row r="17">
@@ -7165,7 +6845,7 @@
         <v>1236.098</v>
       </c>
       <c r="C17" t="n">
-        <v>1670.375425036866</v>
+        <v>568.3939363659118</v>
       </c>
       <c r="D17" t="n">
         <v>2.80835e-07</v>
@@ -7198,16 +6878,13 @@
         <v>-14299.69784118015</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.448334698901164e-08</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1856.200708671826</v>
+        <v>523.759889492708</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000352e-08</v>
+        <v>1.938671323613662e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8264937808231316</v>
+        <v>0.9820107811243258</v>
       </c>
     </row>
     <row r="18">
@@ -7218,7 +6895,7 @@
         <v>1218.23</v>
       </c>
       <c r="C18" t="n">
-        <v>1653.616600913153</v>
+        <v>568.6254557291778</v>
       </c>
       <c r="D18" t="n">
         <v>2.81236e-07</v>
@@ -7251,16 +6928,13 @@
         <v>-13869.47120063771</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.497192290068686e-09</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1834.692257238707</v>
+        <v>517.9450572204001</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000000137e-08</v>
+        <v>1.805237523211327e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8268651153805456</v>
+        <v>0.9884336201666533</v>
       </c>
     </row>
     <row r="19">
@@ -7271,7 +6945,7 @@
         <v>1200.111</v>
       </c>
       <c r="C19" t="n">
-        <v>1632.960057407249</v>
+        <v>567.4744580279307</v>
       </c>
       <c r="D19" t="n">
         <v>2.81805e-07</v>
@@ -7304,16 +6978,13 @@
         <v>-12577.83482922228</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.24225376749655e-09</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1813.426360493051</v>
+        <v>497.4415001793255</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000000008e-08</v>
+        <v>1.438149221238987e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.827226381242459</v>
+        <v>0.9989475709125126</v>
       </c>
     </row>
     <row r="20">
@@ -7324,7 +6995,7 @@
         <v>1182.871</v>
       </c>
       <c r="C20" t="n">
-        <v>1618.365625867356</v>
+        <v>568.6496356922793</v>
       </c>
       <c r="D20" t="n">
         <v>2.82349e-07</v>
@@ -7357,16 +7028,13 @@
         <v>-11912.07840534174</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.776005379892511e-09</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1792.483501758146</v>
+        <v>491.5025640634615</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000036e-08</v>
+        <v>1.462327888754538e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8275886121577776</v>
+        <v>0.9997025553515506</v>
       </c>
     </row>
     <row r="21">
@@ -7377,7 +7045,7 @@
         <v>1166.748</v>
       </c>
       <c r="C21" t="n">
-        <v>1602.758865858035</v>
+        <v>568.8025434466655</v>
       </c>
       <c r="D21" t="n">
         <v>2.82974e-07</v>
@@ -7410,16 +7078,13 @@
         <v>-10863.72742988273</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.606707441049849e-12</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1771.999555216325</v>
+        <v>476.3689633435586</v>
       </c>
       <c r="AA21" t="n">
-        <v>1e-08</v>
+        <v>1.685024361006666e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8279650952822593</v>
+        <v>0.9857820812050619</v>
       </c>
     </row>
     <row r="22">
@@ -7430,7 +7095,7 @@
         <v>1147.86</v>
       </c>
       <c r="C22" t="n">
-        <v>1585.013543688154</v>
+        <v>568.3314905640661</v>
       </c>
       <c r="D22" t="n">
         <v>2.83504e-07</v>
@@ -7463,16 +7128,13 @@
         <v>-10041.34775171374</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.996311958269129e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1752.045499276904</v>
+        <v>464.4825181261007</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000155e-08</v>
+        <v>1.512733434148039e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8283381996472022</v>
+        <v>0.9919883118898157</v>
       </c>
     </row>
   </sheetData>
@@ -7629,7 +7291,7 @@
         <v>2080.499</v>
       </c>
       <c r="C2" t="n">
-        <v>2671.844294075562</v>
+        <v>20600.33469535375</v>
       </c>
       <c r="D2" t="n">
         <v>2.42018e-07</v>
@@ -7662,10 +7324,7 @@
         <v>-21927.46412757324</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.613250234160914e-12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2724.81086859951</v>
+        <v>-17590.10440504111</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000007e-08</v>
@@ -7682,7 +7341,7 @@
         <v>1752.981</v>
       </c>
       <c r="C3" t="n">
-        <v>2251.733009204009</v>
+        <v>775.7209817810696</v>
       </c>
       <c r="D3" t="n">
         <v>2.60505e-07</v>
@@ -7715,16 +7374,13 @@
         <v>-28086.54560608976</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.924982133438359e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2412.801406091939</v>
+        <v>464.3056898334667</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000125615e-08</v>
+        <v>9.791685362784339e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8230839475952438</v>
+        <v>0.9968514789745815</v>
       </c>
     </row>
     <row r="4">
@@ -7735,7 +7391,7 @@
         <v>1667.415</v>
       </c>
       <c r="C4" t="n">
-        <v>2159.066167090395</v>
+        <v>741.1672946423586</v>
       </c>
       <c r="D4" t="n">
         <v>2.63961e-07</v>
@@ -7768,16 +7424,13 @@
         <v>-26752.54792915133</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.745932340444233e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2335.828889204699</v>
+        <v>495.8604480537136</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000057e-08</v>
+        <v>1.543814540023801e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.823231155927322</v>
+        <v>0.9755231507685773</v>
       </c>
     </row>
     <row r="5">
@@ -7788,7 +7441,7 @@
         <v>1631.705</v>
       </c>
       <c r="C5" t="n">
-        <v>2122.236885460613</v>
+        <v>726.0580290558839</v>
       </c>
       <c r="D5" t="n">
         <v>2.65618e-07</v>
@@ -7821,16 +7474,13 @@
         <v>-25998.34806713569</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.102516286622736e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2294.508153669695</v>
+        <v>501.4967298095019</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000004148e-08</v>
+        <v>1.21560171826842e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8233075400036555</v>
+        <v>0.9916299258718357</v>
       </c>
     </row>
     <row r="6">
@@ -7841,7 +7491,7 @@
         <v>1600.884</v>
       </c>
       <c r="C6" t="n">
-        <v>2095.515842247793</v>
+        <v>714.4248220753025</v>
       </c>
       <c r="D6" t="n">
         <v>2.66848e-07</v>
@@ -7874,16 +7524,13 @@
         <v>-25847.10498817057</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.561005022350489e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2260.236937979773</v>
+        <v>484.0668112431738</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000271e-08</v>
+        <v>1.116289624440648e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8234394011820801</v>
+        <v>0.9995742769427313</v>
       </c>
     </row>
     <row r="7">
@@ -7894,7 +7541,7 @@
         <v>1560.339</v>
       </c>
       <c r="C7" t="n">
-        <v>2058.758702827764</v>
+        <v>704.0063568831645</v>
       </c>
       <c r="D7" t="n">
         <v>2.68399e-07</v>
@@ -7927,16 +7574,13 @@
         <v>-22128.90027751403</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.516499178642977e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2227.079988370894</v>
+        <v>507.4320408843067</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000154e-08</v>
+        <v>1.202525016462039e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.823644715759061</v>
+        <v>0.9988740641217638</v>
       </c>
     </row>
     <row r="8">
@@ -7947,7 +7591,7 @@
         <v>1539.223</v>
       </c>
       <c r="C8" t="n">
-        <v>2037.515834860949</v>
+        <v>693.2322169562003</v>
       </c>
       <c r="D8" t="n">
         <v>2.69516e-07</v>
@@ -7980,16 +7624,13 @@
         <v>-22968.99222627899</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.551461243087532e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2194.20346379568</v>
+        <v>508.7465199599487</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000023e-08</v>
+        <v>1.84328340901937e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8239043968418819</v>
+        <v>0.967766333728967</v>
       </c>
     </row>
     <row r="9">
@@ -8000,7 +7641,7 @@
         <v>1505.867</v>
       </c>
       <c r="C9" t="n">
-        <v>2007.208742633907</v>
+        <v>683.9224181579619</v>
       </c>
       <c r="D9" t="n">
         <v>2.71144e-07</v>
@@ -8033,16 +7674,13 @@
         <v>-20592.58714415694</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.455354940667196e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2161.303038555179</v>
+        <v>493.9098397630337</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.155573405245588e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8241806170065185</v>
+        <v>0.9973546792600917</v>
       </c>
     </row>
     <row r="10">
@@ -8053,7 +7691,7 @@
         <v>1480.734</v>
       </c>
       <c r="C10" t="n">
-        <v>1983.469722943864</v>
+        <v>674.6947632758187</v>
       </c>
       <c r="D10" t="n">
         <v>2.72276e-07</v>
@@ -8086,16 +7724,13 @@
         <v>-20336.39985406741</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.817495786104308e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2130.387581425748</v>
+        <v>495.6574317726864</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000024e-08</v>
+        <v>1.519813669755969e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.824483680296065</v>
+        <v>0.9834278930441851</v>
       </c>
     </row>
     <row r="11">
@@ -8106,7 +7741,7 @@
         <v>1463.063</v>
       </c>
       <c r="C11" t="n">
-        <v>1963.548315061728</v>
+        <v>670.6352999394807</v>
       </c>
       <c r="D11" t="n">
         <v>2.73653e-07</v>
@@ -8139,16 +7774,13 @@
         <v>-20051.69724667293</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.378977546756153e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2099.901814899286</v>
+        <v>497.6679775090619</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000004319e-08</v>
+        <v>1.460791014430689e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8247797665825782</v>
+        <v>0.9885598742141195</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +7937,7 @@
         <v>1641.585</v>
       </c>
       <c r="C2" t="n">
-        <v>2109.825246182789</v>
+        <v>743.4741563334871</v>
       </c>
       <c r="D2" t="n">
         <v>2.67715e-07</v>
@@ -8338,16 +7970,13 @@
         <v>-25415.24457657672</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.860479258100244e-12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2330.843702421264</v>
+        <v>508.3568941892777</v>
       </c>
       <c r="AA2" t="n">
-        <v>1e-08</v>
+        <v>1.207769250518112e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8203766296225971</v>
+        <v>0.9941689226099736</v>
       </c>
     </row>
     <row r="3">
@@ -8358,7 +7987,7 @@
         <v>1541.11</v>
       </c>
       <c r="C3" t="n">
-        <v>1980.179204683424</v>
+        <v>713.7599042965376</v>
       </c>
       <c r="D3" t="n">
         <v>2.70687e-07</v>
@@ -8391,16 +8020,13 @@
         <v>-24266.66695552331</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.73284888058118e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2235.560156804875</v>
+        <v>513.9274268692194</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000008756e-08</v>
+        <v>1.346380067745243e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8205588836508823</v>
+        <v>0.9849094550444649</v>
       </c>
     </row>
     <row r="4">
@@ -8411,7 +8037,7 @@
         <v>1509.271</v>
       </c>
       <c r="C4" t="n">
-        <v>1955.448016017084</v>
+        <v>706.9092197081565</v>
       </c>
       <c r="D4" t="n">
         <v>2.71843e-07</v>
@@ -8444,16 +8070,13 @@
         <v>-22851.76486192156</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.168935081485231e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2206.961743971004</v>
+        <v>510.4550768718222</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000001023e-08</v>
+        <v>1.374547830285472e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8203056810271685</v>
+        <v>0.9856125909879634</v>
       </c>
     </row>
     <row r="5">
@@ -8464,7 +8087,7 @@
         <v>1482.039</v>
       </c>
       <c r="C5" t="n">
-        <v>1933.238527441983</v>
+        <v>1257.62959851206</v>
       </c>
       <c r="D5" t="n">
         <v>2.72525e-07</v>
@@ -8497,16 +8120,13 @@
         <v>-20270.92972786303</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.810032929320714e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2183.867276708726</v>
+        <v>8.680365371486026</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000014e-08</v>
+        <v>2.035520660457385e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8201814990230871</v>
+        <v>0.8929910698416561</v>
       </c>
     </row>
     <row r="6">
@@ -8517,7 +8137,7 @@
         <v>1458.855</v>
       </c>
       <c r="C6" t="n">
-        <v>1915.159427429956</v>
+        <v>1277.802571761686</v>
       </c>
       <c r="D6" t="n">
         <v>2.73475e-07</v>
@@ -8550,16 +8170,13 @@
         <v>-19303.39749494659</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.788368056468971e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2161.878319768788</v>
+        <v>3.353989506621423</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000071e-08</v>
+        <v>2.640514328339661e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8202410733306622</v>
+        <v>0.8698608219005224</v>
       </c>
     </row>
     <row r="7">
@@ -8570,7 +8187,7 @@
         <v>1445.709</v>
       </c>
       <c r="C7" t="n">
-        <v>1902.377474202877</v>
+        <v>1270.830078519614</v>
       </c>
       <c r="D7" t="n">
         <v>2.74087e-07</v>
@@ -8603,16 +8220,13 @@
         <v>-19394.21719050666</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.588007331900357e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2138.526822693762</v>
+        <v>2.445158199885856</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>2.734968106151157e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8204063357584395</v>
+        <v>0.8709438561386534</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8237,7 @@
         <v>1426.926</v>
       </c>
       <c r="C8" t="n">
-        <v>1881.38132175755</v>
+        <v>582.3827086294166</v>
       </c>
       <c r="D8" t="n">
         <v>2.74862e-07</v>
@@ -8656,16 +8270,13 @@
         <v>-18463.94432362843</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.318298254907723e-12</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2114.658131670821</v>
+        <v>715.4527885283901</v>
       </c>
       <c r="AA8" t="n">
-        <v>1e-08</v>
+        <v>1.582357414694725e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8206406573280738</v>
+        <v>0.8586603057698957</v>
       </c>
     </row>
     <row r="9">
@@ -8676,7 +8287,7 @@
         <v>1407.073</v>
       </c>
       <c r="C9" t="n">
-        <v>1862.992165898949</v>
+        <v>582.9167156098565</v>
       </c>
       <c r="D9" t="n">
         <v>2.75641e-07</v>
@@ -8709,16 +8320,13 @@
         <v>-17245.96001469352</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.136616869180104e-11</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2090.417843842138</v>
+        <v>614.172058747026</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>1.644883889878677e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8209354191250118</v>
+        <v>0.9981194332823633</v>
       </c>
     </row>
     <row r="10">
@@ -8729,7 +8337,7 @@
         <v>1388.039</v>
       </c>
       <c r="C10" t="n">
-        <v>1845.220739450489</v>
+        <v>2144.153804198519</v>
       </c>
       <c r="D10" t="n">
         <v>2.76416e-07</v>
@@ -8762,10 +8370,7 @@
         <v>-16150.70519243724</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.375164881893975e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2066.653463733323</v>
+        <v>-177.251987355462</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000003e-08</v>
@@ -8782,7 +8387,7 @@
         <v>1370.136</v>
       </c>
       <c r="C11" t="n">
-        <v>1824.856579972031</v>
+        <v>582.8992771854453</v>
       </c>
       <c r="D11" t="n">
         <v>2.76847e-07</v>
@@ -8815,16 +8420,13 @@
         <v>-15566.30593815601</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.908870016520314e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2043.341897333103</v>
+        <v>600.2928705005103</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>1.6322822171739e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8216069672646281</v>
+        <v>0.9951488267287089</v>
       </c>
     </row>
     <row r="12">
@@ -8835,7 +8437,7 @@
         <v>1347.418</v>
       </c>
       <c r="C12" t="n">
-        <v>1802.115801761572</v>
+        <v>582.8888455955938</v>
       </c>
       <c r="D12" t="n">
         <v>2.77809e-07</v>
@@ -8868,16 +8470,13 @@
         <v>-14565.46814579631</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.322615991314992e-08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2020.16053882251</v>
+        <v>583.9267805287762</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000000215e-08</v>
+        <v>1.515115285646229e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8219646244819373</v>
+        <v>0.999462849235644</v>
       </c>
     </row>
     <row r="13">
@@ -8888,7 +8487,7 @@
         <v>1331.037</v>
       </c>
       <c r="C13" t="n">
-        <v>1785.036959759623</v>
+        <v>581.7686778670702</v>
       </c>
       <c r="D13" t="n">
         <v>2.78218e-07</v>
@@ -8921,16 +8520,13 @@
         <v>-13845.92294194618</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.785105645371334e-08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1997.490241548479</v>
+        <v>563.8886223079579</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000008911e-08</v>
+        <v>1.395569209611439e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8223245235574083</v>
+        <v>0.9997558204775839</v>
       </c>
     </row>
     <row r="14">
@@ -8941,7 +8537,7 @@
         <v>1308.014</v>
       </c>
       <c r="C14" t="n">
-        <v>1762.603608455876</v>
+        <v>582.2348048494016</v>
       </c>
       <c r="D14" t="n">
         <v>2.78952e-07</v>
@@ -8974,16 +8570,13 @@
         <v>-12564.12392974316</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.457075084295988e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1974.89311248592</v>
+        <v>561.4097621385117</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000006e-08</v>
+        <v>1.493287153525512e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8226886039602009</v>
+        <v>0.9958598621777969</v>
       </c>
     </row>
     <row r="15">
@@ -8994,7 +8587,7 @@
         <v>1304.887</v>
       </c>
       <c r="C15" t="n">
-        <v>1751.952203538874</v>
+        <v>580.2651072127412</v>
       </c>
       <c r="D15" t="n">
         <v>2.79522e-07</v>
@@ -9027,16 +8620,13 @@
         <v>-11413.52851561091</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.461366273816545e-09</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1952.456187246838</v>
+        <v>547.3620723692029</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000000375e-08</v>
+        <v>1.345007872270982e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8230478757267712</v>
+        <v>0.9998485849881174</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8637,7 @@
         <v>1276.011</v>
       </c>
       <c r="C16" t="n">
-        <v>1726.789581511011</v>
+        <v>583.9372429934864</v>
       </c>
       <c r="D16" t="n">
         <v>2.80144e-07</v>
@@ -9080,16 +8670,13 @@
         <v>-11297.33283682459</v>
       </c>
       <c r="Y16" t="n">
-        <v>7.364805196144608e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1929.821166693281</v>
+        <v>549.5793142929941</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000000034e-08</v>
+        <v>1.540433684938371e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8234251189461679</v>
+        <v>0.9934927333658301</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8687,7 @@
         <v>1263.615</v>
       </c>
       <c r="C17" t="n">
-        <v>1715.214797710403</v>
+        <v>583.4146857894289</v>
       </c>
       <c r="D17" t="n">
         <v>2.80707e-07</v>
@@ -9133,16 +8720,13 @@
         <v>-10003.08752512914</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.090587102766822e-08</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1907.316749380236</v>
+        <v>539.3027425117891</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000005716e-08</v>
+        <v>1.447405081100535e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8238082332403217</v>
+        <v>0.9979534452544851</v>
       </c>
     </row>
     <row r="18">
@@ -9153,7 +8737,7 @@
         <v>1253.506</v>
       </c>
       <c r="C18" t="n">
-        <v>1708.109454342685</v>
+        <v>584.5911512763333</v>
       </c>
       <c r="D18" t="n">
         <v>2.8138e-07</v>
@@ -9186,16 +8770,13 @@
         <v>-8347.899868589046</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.8741747102887855</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2043.001623831462</v>
+        <v>520.9977498901779</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.587433214147698e-08</v>
+        <v>1.414338760423307e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.7908331714846627</v>
+        <v>0.9975940747464036</v>
       </c>
     </row>
     <row r="19">
@@ -9206,7 +8787,7 @@
         <v>1231.156</v>
       </c>
       <c r="C19" t="n">
-        <v>1687.033824412345</v>
+        <v>583.4373592731321</v>
       </c>
       <c r="D19" t="n">
         <v>2.81942e-07</v>
@@ -9239,16 +8820,13 @@
         <v>-8566.868599982852</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.858598537852844e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1862.850944642408</v>
+        <v>514.9449453732809</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000039775e-08</v>
+        <v>1.410326540241311e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8246121096991341</v>
+        <v>0.9995832607749907</v>
       </c>
     </row>
     <row r="20">
@@ -9259,7 +8837,7 @@
         <v>1212.164</v>
       </c>
       <c r="C20" t="n">
-        <v>1664.07109894983</v>
+        <v>583.0474306947013</v>
       </c>
       <c r="D20" t="n">
         <v>2.82641e-07</v>
@@ -9292,16 +8870,13 @@
         <v>-6923.488510870208</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.624299844648675e-10</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1840.576389400926</v>
+        <v>503.9587606685814</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000508e-08</v>
+        <v>1.758447706316188e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8249970307486727</v>
+        <v>0.9819300641348476</v>
       </c>
     </row>
     <row r="21">
@@ -9312,7 +8887,7 @@
         <v>1195.068</v>
       </c>
       <c r="C21" t="n">
-        <v>1647.186222846969</v>
+        <v>584.8310593008346</v>
       </c>
       <c r="D21" t="n">
         <v>2.83264e-07</v>
@@ -9345,16 +8920,13 @@
         <v>-5957.6595670581</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.354992704632171e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1818.722469865537</v>
+        <v>493.7184650860404</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000002211e-08</v>
+        <v>1.639746799059293e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8253992353999942</v>
+        <v>0.9865351884103024</v>
       </c>
     </row>
     <row r="22">
@@ -9365,7 +8937,7 @@
         <v>1179.113</v>
       </c>
       <c r="C22" t="n">
-        <v>1634.216112632073</v>
+        <v>582.3573739449231</v>
       </c>
       <c r="D22" t="n">
         <v>2.83908e-07</v>
@@ -9398,16 +8970,13 @@
         <v>-4080.115603521277</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.697873130761003e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1797.320649040756</v>
+        <v>492.8652008936592</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000001233e-08</v>
+        <v>1.795635004947643e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8257861209646697</v>
+        <v>0.9806192222987196</v>
       </c>
     </row>
   </sheetData>
@@ -9564,7 +9133,7 @@
         <v>1458.226</v>
       </c>
       <c r="C2" t="n">
-        <v>2099.300351889218</v>
+        <v>16533.14041692419</v>
       </c>
       <c r="D2" t="n">
         <v>2.67718e-07</v>
@@ -9597,10 +9166,7 @@
         <v>-23546.06347275934</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.22857215759464e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2084.168446031461</v>
+        <v>-14132.59473756</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000002262e-08</v>
@@ -9617,7 +9183,7 @@
         <v>1300.667</v>
       </c>
       <c r="C3" t="n">
-        <v>1884.336018938228</v>
+        <v>575.22704839594</v>
       </c>
       <c r="D3" t="n">
         <v>2.72726e-07</v>
@@ -9650,16 +9216,13 @@
         <v>-23123.06722751787</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.982835743069414e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1952.384593254094</v>
+        <v>561.4925518797554</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000027e-08</v>
+        <v>1.450523704644273e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.822387035401384</v>
+        <v>0.9997291889585906</v>
       </c>
     </row>
     <row r="4">
@@ -9670,7 +9233,7 @@
         <v>1261.579</v>
       </c>
       <c r="C4" t="n">
-        <v>1839.079660424648</v>
+        <v>586.4183362005629</v>
       </c>
       <c r="D4" t="n">
         <v>2.74296e-07</v>
@@ -9703,16 +9266,13 @@
         <v>-23170.73634900921</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.020905696240408e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1911.773568219954</v>
+        <v>554.9900452621872</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000002281e-08</v>
+        <v>1.999380672955255e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8224192081911762</v>
+        <v>0.9758726962635226</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9283,7 @@
         <v>1238.778</v>
       </c>
       <c r="C5" t="n">
-        <v>1814.636973393718</v>
+        <v>589.3172237454817</v>
       </c>
       <c r="D5" t="n">
         <v>2.75188e-07</v>
@@ -9756,16 +9316,13 @@
         <v>-22692.42861385292</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.39835052292691e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1887.252671064778</v>
+        <v>526.3606247050893</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.00000000008713e-08</v>
+        <v>1.29429550349629e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8224901751808166</v>
+        <v>0.9992333949261334</v>
       </c>
     </row>
     <row r="6">
@@ -9776,7 +9333,7 @@
         <v>1211.349</v>
       </c>
       <c r="C6" t="n">
-        <v>1794.443503119097</v>
+        <v>589.7390881990381</v>
       </c>
       <c r="D6" t="n">
         <v>2.76046e-07</v>
@@ -9809,16 +9366,13 @@
         <v>-21424.85353608882</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.907067596927201e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1862.036001391821</v>
+        <v>534.7958956048116</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000029612e-08</v>
+        <v>1.900401336488029e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8226381285534451</v>
+        <v>0.9772541770732122</v>
       </c>
     </row>
     <row r="7">
@@ -9829,7 +9383,7 @@
         <v>1197.885</v>
       </c>
       <c r="C7" t="n">
-        <v>1780.830079525871</v>
+        <v>592.1476581335215</v>
       </c>
       <c r="D7" t="n">
         <v>2.76752e-07</v>
@@ -9862,16 +9416,13 @@
         <v>-22272.91136226284</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.615166456038347e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1834.106353993896</v>
+        <v>512.6974293401906</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000008e-08</v>
+        <v>1.687477735287427e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8228701369842584</v>
+        <v>0.9832220282225456</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9433,7 @@
         <v>1176.457</v>
       </c>
       <c r="C8" t="n">
-        <v>1758.906633415103</v>
+        <v>593.1855363884703</v>
       </c>
       <c r="D8" t="n">
         <v>2.78237e-07</v>
@@ -9915,16 +9466,13 @@
         <v>-21553.44727666653</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.781378658722411e-12</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1805.56070717832</v>
+        <v>495.2212177223951</v>
       </c>
       <c r="AA8" t="n">
-        <v>1e-08</v>
+        <v>1.429604591625332e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8231657023917989</v>
+        <v>0.9944265247387093</v>
       </c>
     </row>
     <row r="9">
@@ -9935,7 +9483,7 @@
         <v>1151.93</v>
       </c>
       <c r="C9" t="n">
-        <v>1739.93632970659</v>
+        <v>1075.085896216547</v>
       </c>
       <c r="D9" t="n">
         <v>2.79261e-07</v>
@@ -9968,16 +9516,13 @@
         <v>-21796.94330786216</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.54342257965754e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1777.306673248712</v>
+        <v>37.59465295537423</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000001536e-08</v>
+        <v>1.991148827453712e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.823499001339231</v>
+        <v>0.9001627663405989</v>
       </c>
     </row>
     <row r="10">
@@ -9988,7 +9533,7 @@
         <v>1126.673</v>
       </c>
       <c r="C10" t="n">
-        <v>1724.666420304016</v>
+        <v>976.5657169403077</v>
       </c>
       <c r="D10" t="n">
         <v>2.80209e-07</v>
@@ -10021,16 +9566,13 @@
         <v>-19913.25335132917</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14376364950672e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1750.24396193424</v>
+        <v>118.8611813624497</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000896e-08</v>
+        <v>1.875102817205028e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8238785133233281</v>
+        <v>0.9159542492200957</v>
       </c>
     </row>
     <row r="11">
@@ -10041,7 +9583,7 @@
         <v>1101.556</v>
       </c>
       <c r="C11" t="n">
-        <v>1701.951978644532</v>
+        <v>1015.482094954455</v>
       </c>
       <c r="D11" t="n">
         <v>2.81368e-07</v>
@@ -10074,16 +9616,13 @@
         <v>-18812.88591572936</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.90786882155713e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1724.361446082798</v>
+        <v>74.21704943776172</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000064e-08</v>
+        <v>1.969498534896849e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8242397079789507</v>
+        <v>0.906917675562635</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 33.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 33.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,566 @@
         <v>1e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8211914455797964</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1702.875</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2090.726397989934</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.64227e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-65.235</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.48207236842109</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.400931414055879</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.035965386695553</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.499666481378524</v>
+      </c>
+      <c r="L12" t="n">
+        <v>590.3886297375767</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.94582735578604</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>14.10895144108921</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-29859.92229424242</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>8.903408029840648</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000386e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.81982275423088</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1595.431</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9369043529325406</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1987.992217515534</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9508619680828773</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.65191e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-67.15300000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3050061050061186</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4682904411764696</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.577008310249292</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.21507847533634</v>
+      </c>
+      <c r="L13" t="n">
+        <v>14.69264376398916</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.2948350617868</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.14982371510846</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-24355.13519661768</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>18.44907027170666</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000003237e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8199731307578405</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1554.83</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9130617338324891</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1950.6396052919</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9329961142535359</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.65466e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-67.83</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.031893687707678</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.099839743589634</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.370752089136459</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.548501742160285</v>
+      </c>
+      <c r="L14" t="n">
+        <v>11.25307049511366</v>
+      </c>
+      <c r="M14" t="n">
+        <v>84.8813083360975</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>11.16364704744479</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-21874.97582028011</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>19.17335119718257</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8199645705086693</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1525.224</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.895675842325479</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1922.437044593325</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9195067544187484</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.65669e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-68.29900000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.09078726968172954</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1570871261378327</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.180935251798549</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.091418563922966</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.911495962810958</v>
+      </c>
+      <c r="M15" t="n">
+        <v>84.70529366106189</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>10.7905119229467</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-20819.54562883605</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>19.93328583986874</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8199906873213119</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1499.3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8804521764662703</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1900.792293664561</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9091540124485065</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.65641e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-68.694</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5417322834645314</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7358251057827501</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.240104166666692</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.934028294862285</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.087770008437776</v>
+      </c>
+      <c r="M16" t="n">
+        <v>84.52897811928533</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>10.44074343528423</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-19865.04181524135</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>18.46255314147209</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000026e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8200850499410226</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1480.618</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8694813183586582</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1875.541290182365</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8970763902849975</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.65833e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-69.056</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4603085553996977</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.161321909424691</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.24003451251079</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.438137603796026</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>84.51653384220252</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>10.41690421576354</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-19584.63542263712</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>19.33521986021833</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8202484572555447</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1447.972</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8503102106731263</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1853.132900084057</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8863583976677656</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.66245e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-69.39</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1195928753180559</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.3042912873862121</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.8398406374502164</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.391939769707634</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3.368094086808174</v>
+      </c>
+      <c r="M18" t="n">
+        <v>84.04022788674311</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>9.579055831929072</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-17700.28362139756</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>18.3850708099377</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000007962e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8204383417175178</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1435.485</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.8429773177714159</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1830.048288093236</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.875316966319783</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.66563e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-69.702</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9963235294118561</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8723270440251951</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.766092572658859</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.989671610169512</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>84.08656974053565</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>9.654666240907856</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-17641.88651130295</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>18.54016747262267</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8206714947602654</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1405.035</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.8250957938780004</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1809.20616915344</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8653481253658281</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.66705e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-70.01600000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4621276595744636</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2642570281124456</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8114537444933201</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.74745437079728</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>83.80104399174131</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>9.206718879089721</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-16575.32057465745</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>17.92499198931239</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000061e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8209176843098924</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1386.906</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.8144496806870734</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1786.391865172682</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8544359830584025</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.67083e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-70.29900000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3496845425867304</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8812080536913663</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.297379912663769</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.013353798925547</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>83.65353850953689</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>8.991035758161958</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-15976.27246472913</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>18.70107993979013</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8211914455797964</v>
       </c>
     </row>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +3016,1182 @@
         <v>1.000000000005826e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8273530917654275</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1676.785</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2174.615862954897</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.59517e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-66.387</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3498648648648978</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8582846003898275</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.58509202453988</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.238054668086644</v>
+      </c>
+      <c r="L23" t="n">
+        <v>14.76200049900674</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.41844920460768</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.47909530493556</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-26059.5570109247</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-47.38508526251599</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8216355947521953</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1583.639</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9444496461979323</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2058.678346645976</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9466859787588491</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.63148e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-67.569</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4799313893652959</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8714142427281782</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.537384412153228</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.851886792452837</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.38795754740228</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12.39623817975668</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-24702.3958322783</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-34.58077118773542</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8218353998585043</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1534.87</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9153648201767073</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2018.553045080771</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9282343054087422</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.64489e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-67.959</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4499043977055115</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.4347989949748487</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.228180574555391</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.935774218154159</v>
+      </c>
+      <c r="L25" t="n">
+        <v>15.7319907398999</v>
+      </c>
+      <c r="M25" t="n">
+        <v>84.9718179812352</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>11.36566167170466</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-22137.28255878998</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-31.30690073030314</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000042e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.821907509895526</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1514.008</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9029231535348896</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1993.618126611623</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9167679499507871</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.65485e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-68.316</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1988888888888962</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5314356435643262</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.763714902807723</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.314861751152055</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>84.96051487970739</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>11.34003803271538</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-21825.95631522888</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-31.17666106184049</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8220211664326268</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1490.245</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8887513903094313</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1973.412666309692</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9074764421281252</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.66196e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-68.59</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.7158273381295092</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.3926764314247396</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.989651837524171</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.078025751072936</v>
+      </c>
+      <c r="L27" t="n">
+        <v>9.048945698289437</v>
+      </c>
+      <c r="M27" t="n">
+        <v>84.79546621383511</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10.97852532589656</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-20844.75145816288</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-32.38119321886211</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8221677501227233</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1472.704</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.878290299591182</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1951.459949658807</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8973814561469892</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.67142e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-68.84999999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1415902140672975</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.5494661921708068</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.433389687235785</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.316384522369956</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>84.88619344014531</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>11.1743683560806</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-21002.29092656574</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-32.80444211383838</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000028e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.822371698426117</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1439.099</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.858248970500094</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1928.303700696789</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8867330242301205</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.67993e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-69.107</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.364794007490817</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2998355263157834</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.8847036328873156</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.320799999999978</v>
+      </c>
+      <c r="L29" t="n">
+        <v>9.941863304148601</v>
+      </c>
+      <c r="M29" t="n">
+        <v>84.40255464874983</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>10.20347340268368</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-18847.54439819363</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-33.02864545749321</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8225854250764777</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1421.501</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8477538861571401</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1905.603879131653</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8762944810594242</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.68604e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-69.355</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1738127544097739</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6409523809524335</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.328554502369687</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.801531728665196</v>
+      </c>
+      <c r="L30" t="n">
+        <v>3.040995942706003</v>
+      </c>
+      <c r="M30" t="n">
+        <v>84.62380496977696</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>10.62601464768437</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-19448.94091516426</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-32.45751418821237</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8228326258450532</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1395.551</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8322778412259174</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1886.443133588375</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8674833867095273</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.69371e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-69.649</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1610021786492481</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.3360699865410465</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.7757489300998794</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.494150417827324</v>
+      </c>
+      <c r="L31" t="n">
+        <v>5.82202226721379</v>
+      </c>
+      <c r="M31" t="n">
+        <v>84.13958206467814</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>9.742621166844696</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-17551.28809108364</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-33.50592691203974</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000003671e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8231242008609685</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1387.541</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8275008423858753</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1863.715526809145</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8570320664711348</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.70096e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-69.902</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.6927197802197121</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.501510989010983</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.209592760181024</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.327213695395557</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>84.35554874398558</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>10.11795547702424</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-18067.91776146764</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-32.97782256926882</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8234233849416606</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1369.782</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.816909740962616</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1843.581852842458</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8477735696903153</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.70871e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-70.15000000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.3286713286713192</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.477029096477831</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.498476702508994</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.500185988840585</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>84.08605671225612</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>9.653822731309901</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-17005.34640597626</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-33.02467964393531</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8237496713461573</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1349.203</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8046368496855589</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1822.959385378522</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8382903005689754</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.71297e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-70.40300000000001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1543778801843056</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.6257400257400629</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.8887391722810615</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.340226876090768</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>83.89811554975765</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>9.354323772965778</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-16259.35119934392</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-32.98076841032628</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8240747769248813</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1337.807</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7978405102621982</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1807.370863378668</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.831121897971805</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.7203e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-70.63</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.8469184890655707</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.209730538921986</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.108705882353007</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.464153275648998</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>83.72793630392982</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>9.09855758346953</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-15627.05089699396</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-35.35428061754146</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000013e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8244141683169292</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1312.425</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7827032088192584</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1787.993325724137</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8222111114808976</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.72673e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-70.886</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3079491255961759</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.725074626865691</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.630298507462821</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.073650282030629</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>83.1759593932062</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>8.356428007884638</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-14130.27782756219</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-35.45483774438287</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8247686032601121</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1300.218</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7754232057180854</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1777.363995645213</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8173231998915464</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.73212e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-71.122</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.6015624999999677</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8166453265045015</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.733372921615076</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.22810344827591</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>82.49982684944662</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>7.595576736280749</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-12626.27035864673</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-39.23063375628863</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8251218515212776</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1274.406</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7600294611414105</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1758.403563985567</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8086042201477482</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.73692e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-71.342</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.08343949044586582</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.048936170212753</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.349999999999935</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.964772727272719</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>82.52185690839273</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>7.618210041262239</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-12538.88526326918</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-39.08659017458012</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8254789231270092</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1264.397</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7540602999191905</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1748.816049109425</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8041953886665346</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.74213e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-71.56999999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2171383647798574</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.036890243902319</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.501148105625846</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.1738435660219</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>81.84680826846503</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>6.979907395258109</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-11298.30669920068</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-43.60851863213395</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8258447851166493</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1246.777</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7435520952298595</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1736.203847689549</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7983956510509271</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.74817e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-71.81</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2049469964663993</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.227967806841013</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.87187500000013</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.088451668092362</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>80.45896450817675</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>5.949584712429432</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-9418.730443240538</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-46.53138477090715</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8262054678320458</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1235.158</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7366227632045849</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1721.665027045362</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7917099550197986</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.7531e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-72.041</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.5336879432624162</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8279521674140824</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.82271386430676</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.062346185397784</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>78.97838886808351</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>5.134214140647314</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-7937.577567431398</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-48.23743781916028</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000314e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8265912400963579</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1214.839</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7245049305665305</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1711.793179445334</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7871703727569276</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.75968e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-72.23</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.6228174603174474</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.096654929577439</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.091033755274279</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.064186046511649</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>78.36171159587786</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>4.855145934701059</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-7380.131259702622</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-52.77997764777604</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000001505e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8269705879571928</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1192.154</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7109760643135524</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1692.236728584878</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7781773127900595</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.7627e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-72.45399999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.05761453201377743</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.7130882412773585</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.937996036379833</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>9.980899619195149</v>
+      </c>
+      <c r="M43" t="n">
+        <v>79.12113507093649</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>5.203262352340198</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-7900.013300919956</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-51.43631633964958</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000005826e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8273530917654275</v>
       </c>
     </row>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +5524,1182 @@
         <v>1.000000000012479e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8277055231048595</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1643.652</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2040.776435898575</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.62418e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-66.309</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3579051383398678</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.6274422735346141</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.330699364214254</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.002010309278313</v>
+      </c>
+      <c r="L23" t="n">
+        <v>32.05811205644559</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.50992878672422</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.73441741119876</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-26065.30633022426</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>5.676212533837543</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000067e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8219186706503709</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1538.112</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9357893276679004</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1919.314721748608</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9404825967149674</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.6527e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-68.161</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4658720200752547</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.14646271510503</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.587276154571059</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.322985915492937</v>
+      </c>
+      <c r="L24" t="n">
+        <v>7.837979990338566</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.2370321315834</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12.00170550128092</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-23216.30797720005</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>18.62794420851549</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8221535652619504</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1504.796</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9155198302317036</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1882.891490276568</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9226348644345806</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.66039e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-68.76600000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.3756983240223543</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.5195367573010737</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.501974333662486</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.393579072532694</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>84.92505461052374</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>11.26038996916219</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-21325.90088680392</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>20.39178193534576</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000001162e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8222091634447025</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1474.565</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8971272507805788</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1859.435423670323</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9111411671370041</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.66399e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-69.14100000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.01629139072846818</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.6876080691642518</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.240201005025126</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.728072531900668</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.5083756495040356</v>
+      </c>
+      <c r="M26" t="n">
+        <v>84.4734213373351</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10.33514228192132</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-19260.08818227364</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>21.1021355010671</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000403e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8222789341415548</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1456.875</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8863646319293865</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1839.481997588538</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.901363797244452</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.66739e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-69.43600000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.797222222221707</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.5987261146496629</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.749275362318756</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.044019138755969</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>84.39960783810704</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10.19807022341702</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-18782.08376467229</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>20.9869656463826</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000003822e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8224245199003771</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1436.339</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8738705030018519</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1822.220106298233</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8929053051790509</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.67021e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-69.742</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1142857142857149</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.3544262295081979</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.045775301764169</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.767153846153811</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>84.07618099718908</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9.637613676733936</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-17512.34656175634</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>19.41426637406448</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000954e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8226179925527323</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1419.34</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8635282894432641</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1798.999184427475</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8815268310540627</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.67316e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-70.02200000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5517699115044945</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.4197120708748424</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.405296803652972</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.482151442307846</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>83.99663404680085</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>9.508990751549737</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-17069.87532735561</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>20.51357466342279</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.822864831062158</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1384.283</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8421995653581172</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1777.218161480906</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8708539211931752</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.67727e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-70.312</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.001857134415590141</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.5824440358438487</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.409311389880022</v>
+      </c>
+      <c r="K30" t="n">
+        <v>161.3871557774448</v>
+      </c>
+      <c r="L30" t="n">
+        <v>7.743216677337101</v>
+      </c>
+      <c r="M30" t="n">
+        <v>83.47238817139875</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>8.739439930026473</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-15432.59836525563</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>20.48905666561484</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000001008e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8231360229418946</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1368.206</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8324182977905299</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1757.17977821713</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8610349214677334</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.68281e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-70.572</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2458974358974174</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9644000000000549</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.297352024922137</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.862622309197636</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>83.38407604161917</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>8.621759723765363</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-15040.77787025728</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>20.19435687671387</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.00000000000003e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.823439546616572</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1355.843</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8248966326205304</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1739.605791931053</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8524234998651807</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.68569e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-70.791</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1099173553719306</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.4817073170731939</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.993661971831013</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.098720930232617</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>83.59096702059908</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>8.902530438412152</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-15376.03455005842</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>18.76089587097454</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.823755846138125</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1336.551</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8131593548999423</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1722.186713974467</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8438879848277796</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.69017e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-71.08</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1586056644880281</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.5190909090909129</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.6127129750982767</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.613631739572843</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>83.05696024543155</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>8.211828912674969</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-13960.51888178542</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>17.50161677228368</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8240940037430385</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1316.726</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8010977992908473</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1703.982400970154</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8349676970960677</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.69528e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-71.327</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.6098173515981552</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7236486486486938</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.197828863346105</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.577833500501537</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>82.61312021248209</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>7.713402240341975</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-12920.97525885741</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>16.51865386346162</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000012e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.824439880056978</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1292.945</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7866294081715594</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1685.738145172864</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8260278370132278</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.69888e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-71.563</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2997772264303737</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.7341005387874503</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.919615727231762</v>
+      </c>
+      <c r="K35" t="n">
+        <v>134.9165910818152</v>
+      </c>
+      <c r="L35" t="n">
+        <v>8.856622196533639</v>
+      </c>
+      <c r="M35" t="n">
+        <v>82.48480152314912</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>7.580215654036945</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-12542.35796933517</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>15.88656839937482</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8247961509654098</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1286.538</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7827313810952683</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1672.168293847494</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8193784798927382</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.70251e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-71.783</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3725856697819301</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.65656324582322</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.536585365853588</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.264893617021202</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>82.09753003249165</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>7.204330344332525</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-11738.95732576838</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>13.05955393556553</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8251521473337728</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1264.156</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7691141433831492</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1657.255181966119</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8120709122341528</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.70732e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-72.005</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.09201451905625552</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.342332613390901</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.40470756062764</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.138245219347435</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>81.84520404063061</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>6.978515579110808</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-11227.0086366115</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>10.71551887400653</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000002523e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8255125344964727</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1243.506</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7565506567083542</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1641.644131603171</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8044213480347926</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.71091e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-72.21899999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.267708762317431</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8670899335276891</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.742061237140803</v>
+      </c>
+      <c r="K38" t="n">
+        <v>6.648971451577206</v>
+      </c>
+      <c r="L38" t="n">
+        <v>9.999633598850501</v>
+      </c>
+      <c r="M38" t="n">
+        <v>81.8250895427506</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>6.961110440313986</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-11077.09485966097</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>9.418809448742309</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000131e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8258785088841245</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1222.46</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7437462431220234</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1627.456608030245</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7974693255969799</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.71498e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-72.47</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2252598853478025</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.4863307993201499</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.340424254473961</v>
+      </c>
+      <c r="K39" t="n">
+        <v>222.0461020926</v>
+      </c>
+      <c r="L39" t="n">
+        <v>7.81397569371829</v>
+      </c>
+      <c r="M39" t="n">
+        <v>81.03643831979308</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>6.339844167790614</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-9920.344163946565</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>7.445747780914985</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000128e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8262411842592029</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1214.631</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7389830694088528</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1611.806777337829</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.789800758664745</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.71864e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-72.687</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1762906309751435</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9829174664108274</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.392434662998503</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.803735632183932</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>79.37238831340754</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>5.329247540081708</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-8122.600467169436</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>6.614893050622641</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000915e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8265940936078365</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1190.607</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7243668367756678</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1596.911412651145</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7825018873015401</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.72255e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-72.911</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.01059876956813175</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.3243992355791574</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.441325307988031</v>
+      </c>
+      <c r="K41" t="n">
+        <v>35.48909235669068</v>
+      </c>
+      <c r="L41" t="n">
+        <v>8.353957243352188</v>
+      </c>
+      <c r="M41" t="n">
+        <v>79.3740569682499</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>5.330103930128508</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-8055.101954908589</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>5.157278835143302</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8269723034584328</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1178.969</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7172862625421926</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1582.182310540636</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7752844861931114</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.72595e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-73.10899999999999</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9723878903388321</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.960927134289194</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>10.97861997858375</v>
+      </c>
+      <c r="M42" t="n">
+        <v>78.08299783233819</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>4.738370995031646</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-6998.014253918594</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.80841251455422</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000000504e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8273353370494128</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1166.267</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7095583493342872</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1568.739211581626</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7686972389461635</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.73001e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-73.34</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.4953947368421447</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.058117520481102</v>
+      </c>
+      <c r="J43" t="n">
+        <v>358.2361475530578</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.767699649999159</v>
+      </c>
+      <c r="L43" t="n">
+        <v>11.23496669277206</v>
+      </c>
+      <c r="M43" t="n">
+        <v>74.91059589705391</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>3.708891747000915</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-5270.136166751174</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.152157824886672</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000012479e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8277055231048595</v>
       </c>
     </row>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,6 +7416,566 @@
         <v>1e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8228636931858677</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2064.958</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2473.755274136014</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.47098e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-60.345</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2503368623676738</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6286616886846471</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.404273858921136</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.798421169668669</v>
+      </c>
+      <c r="L12" t="n">
+        <v>39.26066559743369</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.74625765654378</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.87512574499219</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-26749.09270856584</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-7.323348717900672</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8200905420564774</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1826.03</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.884294014696667</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2198.838409787363</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8888665878864399</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.59225e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-64.264</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.05472636815920133</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7280320366132469</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.218796561604556</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.459468957438557</v>
+      </c>
+      <c r="L13" t="n">
+        <v>35.40976257885469</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.31455811676005</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.20119776463443</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-27066.49417195981</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>20.58018114350921</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8208648474971949</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1762.934</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8537384295467511</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2129.946187035416</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8610173404397583</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.61657e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-65.47199999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1352583586626175</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7505446623094025</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.639275956284139</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.481667309918941</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.01066443356866</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>11.45460776318867</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-24587.76846220544</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>25.39646263095824</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8210685047357984</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1736.608</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8409895019656572</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2092.772741277316</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8459902089580141</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.62951e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-66.148</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6610372340425219</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8157698056801249</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.133430742256008</v>
+      </c>
+      <c r="K15" t="n">
+        <v>174.1331821617531</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6.961567241737709</v>
+      </c>
+      <c r="M15" t="n">
+        <v>84.7079322811538</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>10.79592280664031</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-22734.58597698457</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>26.0733281395751</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.00000000019688e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8211823698758364</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1687.32</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8171207356275525</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2060.455418168988</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8329261344934876</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.64183e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-66.663</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3583434835566406</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.6355415352260882</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.259999999999965</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.286107784431023</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>83.69587766788189</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>9.051915611239215</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-18601.30345305698</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>26.44789296345039</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000241e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8213723981014407</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1665.352</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8064822625932343</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2032.746354862858</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8217249200500714</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.65391e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-67.111</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6368686868686673</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7930635838150775</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.467676767676839</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.763910761154819</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>83.03470530347117</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.185332102970408</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-16492.84802676491</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>25.0443686386169</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000014953e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8216248132197638</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1628.198</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7884896448257059</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2004.847978632022</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8104471770483591</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.66435e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-67.459</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1737847222222228</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.3862420382165547</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.175901495162729</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.916097077761236</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>82.87920329466156</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>8.004789855837927</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-15867.96524100771</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>24.15867358909702</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000001489e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.82188949392447</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1598.827</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7742661109814339</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1973.916818858056</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7979434503873746</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.67776e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-67.846</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3885634588563568</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.24547983310148</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.229591836734678</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.909664082687268</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>81.76779421434706</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>6.911995645591436</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-13392.60553694756</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>25.14888033418549</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8221916440689659</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1569.12</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.759879861963294</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1946.503661003196</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7868618538602346</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.68876e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-68.179</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2464012251148298</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5136239782016202</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.278227360308344</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.470738440303673</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>81.19911037390143</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>6.458943672136752</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-12272.7489078232</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>24.34403618436443</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000053e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8225428378599089</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1543.351</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7474006735245946</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1920.146978584585</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7762073308788466</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.69876e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-68.517</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.104749679075746</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8521103896103747</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.702304609218545</v>
+      </c>
+      <c r="K21" t="n">
+        <v>270.4158163265315</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5.854183510675107</v>
+      </c>
+      <c r="M21" t="n">
+        <v>80.22474139061949</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>5.804324937575564</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-10794.5618610638</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>24.16569564699171</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8228636931858677</v>
       </c>
     </row>
@@ -4518,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9308,1182 @@
         <v>1.000000000001634e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8271204443236575</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1653.006</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2117.112033057669</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.65784e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-65.36499999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1549234135667359</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7841256366723153</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.274252873563301</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.317019722425083</v>
+      </c>
+      <c r="L23" t="n">
+        <v>45.67542656572978</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.56228544008681</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.8852727813639</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-26604.87470843148</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-32.69885370488805</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.00000000000002e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8232333125127144</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1560.377</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9439633007986662</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1917.987912287618</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9059454021984549</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.68056e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-67.553</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.6516556291390079</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.315028901734066</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.704815073272805</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.735790370685948</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.32959225175115</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12.24064902928935</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-23930.41968659493</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>25.38027457417479</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000000024e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8222037681080281</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1512.67</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.915102546512233</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1897.679279185489</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8963527907612611</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.69365e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-68.133</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1611023622047158</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.4715762273901579</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.8545353982300221</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.664186046511682</v>
+      </c>
+      <c r="L25" t="n">
+        <v>10.52590894672121</v>
+      </c>
+      <c r="M25" t="n">
+        <v>84.76062942108304</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>10.90512420979309</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-20799.78435183375</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>20.78716075913326</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.822051624670001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1497.537</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9059477098086758</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1875.180210133127</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.885725545390657</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.70344e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-68.48999999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5862433862433301</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9122377622377509</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.596229802513449</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.200059171597498</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>84.74273982432568</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10.86780782170767</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-20488.69997991271</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>20.86238621931989</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000003598e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8220916949254755</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1470.086</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8893409945275457</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1854.384585280449</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8759029075103919</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.71011e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-68.74299999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3935652173912987</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.7655263157895068</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.009775086505134</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.863333333333299</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2.342511895202115</v>
+      </c>
+      <c r="M27" t="n">
+        <v>84.48996503234633</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10.36636622202483</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-19278.11534444883</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>20.71708441072383</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000001432e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8221880205424738</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1454.206</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8797342538381593</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1834.915709152875</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.866706948192426</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.71684e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-69.023</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1708955223880645</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.5300389105058139</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.672238514173972</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.313247362250765</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>84.41211347390004</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10.22103926347767</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-18801.33133444286</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>20.71405620535302</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000018e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8223490635523646</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1434.165</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8676102809064214</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1814.49245481292</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8570601963809698</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.72394e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-69.292</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3823617339312608</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8615835777125675</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.661111111111147</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.466819371727763</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>84.22639826351902</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>9.890137661658422</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-17967.85918710846</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>20.4570540651689</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000676e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8225627796279517</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1414.712</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.855842023561923</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1796.460454334671</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8485429331484682</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.73011e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-69.554</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.8513089005235369</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6718220338983197</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.475136116152505</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.448584298584322</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>84.01308378521934</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>9.535309737974229</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-17097.27075471849</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>19.27190616772646</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8228046894797199</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1393.566</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8430495715079075</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1778.366379899264</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8399963498062185</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.738e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-69.855</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.07552742616032819</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.4673151750972815</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.760132890365512</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.006757843925887</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>83.2342641148764</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>8.429123361941482</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-14856.2406325536</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>18.55251265189702</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8230699406618915</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1372.689</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.830419853285469</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1756.14757910088</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8295014867798656</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.73995e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-70.059</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1355263157894502</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.4376249999999644</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.240355029585817</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.85544703230658</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>83.46946754329267</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>8.735497385260576</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-15261.00259271918</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>20.48488450111381</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.00000000000002e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8233651418284813</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1352.863</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8184259464272968</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1739.872436905254</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8218140607289536</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.74768e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-70.33499999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2967370441458553</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.2879699248120292</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.6229577464788624</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.438682432432453</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>82.69994191030902</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>7.806158414285634</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-13408.68380952146</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>19.02420875661824</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8236660766185427</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1332.451</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8060775338988486</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1725.860828165234</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.815195795601159</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.75174e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-70.557</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1740975077081064</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7745059754498637</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.417360560640208</v>
+      </c>
+      <c r="K34" t="n">
+        <v>180.4342785643213</v>
+      </c>
+      <c r="L34" t="n">
+        <v>8.225472155469568</v>
+      </c>
+      <c r="M34" t="n">
+        <v>82.59350423339932</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>7.692744976888316</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-13069.58629970245</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>16.89866926263232</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000005184e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8239785177168746</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1319.375</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7981670967921473</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1706.639408558042</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8061167202820173</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.7566e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-70.79000000000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.07228017883756932</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.5903743315508162</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.872657743785835</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.830857740585665</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>82.0950520240951</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>7.202043060715459</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-12063.39893161598</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>17.75131146551018</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.824319895403579</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1305.521</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7897860019866838</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1696.410298674444</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.801285086564068</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.7625e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-71.023</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.7080691642650176</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.03500000000012</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.120486111111598</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.706535269709471</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>81.45129944275661</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>6.652471093500997</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-10976.93973333983</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>13.9566794282199</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8246568875002308</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1287.448</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7788525873469305</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1683.026334637798</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7949632841144754</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.76572e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-71.26900000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2940217391304338</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.5027950310559265</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.060914760914743</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.405245346869701</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>80.5446591910015</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>6.0045116892535</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-9732.800878275835</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>12.25204792546356</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000026e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8249424076402582</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1277.658</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7729300438110932</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1667.320417684007</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7875447268021788</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.77116e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-71.499</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.5907407407406674</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9509459459459231</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.09574468085107</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.951561248999203</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>78.20205392491371</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>4.787587379052066</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-7522.882911668597</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>10.8877388767786</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8252732783295348</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1253.345</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7582216882455358</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1650.972955373452</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7798231409553754</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.77452e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-71.691</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.05265833102465583</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.7998210873784934</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.902399482802148</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>9.373800261783792</v>
+      </c>
+      <c r="M39" t="n">
+        <v>79.81499891722838</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>5.566126354006498</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-8795.636872520881</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>10.39692542397518</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8256325459764058</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1246.089</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7538321095023249</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1640.568285491202</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7749085829538214</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.78037e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-71.929</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.857142857142704</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9847133757962135</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.7144047619047696</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.830672748004423</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>76.68177150693184</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>4.224294248849631</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-6428.455628008577</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>6.781719017732371</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000125e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8260036706665999</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1225.326</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7412713565468003</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1627.787718600611</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7688717900533849</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.78435e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-72.149</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.02145110410093945</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.708555133079825</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.41637426900578</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.649490268767301</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>74.58129143416832</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>3.625852327212794</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-5358.523427761919</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>4.2780034651189</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000021e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8263735995242902</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1206.616</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7299525833542044</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1611.247422854824</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7610591209609996</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.7898e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-72.392</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.005976717288810052</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8701798541264308</v>
+      </c>
+      <c r="J42" t="n">
+        <v>376.4305183689333</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.284040568836838</v>
+      </c>
+      <c r="L42" t="n">
+        <v>10.15971456049067</v>
+      </c>
+      <c r="M42" t="n">
+        <v>72.7319841918561</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>3.216954237310666</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-4640.010902268752</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.928439036480313</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8267393185947064</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1200.128</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7260276127249387</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1593.987026905801</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7529063186153936</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.79508e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-72.57299999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.5602150537634824</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9211188811189446</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.729335260115459</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>6.935952516011239</v>
+      </c>
+      <c r="M43" t="n">
+        <v>56.62122742932809</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.517802909463928</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-1761.507980488734</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.84372342598283</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000001634e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8271204443236575</v>
       </c>
     </row>
@@ -5850,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6552,6 +11200,566 @@
         <v>1.000000000000297e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8203877992848398</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2260.513</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2762.492372994792</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.33552e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-57.967</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.09109286165508743</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6247368421052423</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.23029480217222</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.445699765441741</v>
+      </c>
+      <c r="L12" t="n">
+        <v>25.89752808988752</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.80765960470836</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.216632053565732</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-24610.88784398716</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-55.78825638246212</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8174605004191169</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1824.185</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8069783274858404</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2228.587561773107</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8067307564571177</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.57134e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-63.752</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1692753623188512</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3643251775848382</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.22494261667939</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.818419777023742</v>
+      </c>
+      <c r="L13" t="n">
+        <v>27.90072492848662</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.06810833982642</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11.58869756141384</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-25885.72601678587</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>9.407851532424502</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000201e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8186566601939841</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1734.85</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7674585370665861</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2126.856157474734</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.769904807074283</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.61433e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-65.229</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.05367454068241435</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5109987357774642</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.354144805876208</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.990791599353727</v>
+      </c>
+      <c r="L14" t="n">
+        <v>24.20834884299304</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.09578309874748</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>11.65441643966845</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-24952.47167301413</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>18.2205302990285</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.00000000000012e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8188875523917936</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1701.509</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7527092301614721</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2085.728882162128</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.755017064499986</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.62997e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-65.84099999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4908979089790891</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6739959839357871</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.304851425106044</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.635847526358431</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.34465363018386</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>12.28042671939983</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-25876.23364109322</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>19.89473212230769</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000314e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8189936531108708</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1666.333</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7371481606166386</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2056.697381608442</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7445078950132251</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.64377e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-66.319</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.03820422535212128</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7253079507278997</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.23071297989036</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.017837837837821</v>
+      </c>
+      <c r="L16" t="n">
+        <v>8.090640802271711</v>
+      </c>
+      <c r="M16" t="n">
+        <v>84.89622426258084</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>11.196447109231</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-23152.4503518414</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>19.58996095827933</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8191128686660192</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1636.368</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7238923200176242</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2029.648662781059</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7347164765493037</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.65565e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-66.71299999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1233807266982714</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.053680203045704</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.605777310924286</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.060463800904861</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>84.68915754534621</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>10.75753905720819</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-21908.66417864332</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>19.40443609071258</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000000108e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8192964298817575</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1616.489</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7150982984835742</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2001.407664141379</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.724493462391598</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.66743e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-67.089</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4805377720870485</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8029940119760549</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.696036801132299</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.781554227156302</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>84.67237947613681</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>10.72346561705794</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-21553.71420906695</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>19.38604583268261</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000139e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8195047748476998</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1576.785</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6975341437983323</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1974.244533748061</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7146606278618611</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.68108e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-67.413</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1259677419354762</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.7469026548672157</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.908752025931885</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.65399293286225</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.123815247365526</v>
+      </c>
+      <c r="M19" t="n">
+        <v>84.05347696306657</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>9.600552881772764</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-18920.23360691632</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>19.51390078248255</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000144e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8197871273052044</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1556.787</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6886874793465021</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1949.371911986723</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.70565693901751</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.69206e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-67.696</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.100273972602726</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5396026490065886</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.152487008166276</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.253723706651552</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>84.25065353894558</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>9.932145258561153</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-19355.01344117668</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>18.29989610074267</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.820086404286682</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1526.186</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.675150286682713</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1921.810801735908</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6956800389832357</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.70435e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-68.003</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2180821917808301</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.048662207357943</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.203913630229352</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.792718822618102</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>83.89167338657766</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>9.344383178060468</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-17907.33525987165</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>19.34965931550903</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000000297e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8203877992848398</v>
       </c>
     </row>
@@ -6566,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +13092,1182 @@
         <v>1.000000000000155e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8283381996472022</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1609.91</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2005.108076574099</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.70776e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-64.414</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.07584905660377424</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.064193548386997</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.670253807106499</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.073858695652242</v>
+      </c>
+      <c r="L23" t="n">
+        <v>23.44648566664206</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.11404348831725</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11.69818581270852</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-23620.79989265063</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>7.783668041533247</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000508e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8226285353246754</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1533.943</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.952812890161562</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1912.050336842883</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9535896639096813</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.70426e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-67.10299999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2406578947368502</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.046183206106803</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.430521091811341</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.026781970649952</v>
+      </c>
+      <c r="L24" t="n">
+        <v>33.57000149001077</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.68576719638271</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.25553288850296</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-25690.8969326318</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>18.65799538038948</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.00000000000296e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.822687494559461</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1501.203</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9324763496096056</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1879.448920195859</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9373304821588772</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.71258e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-67.789</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.7180645161290309</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.591984732824409</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.656389452332802</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.373803827751231</v>
+      </c>
+      <c r="L25" t="n">
+        <v>26.03766825901814</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.58964852361886</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>12.96553632930162</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-24674.24474221483</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>19.93416232075538</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.00000000000007e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8227010879327041</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1470.704</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9135318123373357</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1855.633229631781</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.925452972491284</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.72158e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-68.175</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.064578833693177</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.6492588369441223</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.9906542056074612</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.9778681855167</v>
+      </c>
+      <c r="L26" t="n">
+        <v>20.83001940265311</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.3194994772585</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>12.21413655300717</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-22867.40411278554</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>19.86999136871464</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000369e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8227968142890212</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1447.689</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8992359821356474</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1831.432562999532</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9133834651589919</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.73062e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-68.462</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1124555160142279</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.3077008928571481</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.322046285018268</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.746796874999952</v>
+      </c>
+      <c r="L27" t="n">
+        <v>20.15279901815257</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.370899357526</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>12.35035987792007</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-22849.57908735387</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>20.27380654543583</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8229708081128672</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1420.083</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8820884397264445</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1810.589787868157</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9029886264094585</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.7394e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-68.74299999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2934086629001744</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.3926380368097859</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.650085470085539</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.587379576107959</v>
+      </c>
+      <c r="L28" t="n">
+        <v>18.14656418307256</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.16055918361722</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>11.8111706923796</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-21523.63167762938</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>19.31270753126375</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000114e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8232214068193421</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1407.208</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8740910982601513</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1787.186028505083</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8913165576384515</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.75028e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-69.087</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.4926708074534421</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.417706576728563</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.595721393034925</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.809263311451663</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.624638146692394</v>
+      </c>
+      <c r="M29" t="n">
+        <v>85.33776379585787</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>12.26219857478057</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-22142.38100978825</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>19.81729949192004</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000784e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8234818555599837</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1387.607</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.861915883496593</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1770.591577754489</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8830404697085946</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.75623e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-69.34699999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3753564154785911</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.3752762430938947</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.5808344198175</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.747588652482267</v>
+      </c>
+      <c r="L30" t="n">
+        <v>11.96818497705109</v>
+      </c>
+      <c r="M30" t="n">
+        <v>85.13304476401103</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>11.74407890610036</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-20908.72258690815</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>17.66539717526302</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8237680616765072</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1366.414</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.848751793578523</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1751.848521365911</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8736928157803325</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.76358e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-69.59</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2436585365854118</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.550761421319756</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.594674556213093</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.834782608695657</v>
+      </c>
+      <c r="L31" t="n">
+        <v>11.09635722699806</v>
+      </c>
+      <c r="M31" t="n">
+        <v>85.17625381144693</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>11.8497828169039</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-20853.77385718287</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>16.14816265786919</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.00000000000128e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8240725341018178</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1347.876</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8372368641725314</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1731.284164289733</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8634368314189736</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.77004e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-69.914</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1056179775281018</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.5942890442889717</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.534677419354755</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.072188841201735</v>
+      </c>
+      <c r="L32" t="n">
+        <v>4.700042027831177</v>
+      </c>
+      <c r="M32" t="n">
+        <v>84.97806591274967</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>11.37987483363913</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-19764.40946694198</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>16.34790491630247</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8243843461484566</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1323.162</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.82188569547366</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1713.888414407097</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.854761114590603</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.77827e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-70.126</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1457085828343149</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.181107491856748</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.7885148514851397</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.463856427378901</v>
+      </c>
+      <c r="L33" t="n">
+        <v>9.830817834200094</v>
+      </c>
+      <c r="M33" t="n">
+        <v>84.73535267549072</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>10.85247254574038</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-18589.9176031032</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>15.05757951050441</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000010839e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8247131982781635</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1305.796</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8110987570733768</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1698.147746736584</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8469108306810157</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.78304e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-70.42400000000001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.7941988950275826</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.1318234610917418</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.7736543909347754</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.012550607287457</v>
+      </c>
+      <c r="L34" t="n">
+        <v>6.755100425087938</v>
+      </c>
+      <c r="M34" t="n">
+        <v>84.52678892630873</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>10.43654181402999</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-17643.11913838646</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>13.24144960056492</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000047e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8250518781297221</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1286.966</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7994024510686935</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1680.877328946706</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8382976202552783</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.78987e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-70.67100000000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2978896103896136</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.054352030947658</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.6036748329621043</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.679307201458577</v>
+      </c>
+      <c r="L35" t="n">
+        <v>4.180720242968725</v>
+      </c>
+      <c r="M35" t="n">
+        <v>84.36149186208348</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>10.12868931363004</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-16908.97798759751</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>11.87917037696502</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8254103940322196</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1274.237</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7914957979017462</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1663.926158115734</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8298436266631051</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.79545e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-70.928</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.6541198501872596</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.658260869565182</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.667524509803852</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.872619047619055</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>84.31767378985994</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>10.05007549814596</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-16587.38220079639</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>10.11701911222576</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000019e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8257762745721798</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1255.979</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7801547912616235</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1654.201070744637</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8249934704621918</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.80233e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-71.17400000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.6683257918550842</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.3953599999999707</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.261853188929063</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.745937813440248</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>84.01873278681242</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>9.544381207279393</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-15529.55453338808</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>5.161889552981052</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000004754e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8261421362313737</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1236.098</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7678056537321962</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1632.970251542052</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8144051039543581</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.80835e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-71.425</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.5019955654102487</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.7874476987446895</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.003699136868</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.183928571428503</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>83.59985721293998</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>8.915000287946038</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-14299.69784118015</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>6.964834839646528</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000352e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8264937808231316</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1218.23</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7567068966588195</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1615.994153659497</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8059386785876214</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.81236e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-71.65300000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1499199999999961</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.4361921097769856</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.532315112540325</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.467336244541429</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>83.48341894311713</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>8.754362067652787</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-13869.47120063771</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>6.30495031359294</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000137e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8268651153805456</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1200.111</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7454522302488958</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1600.539655407945</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7982311148746682</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.81805e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-71.911</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2925696996148781</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.562924099970449</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.85518955223104</v>
+      </c>
+      <c r="K40" t="n">
+        <v>162.1301122954848</v>
+      </c>
+      <c r="L40" t="n">
+        <v>8.814223924086953</v>
+      </c>
+      <c r="M40" t="n">
+        <v>82.93010656660049</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>8.063020024023471</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-12577.83482922228</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>5.116061153145324</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.827226381242459</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1182.871</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7347435570932537</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1585.401732693843</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7906814356873169</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.82349e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-72.129</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2925970109286169</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.6305830558962776</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.929434579345934</v>
+      </c>
+      <c r="K41" t="n">
+        <v>123.1873000005592</v>
+      </c>
+      <c r="L41" t="n">
+        <v>9.270953039274513</v>
+      </c>
+      <c r="M41" t="n">
+        <v>82.63846008968149</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>7.740249301497883</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-11912.07840534174</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>3.338510087804025</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000036e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8275886121577776</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1166.748</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7247287115428813</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1570.780560455152</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7833894735185378</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.82974e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-72.36199999999999</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1596055150152194</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9359730132649966</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.758762539153802</v>
+      </c>
+      <c r="K42" t="n">
+        <v>47.57537566104428</v>
+      </c>
+      <c r="L42" t="n">
+        <v>9.611448363536983</v>
+      </c>
+      <c r="M42" t="n">
+        <v>82.06207163726515</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>7.171736193512427</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-10863.72742988273</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.833739956997533</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8279650952822593</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1147.86</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7129963786795536</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1556.213598822791</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7761245476013029</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.83504e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-72.586</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.06827836582401391</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.6569812868080362</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.458485667041711</v>
+      </c>
+      <c r="K43" t="n">
+        <v>225.367033219555</v>
+      </c>
+      <c r="L43" t="n">
+        <v>7.87666188600532</v>
+      </c>
+      <c r="M43" t="n">
+        <v>81.54512984426755</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>6.727399900304138</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-10041.34775171374</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.4581304921989613</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000155e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8283381996472022</v>
       </c>
     </row>
@@ -7898,7 +14282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +14984,566 @@
         <v>1.000000000004319e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8247797665825782</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2080.499</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2620.997616905779</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.42018e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-58.858</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.008651026392965833</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7536173089925484</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.558067299396029</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.618088597210754</v>
+      </c>
+      <c r="L12" t="n">
+        <v>20.3586741442251</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.54108925815363</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.833203180643856</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-21927.46412757324</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-72.91478190006001</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8221723623971363</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1752.981</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8425771894146551</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2201.784037560693</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8400557189975668</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.60505e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-64.26900000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4456007568590308</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9687327823691341</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.770609981515682</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.215442124258851</v>
+      </c>
+      <c r="L13" t="n">
+        <v>88.51087387189081</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.6027742174788</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.00439145413499</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-28086.54560608976</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-25.98671973814839</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000125615e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8230839475952438</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1667.415</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8014495560920722</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2116.834576033451</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8076446015744498</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.63961e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-65.637</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.06873065015479886</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.222237569060778</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.604619758351159</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.568809904153365</v>
+      </c>
+      <c r="L14" t="n">
+        <v>45.13849373294494</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.56660121506683</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>12.89786647213452</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-26752.54792915133</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-20.36506733297347</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000057e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.823231155927322</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1631.705</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7842854046072602</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2078.461364798904</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7930039124768961</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.65618e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-66.33199999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2373477672530448</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.792187500000004</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.410830564784058</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.747711340206129</v>
+      </c>
+      <c r="L15" t="n">
+        <v>32.58256966503075</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.52692118623042</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>12.78299136164219</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-25998.34806713569</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-19.88308728601646</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000004148e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8233075400036555</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1600.884</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7694711701375488</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2049.19079644296</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.781836192152717</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.66848e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-66.77</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5774946921444087</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7767556874381277</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.708462104488579</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.566574037316406</v>
+      </c>
+      <c r="L16" t="n">
+        <v>18.72253390820691</v>
+      </c>
+      <c r="M16" t="n">
+        <v>85.56520778885677</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>12.89379769666671</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-25847.10498817057</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-20.05471520481376</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000271e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8234394011820801</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1560.339</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7499830569493184</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2018.69450230858</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7702008156313213</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.68399e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-67.169</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.08157480314960862</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.09305019305018739</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.151591657519093</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.651052274270251</v>
+      </c>
+      <c r="L17" t="n">
+        <v>18.88880736851029</v>
+      </c>
+      <c r="M17" t="n">
+        <v>84.93502674377717</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>11.28267616714277</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-22128.90027751403</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-18.9832086717621</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000000154e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.823644715759061</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1539.223</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7398335687736453</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1996.151878158267</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7616000355295348</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.69516e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-67.535</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.04660056657223897</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.6382413087934158</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.525897920604922</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.053931339977845</v>
+      </c>
+      <c r="L18" t="n">
+        <v>13.56455503513303</v>
+      </c>
+      <c r="M18" t="n">
+        <v>85.17315262309545</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>11.84213337489338</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-22968.99222627899</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-21.80974443873049</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000023e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8239043968418819</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1505.867</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7238008766166194</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1967.618501946579</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7507135791559599</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.71144e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-67.88800000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1167400881057179</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.531403762662749</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.690322580645145</v>
+      </c>
+      <c r="L19" t="n">
+        <v>12.94642971227228</v>
+      </c>
+      <c r="M19" t="n">
+        <v>84.71958730230838</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>10.81988767641835</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-20592.58714415694</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-21.74352575286946</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8241806170065185</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1480.734</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7117206016441249</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1942.727176705177</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7412166894675264</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.72276e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-68.184</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.05263157894736913</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.1687086092715229</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8568083261057844</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.683510638297869</v>
+      </c>
+      <c r="L20" t="n">
+        <v>11.92422172197388</v>
+      </c>
+      <c r="M20" t="n">
+        <v>84.7263210322689</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>10.83378160695113</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-20336.39985406741</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-22.52934665384237</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000024e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.824483680296065</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1463.063</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7032269662230071</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1917.697106524807</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7316668638519197</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.73653e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-68.511</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2019036954087416</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8024060150376519</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.629750271444179</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.206484069312374</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>84.72152588834932</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>10.82388400250907</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-20051.69724667293</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-23.61365804720492</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000004319e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8247797665825782</v>
       </c>
     </row>
@@ -8614,7 +15558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +16876,1182 @@
         <v>1.000000000001233e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8257861209646697</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1641.585</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2058.071577840234</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.67715e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-65.196</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.09565217391305351</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.3760362694300565</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.266295979469627</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.028315217391322</v>
+      </c>
+      <c r="L23" t="n">
+        <v>30.76157683985218</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.36396841722031</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.33181524001659</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-25415.24457657672</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.3197883663378889</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8203766296225971</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1541.11</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9387939095447387</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1932.503123285811</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9389873239072687</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.70687e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-67.27200000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4249999999999682</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8628468033775595</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.973017902813367</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.380555555555528</v>
+      </c>
+      <c r="L24" t="n">
+        <v>18.24815844735111</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.40269372275485</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12.43614488624027</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-24266.66695552331</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>16.78285982206148</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000008756e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8205588836508823</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1509.271</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9193986299826082</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1911.645026594586</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.928852546810199</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.71843e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-67.739</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.6311396468699522</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.071835443037821</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.602328042328213</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.402256097561017</v>
+      </c>
+      <c r="L25" t="n">
+        <v>6.343517764773297</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.19808684191781</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>11.90391550482903</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-22851.76486192156</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>13.29138240098905</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000001023e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8203056810271685</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1482.039</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9028097844461298</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1890.225905361504</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9184451725168525</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.72525e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-68.03700000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4953586497890795</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.9291237113401298</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.61889999999995</v>
+      </c>
+      <c r="L26" t="n">
+        <v>13.38990426544112</v>
+      </c>
+      <c r="M26" t="n">
+        <v>84.67205111985109</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10.72280091545431</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-20270.92972786303</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>12.93823033777369</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000014e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8201814990230871</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1458.855</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.88868684838129</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1872.087111273708</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9096316821197736</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.73475e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-68.292</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.03059418457648222</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.4854563691073385</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.652229299363019</v>
+      </c>
+      <c r="L27" t="n">
+        <v>10.86412025406285</v>
+      </c>
+      <c r="M27" t="n">
+        <v>84.46964869843256</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10.32804802326924</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-19303.39749494659</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>12.83283564656597</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000000071e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8202410733306622</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1445.709</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8806787342720601</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1855.061145616849</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9013589058761377</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.74087e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-68.557</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.07424242424241982</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.5051820728291012</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.389192886456758</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.13207222699904</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3.32610079702669</v>
+      </c>
+      <c r="M28" t="n">
+        <v>84.54512158834066</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10.47183069327585</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-19394.21719050666</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>11.48561304326779</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8204063357584395</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1426.926</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8692367437567959</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1834.444865515852</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8913416254652043</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.74862e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-68.82299999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2285340314135975</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.4889724310777098</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.9429463171035998</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.031394422310729</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>84.34071743962127</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>10.09126674292746</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-18463.94432362843</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>12.43222803191736</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8206406573280738</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1407.073</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8571429441667657</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1815.599571737194</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8821848526971577</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.75641e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-69.098</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3391941391941372</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.645475638051205</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.8373549883990704</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.941515151515152</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>84.02412406788345</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>9.553054751683643</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-17245.96001469352</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>11.63058871236228</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8209354191250118</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1388.039</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8455480526442432</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1795.309455664683</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8723260526967207</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.76416e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-69.379</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.04947807933195218</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.4847477064219801</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.9733131923464232</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.865937940761754</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>83.7070182799701</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>9.068070379306514</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-16150.70519243724</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>11.71956163860307</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8212700572724676</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1370.136</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8346421294054222</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1775.684483827368</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8627904407925373</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.76847e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-69.63800000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1564903846153702</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9706375838925765</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.119244391971689</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.10378469301945</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>83.55096211806342</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>8.846841128214962</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-15566.30593815601</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>12.37101244738415</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8216069672646281</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1347.418</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8208030653301536</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1757.573318593986</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8539903750278723</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.77809e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-69.866</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1739932885906085</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.1132379248658307</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.6405815423514604</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.569369369369288</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>83.20510911841539</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>8.392617186799223</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-14565.46814579631</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>11.7757936727603</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000000215e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8219646244819373</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1331.037</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8108242948126354</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1739.918127451593</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8454118633121038</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.78218e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-70.121</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.4521164021163669</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9412955465588009</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.6748878923766799</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.931951466127305</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>82.94416941427731</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>8.079254406962169</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-13845.92294194618</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>11.40008192322898</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000008911e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8223245235574083</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1308.014</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7967994346926902</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1723.469095536748</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8374194144138457</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.78952e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-70.384</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1515644652222351</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.5222139229722351</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.593047566679986</v>
+      </c>
+      <c r="K35" t="n">
+        <v>164.8279800581413</v>
+      </c>
+      <c r="L35" t="n">
+        <v>7.702394480825878</v>
+      </c>
+      <c r="M35" t="n">
+        <v>82.35141532004666</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>7.44647967384027</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-12564.12392974316</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>10.3681748381066</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8226886039602009</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1304.887</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7948945683592381</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1704.15454176901</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8280346320886329</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.79522e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-70.627</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.204555808655929</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9003048780487891</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.356282722513064</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.783816793893121</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>81.72614278279597</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>6.876715204637087</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-11413.52851561091</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>10.46532278964708</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000375e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8230478757267712</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1276.011</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7773042516835863</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1684.024134133701</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8182534331001925</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.80144e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-70.851</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.01718438594787496</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.5826787007632475</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.772797842865857</v>
+      </c>
+      <c r="K37" t="n">
+        <v>145.0816396550703</v>
+      </c>
+      <c r="L37" t="n">
+        <v>8.281208609144949</v>
+      </c>
+      <c r="M37" t="n">
+        <v>81.72800993101737</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>6.878289200609808</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-11297.33283682459</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>11.29602623198855</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000034e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8234251189461679</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1263.615</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7697530130940525</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1673.738984427822</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8132559637134994</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.80707e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-71.101</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.0949675324675343</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.521678321678396</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.146218487394926</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.7291224686595</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>80.84340596270073</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>6.203962595418215</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-10003.08752512914</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>6.266945215914461</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000005716e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8238082332403217</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1253.506</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7635949402559112</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1665.212843277035</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.809113182071408</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.8138e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-71.339</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.9046109510085468</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.7600512163892895</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.053241232731154</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.868485780169084</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>79.33274326220959</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>5.308978731405515</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-8347.899868589046</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-1.076696565551515</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.587433214147698e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.7908331714846627</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1231.156</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7499800497689733</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1649.031460618941</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8012507817388232</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.81942e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-71.55500000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1497584541062756</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.4835755813953593</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.280663780663775</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.151728553137068</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>79.67337303619779</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>5.488145367605095</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-8566.868599982852</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-2.299710315147649</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000039775e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8246121096991341</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1212.164</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7384107432755538</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1624.492548852389</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7893275269644178</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.82641e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-71.806</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.7782894736843026</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.6825795644891205</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.23505535055348</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.852758620689751</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>77.64206186317803</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>4.564234753341464</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-6923.488510870208</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.292522854324716</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000508e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8249970307486727</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1195.068</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7279964180959257</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1608.817422867226</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7817111125724495</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.83264e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-72.03100000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1429894179894242</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.7417102966841128</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.412701252235966</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.485355987055041</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>76.05685305220399</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>4.027803019965535</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-5957.6595670581</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.5222102948235943</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000002211e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8253992353999942</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1179.113</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7182771528735947</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1592.926170744112</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7739896842731531</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.83908e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-72.285</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.8309197651664135</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.326582278481058</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.007177615571756</v>
+      </c>
+      <c r="K43" t="n">
+        <v>454.6464218455981</v>
+      </c>
+      <c r="L43" t="n">
+        <v>5.943241914527687</v>
+      </c>
+      <c r="M43" t="n">
+        <v>71.097240544453</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>2.920302033270598</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-4080.115603521277</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-1.448790073567579</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000001233e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8257861209646697</v>
       </c>
     </row>
@@ -9946,7 +18066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18771,566 @@
         <v>0.8242397079789507</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1458.226</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2018.696597493404</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.67718e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-66.506</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2852542372881259</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7714851485148612</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.096014492753658</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.046406882591032</v>
+      </c>
+      <c r="L12" t="n">
+        <v>25.80996261284777</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.3613115306383</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>12.32472105366688</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-23546.06347275934</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-77.27646410752709</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000002262e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8220579956095682</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1300.667</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8919515904942031</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1825.671717906518</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9043814311538624</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.72726e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-69.238</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1531568228105742</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7410931174088786</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.9187777777777901</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.726666666666739</v>
+      </c>
+      <c r="L13" t="n">
+        <v>25.05202177734791</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.66532433142999</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.19278067786018</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-23123.06722751787</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-48.09384228150225</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000027e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.822387035401384</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1261.579</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8651464176334808</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1781.260407695736</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8823814385517414</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.74296e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-69.887</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2209359605911179</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.499839486356329</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.700798722044964</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.255249999999957</v>
+      </c>
+      <c r="L14" t="n">
+        <v>25.84946700873441</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.77257657518797</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13.52875406994632</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-23170.73634900921</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-45.57320810102487</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000002281e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8224192081911762</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1238.778</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8495102953863116</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1866.982347164496</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9248454420950178</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.75188e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-70.28700000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3371757925072901</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.718956043956055</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.9045081967213567</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.791830708661422</v>
+      </c>
+      <c r="L15" t="n">
+        <v>24.82427040488874</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.74195647875764</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13.43111193371858</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-22692.42861385292</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-102.4912095183934</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.00000000008713e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8224901751808166</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1211.349</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8307004538391168</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1850.749339953219</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9168041112524169</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.76046e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-70.55500000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1946758238096207</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.6787346603253223</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.630020923073599</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.894761539382507</v>
+      </c>
+      <c r="L16" t="n">
+        <v>26.49121766762209</v>
+      </c>
+      <c r="M16" t="n">
+        <v>85.55789911488958</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>12.87249824511795</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-21424.85353608882</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-105.7930696168235</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000029612e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8226381285534451</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1197.885</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8214673171373985</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1826.85494213805</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9049675639253754</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.76752e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-70.846</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.06146179401994146</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.3204347826087292</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.8577992744860031</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.351133501259423</v>
+      </c>
+      <c r="L17" t="n">
+        <v>24.44619133088342</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.77356266450983</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13.53192200844641</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-22272.91136226284</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-106.7188284685343</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8228701369842584</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1176.457</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8067727499029643</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1799.722274253229</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8915268775347055</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.78237e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-71.167</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.7244274809162158</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.4811111111111239</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.7914749661704583</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.827318045862494</v>
+      </c>
+      <c r="L18" t="n">
+        <v>22.36312351692236</v>
+      </c>
+      <c r="M18" t="n">
+        <v>85.70049180232654</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>13.30110111065315</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-21553.44727666653</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-105.6129120718359</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8231657023917989</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1151.93</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7899529976834866</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1682.102210689821</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8332615276503021</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.79261e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-71.404</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.126560232220608</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4869639794168606</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.074228187919477</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.37984693877555</v>
+      </c>
+      <c r="L19" t="n">
+        <v>23.63977950402403</v>
+      </c>
+      <c r="M19" t="n">
+        <v>85.80781188803128</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>13.64287515778695</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-21796.94330786216</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-55.23625861927815</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000001536e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.823499001339231</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1126.673</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7726326371906687</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1770.124639606275</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8768651226758003</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.80209e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-71.727</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3084636983553835</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.7324676492259518</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.635679175354032</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.103264310815551</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>85.49453606475325</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>12.69073188331934</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-19913.25335132917</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-119.4952113492691</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000896e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8238785133233281</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1101.556</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7554082837639707</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1657.758428238273</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.821202369041834</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.81368e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-71.98699999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1387749823776312</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.5792369352932712</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.282594385916409</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.426737320119038</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.172320968194426</v>
+      </c>
+      <c r="M21" t="n">
+        <v>85.31105570871897</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>12.19204330356146</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-18812.88591572936</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-69.62280912470362</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000000064e-08</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.8242397079789507</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
